--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1339,7 +1339,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
     <row r="8" ht="15" customHeight="1">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A 33685-2025</t>
+          <t>A 8529-2023</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="D8" s="1" t="n">
-        <v>45841</v>
+        <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1483,19 +1483,19 @@
         </is>
       </c>
       <c r="I8" t="n">
-        <v>12.2</v>
+        <v>2.7</v>
       </c>
       <c r="J8" t="n">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="M8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -1507,21 +1507,151 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="S8" t="n">
         <v>18</v>
       </c>
       <c r="T8" t="n">
+        <v>25</v>
+      </c>
+      <c r="U8" t="n">
+        <v>25</v>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Brunlångöra
+Dropptaggsvamp
+Ladusvala
+Rödvingetrast
+Talltita
+Tvåblad
+Tofsmes
+Buskskvätta
+Grönsiska
+Kråka
+Kungsfågel
+Svartvit flugsnappare
+Sävsparv
+Huggorm
+Skogsödla
+Fläcknycklar
+Revlummer</t>
+        </is>
+      </c>
+      <c r="W8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/artfynd/A 8529-2023 artfynd.xlsx", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="X8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/kartor/A 8529-2023 karta.png", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="Y8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/kartor_geotiff/A 8529-2023 georefererad karta.tif", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="Z8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/knärot/A 8529-2023 karta knärot.png", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="AA8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/klagomål/A 8529-2023 FSC-klagomål.docx", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="AB8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/klagomålsmail/A 8529-2023 FSC-klagomål mail.docx", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="AC8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/tillsyn/A 8529-2023 tillsynsbegäran.docx", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="AD8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/tillsynsmail/A 8529-2023 tillsynsbegäran mail.docx", "A 8529-2023")</f>
+        <v/>
+      </c>
+      <c r="AE8">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2029/fåglar/A 8529-2023 prioriterade fågelarter.docx", "A 8529-2023")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="15" customHeight="1">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>A 33685-2025</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D9" s="1" t="n">
+        <v>45841</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>DALARNAS LÄN</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>LEKSAND</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>4</v>
+      </c>
+      <c r="K9" t="n">
+        <v>4</v>
+      </c>
+      <c r="L9" t="n">
+        <v>10</v>
+      </c>
+      <c r="M9" t="n">
+        <v>2</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>12</v>
+      </c>
+      <c r="R9" t="n">
+        <v>2</v>
+      </c>
+      <c r="S9" t="n">
+        <v>18</v>
+      </c>
+      <c r="T9" t="n">
         <v>45</v>
       </c>
-      <c r="U8" t="n">
+      <c r="U9" t="n">
         <v>32</v>
       </c>
-      <c r="V8" s="2" t="inlineStr">
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>Garnlav
 Knärot
@@ -1543,169 +1673,40 @@
 Nattviol</t>
         </is>
       </c>
-      <c r="W8">
+      <c r="W9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/artfynd/A 33685-2025 artfynd.xlsx", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="X8">
+      <c r="X9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/kartor/A 33685-2025 karta.png", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="Y8">
+      <c r="Y9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/kartor_geotiff/A 33685-2025 georefererad karta.tif", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="Z8">
+      <c r="Z9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/knärot/A 33685-2025 karta knärot.png", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="AA8">
+      <c r="AA9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/klagomål/A 33685-2025 FSC-klagomål.docx", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="AB8">
+      <c r="AB9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/klagomålsmail/A 33685-2025 FSC-klagomål mail.docx", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="AC8">
+      <c r="AC9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/tillsyn/A 33685-2025 tillsynsbegäran.docx", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="AD8">
+      <c r="AD9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/tillsynsmail/A 33685-2025 tillsynsbegäran mail.docx", "A 33685-2025")</f>
         <v/>
       </c>
-      <c r="AE8">
+      <c r="AE9">
         <f>HYPERLINK("https://klasma.github.io/Logging_2029/fåglar/A 33685-2025 prioriterade fågelarter.docx", "A 33685-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9" ht="15" customHeight="1">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>A 8529-2023</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>44977</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>46284</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>DALARNAS LÄN</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>LEKSAND</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="J9" t="n">
-        <v>17</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1</v>
-      </c>
-      <c r="L9" t="n">
-        <v>4</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1</v>
-      </c>
-      <c r="N9" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1</v>
-      </c>
-      <c r="S9" t="n">
-        <v>17</v>
-      </c>
-      <c r="T9" t="n">
-        <v>24</v>
-      </c>
-      <c r="U9" t="n">
-        <v>24</v>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Brunlångöra
-Ladusvala
-Rödvingetrast
-Talltita
-Tvåblad
-Tofsmes
-Buskskvätta
-Grönsiska
-Kråka
-Kungsfågel
-Svartvit flugsnappare
-Sävsparv
-Huggorm
-Skogsödla
-Fläcknycklar
-Revlummer</t>
-        </is>
-      </c>
-      <c r="W9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/artfynd/A 8529-2023 artfynd.xlsx", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="X9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/kartor/A 8529-2023 karta.png", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="Y9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/kartor_geotiff/A 8529-2023 georefererad karta.tif", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="Z9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/knärot/A 8529-2023 karta knärot.png", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="AA9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/klagomål/A 8529-2023 FSC-klagomål.docx", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="AB9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/klagomålsmail/A 8529-2023 FSC-klagomål mail.docx", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="AC9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/tillsyn/A 8529-2023 tillsynsbegäran.docx", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="AD9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/tillsynsmail/A 8529-2023 tillsynsbegäran mail.docx", "A 8529-2023")</f>
-        <v/>
-      </c>
-      <c r="AE9">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2029/fåglar/A 8529-2023 prioriterade fågelarter.docx", "A 8529-2023")</f>
         <v/>
       </c>
     </row>
@@ -1729,7 +1730,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1854,7 +1855,7 @@
         <v>45835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1981,7 +1982,7 @@
         <v>46047</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2104,7 +2105,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2230,7 +2231,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2355,7 +2356,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2478,7 +2479,7 @@
         <v>45936</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2598,7 +2599,7 @@
         <v>45827</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2714,7 +2715,7 @@
         <v>45272</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2830,7 +2831,7 @@
         <v>44992</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2941,7 +2942,7 @@
         <v>46178</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3061,7 +3062,7 @@
         <v>45489</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3171,7 +3172,7 @@
         <v>45896</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3294,7 +3295,7 @@
         <v>45614</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3408,7 +3409,7 @@
         <v>45715</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3526,7 +3527,7 @@
         <v>45334</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3636,7 +3637,7 @@
         <v>45632</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3746,7 +3747,7 @@
         <v>45638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3855,7 +3856,7 @@
         <v>44475</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3964,7 +3965,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4073,7 +4074,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4190,7 +4191,7 @@
         <v>46166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4303,7 +4304,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4411,7 +4412,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4523,7 +4524,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4635,7 +4636,7 @@
         <v>44477</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4742,7 +4743,7 @@
         <v>45901</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4858,7 +4859,7 @@
         <v>45637</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4965,7 +4966,7 @@
         <v>46097</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5076,7 +5077,7 @@
         <v>46237</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5187,7 +5188,7 @@
         <v>45632</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5294,7 +5295,7 @@
         <v>45254</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5400,7 +5401,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5506,7 +5507,7 @@
         <v>44829</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5616,7 +5617,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5722,7 +5723,7 @@
         <v>45028</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5828,7 +5829,7 @@
         <v>45358</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5934,7 +5935,7 @@
         <v>45656</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6040,7 +6041,7 @@
         <v>45274</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6150,7 +6151,7 @@
         <v>46027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6256,7 +6257,7 @@
         <v>45251</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6366,7 +6367,7 @@
         <v>44602</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6481,7 +6482,7 @@
         <v>46226</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6592,7 +6593,7 @@
         <v>46283</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6703,7 +6704,7 @@
         <v>45812</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6809,7 +6810,7 @@
         <v>45835</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6919,7 +6920,7 @@
         <v>45849</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7025,7 +7026,7 @@
         <v>44536</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7130,7 +7131,7 @@
         <v>44869</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7240,7 +7241,7 @@
         <v>44735</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7345,7 +7346,7 @@
         <v>44761</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7454,7 +7455,7 @@
         <v>45110</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7559,7 +7560,7 @@
         <v>45127</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7668,7 +7669,7 @@
         <v>45690</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7777,7 +7778,7 @@
         <v>45621</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7882,7 +7883,7 @@
         <v>44588</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7987,7 +7988,7 @@
         <v>45294</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8096,7 +8097,7 @@
         <v>45334</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8201,7 +8202,7 @@
         <v>45016</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8306,7 +8307,7 @@
         <v>45061</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8411,7 +8412,7 @@
         <v>45839</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8521,7 +8522,7 @@
         <v>45959</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8630,7 +8631,7 @@
         <v>45960</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8740,7 +8741,7 @@
         <v>45981</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8845,7 +8846,7 @@
         <v>46113</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8959,7 +8960,7 @@
         <v>45228</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9068,7 +9069,7 @@
         <v>45638</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9177,7 +9178,7 @@
         <v>45988</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9282,7 +9283,7 @@
         <v>46041</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9387,7 +9388,7 @@
         <v>44973</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9492,7 +9493,7 @@
         <v>46069</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9597,7 +9598,7 @@
         <v>46155</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9711,7 +9712,7 @@
         <v>46244</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9816,7 +9817,7 @@
         <v>46120</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9921,7 +9922,7 @@
         <v>46202</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10030,7 +10031,7 @@
         <v>44909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10139,7 +10140,7 @@
         <v>44992</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10248,7 +10249,7 @@
         <v>45091</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10353,7 +10354,7 @@
         <v>45761</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10458,7 +10459,7 @@
         <v>45005</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10567,7 +10568,7 @@
         <v>45754</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10672,7 +10673,7 @@
         <v>45502</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10777,7 +10778,7 @@
         <v>45256</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10882,7 +10883,7 @@
         <v>45793</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10987,7 +10988,7 @@
         <v>44918</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11092,7 +11093,7 @@
         <v>45181</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11197,7 +11198,7 @@
         <v>45996</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11307,7 +11308,7 @@
         <v>44782</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11380,7 +11381,7 @@
         <v>44491</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11453,7 +11454,7 @@
         <v>44834</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11526,7 +11527,7 @@
         <v>44802</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11604,7 +11605,7 @@
         <v>44671</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11677,7 +11678,7 @@
         <v>44872</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11755,7 +11756,7 @@
         <v>44512</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11828,7 +11829,7 @@
         <v>44869</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11906,7 +11907,7 @@
         <v>44509</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11984,7 +11985,7 @@
         <v>44570</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12057,7 +12058,7 @@
         <v>44670</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12130,7 +12131,7 @@
         <v>44488</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12203,7 +12204,7 @@
         <v>44877</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12276,7 +12277,7 @@
         <v>44539</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12349,7 +12350,7 @@
         <v>44529</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12422,7 +12423,7 @@
         <v>44824</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12495,7 +12496,7 @@
         <v>44834</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12568,7 +12569,7 @@
         <v>44693</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12641,7 +12642,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12714,7 +12715,7 @@
         <v>44503</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12787,7 +12788,7 @@
         <v>44851</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12860,7 +12861,7 @@
         <v>44865</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12938,7 +12939,7 @@
         <v>44792</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13011,7 +13012,7 @@
         <v>44690</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13089,7 +13090,7 @@
         <v>44684</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13167,7 +13168,7 @@
         <v>44543</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13240,7 +13241,7 @@
         <v>44651</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13313,7 +13314,7 @@
         <v>44777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13386,7 +13387,7 @@
         <v>44862</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13459,7 +13460,7 @@
         <v>44797</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13532,7 +13533,7 @@
         <v>44533</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13605,7 +13606,7 @@
         <v>44719</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13678,7 +13679,7 @@
         <v>45561</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13751,7 +13752,7 @@
         <v>44846</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13824,7 +13825,7 @@
         <v>45425</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13897,7 +13898,7 @@
         <v>45397</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13970,7 +13971,7 @@
         <v>44993</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14043,7 +14044,7 @@
         <v>45518</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14116,7 +14117,7 @@
         <v>44533</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14189,7 +14190,7 @@
         <v>45098</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14262,7 +14263,7 @@
         <v>45219</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14335,7 +14336,7 @@
         <v>45362</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14408,7 +14409,7 @@
         <v>44543</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14486,7 +14487,7 @@
         <v>45637</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14559,7 +14560,7 @@
         <v>45161</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14632,7 +14633,7 @@
         <v>45373</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14705,7 +14706,7 @@
         <v>45257</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14778,7 +14779,7 @@
         <v>45266</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14851,7 +14852,7 @@
         <v>45132</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14924,7 +14925,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14997,7 +14998,7 @@
         <v>45446</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15075,7 +15076,7 @@
         <v>45208</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15153,7 +15154,7 @@
         <v>44929</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15231,7 +15232,7 @@
         <v>45455</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15309,7 +15310,7 @@
         <v>45127</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15382,7 +15383,7 @@
         <v>45261</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15455,7 +15456,7 @@
         <v>45476</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15528,7 +15529,7 @@
         <v>45044</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15601,7 +15602,7 @@
         <v>45523</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15674,7 +15675,7 @@
         <v>44915</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15747,7 +15748,7 @@
         <v>45264</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15820,7 +15821,7 @@
         <v>45256</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15893,7 +15894,7 @@
         <v>45302</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15966,7 +15967,7 @@
         <v>45103</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16039,7 +16040,7 @@
         <v>45608</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16112,7 +16113,7 @@
         <v>44711</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16190,7 +16191,7 @@
         <v>44546</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16263,7 +16264,7 @@
         <v>44546</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16336,7 +16337,7 @@
         <v>45518</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16409,7 +16410,7 @@
         <v>45037</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16482,7 +16483,7 @@
         <v>44978</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16555,7 +16556,7 @@
         <v>45296</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16628,7 +16629,7 @@
         <v>45015</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16701,7 +16702,7 @@
         <v>44580</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16774,7 +16775,7 @@
         <v>45637</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16847,7 +16848,7 @@
         <v>45244</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16920,7 +16921,7 @@
         <v>45454</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16993,7 +16994,7 @@
         <v>45230</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17066,7 +17067,7 @@
         <v>45446</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17139,7 +17140,7 @@
         <v>45154</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17212,7 +17213,7 @@
         <v>44986</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17285,7 +17286,7 @@
         <v>45198</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17358,7 +17359,7 @@
         <v>45515</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17431,7 +17432,7 @@
         <v>44977</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17504,7 +17505,7 @@
         <v>45103</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17582,7 +17583,7 @@
         <v>45490</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17655,7 +17656,7 @@
         <v>45568</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17728,7 +17729,7 @@
         <v>45376</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17801,7 +17802,7 @@
         <v>45497</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17879,7 +17880,7 @@
         <v>45219</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17952,7 +17953,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18030,7 +18031,7 @@
         <v>45261</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18103,7 +18104,7 @@
         <v>45258</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18176,7 +18177,7 @@
         <v>45183</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18249,7 +18250,7 @@
         <v>45480</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18322,7 +18323,7 @@
         <v>45397</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18395,7 +18396,7 @@
         <v>44867</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18468,7 +18469,7 @@
         <v>45260</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18541,7 +18542,7 @@
         <v>44966</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18614,7 +18615,7 @@
         <v>45261</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18687,7 +18688,7 @@
         <v>45667</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18760,7 +18761,7 @@
         <v>45110</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18833,7 +18834,7 @@
         <v>45001</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18906,7 +18907,7 @@
         <v>45015</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18979,7 +18980,7 @@
         <v>45232</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19052,7 +19053,7 @@
         <v>45027</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19125,7 +19126,7 @@
         <v>45376</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19198,7 +19199,7 @@
         <v>45695</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19271,7 +19272,7 @@
         <v>44987</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19344,7 +19345,7 @@
         <v>45259</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19417,7 +19418,7 @@
         <v>45151</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19490,7 +19491,7 @@
         <v>45306</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19563,7 +19564,7 @@
         <v>45677</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19636,7 +19637,7 @@
         <v>44749</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19714,7 +19715,7 @@
         <v>45001</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19787,7 +19788,7 @@
         <v>45510</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19860,7 +19861,7 @@
         <v>45425</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19933,7 +19934,7 @@
         <v>45624</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20006,7 +20007,7 @@
         <v>44837</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20079,7 +20080,7 @@
         <v>45351</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20152,7 +20153,7 @@
         <v>45061</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20225,7 +20226,7 @@
         <v>45574</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20298,7 +20299,7 @@
         <v>45611</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20371,7 +20372,7 @@
         <v>45349</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20444,7 +20445,7 @@
         <v>45618</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20517,7 +20518,7 @@
         <v>44501</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20590,7 +20591,7 @@
         <v>45559</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20663,7 +20664,7 @@
         <v>45631</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20736,7 +20737,7 @@
         <v>45583</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20809,7 +20810,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20882,7 +20883,7 @@
         <v>45036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20955,7 +20956,7 @@
         <v>45749</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21028,7 +21029,7 @@
         <v>44962</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21101,7 +21102,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21174,7 +21175,7 @@
         <v>44974</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21247,7 +21248,7 @@
         <v>44992</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21320,7 +21321,7 @@
         <v>45803</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21393,7 +21394,7 @@
         <v>44820</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21466,7 +21467,7 @@
         <v>45474</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21539,7 +21540,7 @@
         <v>45160</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21612,7 +21613,7 @@
         <v>45203</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21685,7 +21686,7 @@
         <v>45782</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21758,7 +21759,7 @@
         <v>45433</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21831,7 +21832,7 @@
         <v>45433</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21904,7 +21905,7 @@
         <v>45705</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21977,7 +21978,7 @@
         <v>44959</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22050,7 +22051,7 @@
         <v>45670</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22123,7 +22124,7 @@
         <v>45342</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22201,7 +22202,7 @@
         <v>45834</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22279,7 +22280,7 @@
         <v>45456</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22357,7 +22358,7 @@
         <v>45104</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22430,7 +22431,7 @@
         <v>45113</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22503,7 +22504,7 @@
         <v>45732</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22576,7 +22577,7 @@
         <v>45509</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22649,7 +22650,7 @@
         <v>45114</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22722,7 +22723,7 @@
         <v>45453</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22795,7 +22796,7 @@
         <v>45884</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22868,7 +22869,7 @@
         <v>45553</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22946,7 +22947,7 @@
         <v>45408</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23019,7 +23020,7 @@
         <v>45555</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23092,7 +23093,7 @@
         <v>45195</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23165,7 +23166,7 @@
         <v>45890</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23243,7 +23244,7 @@
         <v>45890</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23316,7 +23317,7 @@
         <v>45085</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23389,7 +23390,7 @@
         <v>45890</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23462,7 +23463,7 @@
         <v>45726</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23535,7 +23536,7 @@
         <v>45334</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23608,7 +23609,7 @@
         <v>45863</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23681,7 +23682,7 @@
         <v>44993</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23754,7 +23755,7 @@
         <v>45553</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23832,7 +23833,7 @@
         <v>45625</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23905,7 +23906,7 @@
         <v>46035</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -23978,7 +23979,7 @@
         <v>45901</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24056,7 +24057,7 @@
         <v>45898</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24134,7 +24135,7 @@
         <v>45898</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24212,7 +24213,7 @@
         <v>44951</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24285,7 +24286,7 @@
         <v>46139</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24358,7 +24359,7 @@
         <v>45567</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24431,7 +24432,7 @@
         <v>45898</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24509,7 +24510,7 @@
         <v>45886</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24582,7 +24583,7 @@
         <v>45707</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24655,7 +24656,7 @@
         <v>45903</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24728,7 +24729,7 @@
         <v>45104</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24806,7 +24807,7 @@
         <v>45751</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24879,7 +24880,7 @@
         <v>45630</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24952,7 +24953,7 @@
         <v>45303</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25025,7 +25026,7 @@
         <v>46114</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25103,7 +25104,7 @@
         <v>45030</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25176,7 +25177,7 @@
         <v>44994</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25249,7 +25250,7 @@
         <v>45695</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25322,7 +25323,7 @@
         <v>45958</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25395,7 +25396,7 @@
         <v>45911</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25468,7 +25469,7 @@
         <v>45911</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25541,7 +25542,7 @@
         <v>45911</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25614,7 +25615,7 @@
         <v>44978</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25687,7 +25688,7 @@
         <v>45912</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25765,7 +25766,7 @@
         <v>46064</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25838,7 +25839,7 @@
         <v>45912</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25911,7 +25912,7 @@
         <v>45567</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -25984,7 +25985,7 @@
         <v>46140</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26057,7 +26058,7 @@
         <v>45915</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26130,7 +26131,7 @@
         <v>46030</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26203,7 +26204,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26276,7 +26277,7 @@
         <v>45197</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26349,7 +26350,7 @@
         <v>45916</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26422,7 +26423,7 @@
         <v>44902</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26495,7 +26496,7 @@
         <v>45917</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26568,7 +26569,7 @@
         <v>45919</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26641,7 +26642,7 @@
         <v>45351</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26714,7 +26715,7 @@
         <v>45125</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26792,7 +26793,7 @@
         <v>45308</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26865,7 +26866,7 @@
         <v>45921</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26938,7 +26939,7 @@
         <v>45921</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27011,7 +27012,7 @@
         <v>44628</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27084,7 +27085,7 @@
         <v>45924</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27157,7 +27158,7 @@
         <v>45558</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27230,7 +27231,7 @@
         <v>45925</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27303,7 +27304,7 @@
         <v>45925</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27376,7 +27377,7 @@
         <v>45406</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27449,7 +27450,7 @@
         <v>45022</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27522,7 +27523,7 @@
         <v>46036</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27600,7 +27601,7 @@
         <v>45334</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27678,7 +27679,7 @@
         <v>44837</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27751,7 +27752,7 @@
         <v>45929</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27824,7 +27825,7 @@
         <v>45317</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27897,7 +27898,7 @@
         <v>45002</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -27970,7 +27971,7 @@
         <v>45552</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28043,7 +28044,7 @@
         <v>45932</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28121,7 +28122,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28199,7 +28200,7 @@
         <v>45490</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28272,7 +28273,7 @@
         <v>44959</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28345,7 +28346,7 @@
         <v>45418</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28418,7 +28419,7 @@
         <v>46146</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28491,7 +28492,7 @@
         <v>45934</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28564,7 +28565,7 @@
         <v>45630</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28637,7 +28638,7 @@
         <v>45630</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28710,7 +28711,7 @@
         <v>45939</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28788,7 +28789,7 @@
         <v>45706</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28861,7 +28862,7 @@
         <v>45937</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28934,7 +28935,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29007,7 +29008,7 @@
         <v>44998</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29080,7 +29081,7 @@
         <v>44998</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29153,7 +29154,7 @@
         <v>46147</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29226,7 +29227,7 @@
         <v>45621</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29299,7 +29300,7 @@
         <v>45478</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29372,7 +29373,7 @@
         <v>45624</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29445,7 +29446,7 @@
         <v>46149</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29518,7 +29519,7 @@
         <v>46119</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29591,7 +29592,7 @@
         <v>46149</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29669,7 +29670,7 @@
         <v>45944</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29742,7 +29743,7 @@
         <v>45946</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29815,7 +29816,7 @@
         <v>46148</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29893,7 +29894,7 @@
         <v>46149</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -29971,7 +29972,7 @@
         <v>44992</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30044,7 +30045,7 @@
         <v>45103</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30117,7 +30118,7 @@
         <v>45877</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30190,7 +30191,7 @@
         <v>45429</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30263,7 +30264,7 @@
         <v>45951</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30341,7 +30342,7 @@
         <v>45618</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30414,7 +30415,7 @@
         <v>45554</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30492,7 +30493,7 @@
         <v>45167</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30565,7 +30566,7 @@
         <v>45951</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30643,7 +30644,7 @@
         <v>44974</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30716,7 +30717,7 @@
         <v>44974</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30789,7 +30790,7 @@
         <v>45675</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30862,7 +30863,7 @@
         <v>46153</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30940,7 +30941,7 @@
         <v>45952</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31013,7 +31014,7 @@
         <v>45726</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31086,7 +31087,7 @@
         <v>45955</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31159,7 +31160,7 @@
         <v>46038</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31232,7 +31233,7 @@
         <v>45121</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31305,7 +31306,7 @@
         <v>45958</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31378,7 +31379,7 @@
         <v>45131</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31451,7 +31452,7 @@
         <v>46092</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31524,7 +31525,7 @@
         <v>45112</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31597,7 +31598,7 @@
         <v>46153</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31675,7 +31676,7 @@
         <v>45961</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31748,7 +31749,7 @@
         <v>45961</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31821,7 +31822,7 @@
         <v>45960</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31894,7 +31895,7 @@
         <v>45961</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -31967,7 +31968,7 @@
         <v>45965</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32045,7 +32046,7 @@
         <v>45964</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32118,7 +32119,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32191,7 +32192,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32264,7 +32265,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32337,7 +32338,7 @@
         <v>45965</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32410,7 +32411,7 @@
         <v>45365</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32483,7 +32484,7 @@
         <v>45966</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32556,7 +32557,7 @@
         <v>45966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32629,7 +32630,7 @@
         <v>45966</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32702,7 +32703,7 @@
         <v>45966</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32775,7 +32776,7 @@
         <v>45027</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32848,7 +32849,7 @@
         <v>45966</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -32921,7 +32922,7 @@
         <v>45966</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -32994,7 +32995,7 @@
         <v>45835</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33067,7 +33068,7 @@
         <v>45257</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33145,7 +33146,7 @@
         <v>45971</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33218,7 +33219,7 @@
         <v>45165</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33291,7 +33292,7 @@
         <v>45610</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33364,7 +33365,7 @@
         <v>45397</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33437,7 +33438,7 @@
         <v>45454</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33510,7 +33511,7 @@
         <v>45896</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33583,7 +33584,7 @@
         <v>46155</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33661,7 +33662,7 @@
         <v>46155</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33739,7 +33740,7 @@
         <v>45972</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33812,7 +33813,7 @@
         <v>45169</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33885,7 +33886,7 @@
         <v>46043</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -33958,7 +33959,7 @@
         <v>45975</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34036,7 +34037,7 @@
         <v>45974</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34109,7 +34110,7 @@
         <v>45727</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34182,7 +34183,7 @@
         <v>45974</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34255,7 +34256,7 @@
         <v>46154</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34333,7 +34334,7 @@
         <v>45180</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34406,7 +34407,7 @@
         <v>45978</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34479,7 +34480,7 @@
         <v>46052</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34552,7 +34553,7 @@
         <v>45994</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34625,7 +34626,7 @@
         <v>45981</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34698,7 +34699,7 @@
         <v>46044</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34771,7 +34772,7 @@
         <v>45966</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34844,7 +34845,7 @@
         <v>45985</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34917,7 +34918,7 @@
         <v>45985</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -34990,7 +34991,7 @@
         <v>45985</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35063,7 +35064,7 @@
         <v>45985</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35136,7 +35137,7 @@
         <v>45621</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35209,7 +35210,7 @@
         <v>45982</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35282,7 +35283,7 @@
         <v>45446</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35360,7 +35361,7 @@
         <v>46156</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35433,7 +35434,7 @@
         <v>45623</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35506,7 +35507,7 @@
         <v>46156</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35579,7 +35580,7 @@
         <v>45986</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35652,7 +35653,7 @@
         <v>45986</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35725,7 +35726,7 @@
         <v>45695</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35798,7 +35799,7 @@
         <v>45113</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35871,7 +35872,7 @@
         <v>45127</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -35944,7 +35945,7 @@
         <v>45127</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36017,7 +36018,7 @@
         <v>45160</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36090,7 +36091,7 @@
         <v>45621</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36163,7 +36164,7 @@
         <v>45988</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36236,7 +36237,7 @@
         <v>45903</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36314,7 +36315,7 @@
         <v>45988</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36412,7 +36413,7 @@
         <v>45127</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36485,7 +36486,7 @@
         <v>44474</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36558,7 +36559,7 @@
         <v>45664</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36631,7 +36632,7 @@
         <v>46161</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36704,7 +36705,7 @@
         <v>45993</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36777,7 +36778,7 @@
         <v>45608</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36850,7 +36851,7 @@
         <v>45667</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36923,7 +36924,7 @@
         <v>45198</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -36996,7 +36997,7 @@
         <v>45625</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37069,7 +37070,7 @@
         <v>44912</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37142,7 +37143,7 @@
         <v>46162</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37215,7 +37216,7 @@
         <v>45747</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37288,7 +37289,7 @@
         <v>45068</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37361,7 +37362,7 @@
         <v>45995</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37434,7 +37435,7 @@
         <v>44746</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37507,7 +37508,7 @@
         <v>44917</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37580,7 +37581,7 @@
         <v>45995</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37653,7 +37654,7 @@
         <v>45996</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37726,7 +37727,7 @@
         <v>44909</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37799,7 +37800,7 @@
         <v>45282</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37872,7 +37873,7 @@
         <v>46001</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -37945,7 +37946,7 @@
         <v>45526</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38018,7 +38019,7 @@
         <v>45369</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38091,7 +38092,7 @@
         <v>46002</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38164,7 +38165,7 @@
         <v>46006</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38237,7 +38238,7 @@
         <v>46006</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38310,7 +38311,7 @@
         <v>46006</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38383,7 +38384,7 @@
         <v>46167</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38456,7 +38457,7 @@
         <v>46006</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38529,7 +38530,7 @@
         <v>46007</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38602,7 +38603,7 @@
         <v>46007</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38675,7 +38676,7 @@
         <v>45027</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38748,7 +38749,7 @@
         <v>46168</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38821,7 +38822,7 @@
         <v>46168</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38894,7 +38895,7 @@
         <v>45197</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -38967,7 +38968,7 @@
         <v>45608</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39040,7 +39041,7 @@
         <v>45615</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39113,7 +39114,7 @@
         <v>46010</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39186,7 +39187,7 @@
         <v>46010</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39259,7 +39260,7 @@
         <v>46013</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39332,7 +39333,7 @@
         <v>45741</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39405,7 +39406,7 @@
         <v>45910</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39478,7 +39479,7 @@
         <v>45280</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39551,7 +39552,7 @@
         <v>46018</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39624,7 +39625,7 @@
         <v>46020</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39697,7 +39698,7 @@
         <v>46021</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39770,7 +39771,7 @@
         <v>46020</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39843,7 +39844,7 @@
         <v>44875</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -39916,7 +39917,7 @@
         <v>46021</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -39989,7 +39990,7 @@
         <v>46024</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40062,7 +40063,7 @@
         <v>46027</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40135,7 +40136,7 @@
         <v>46029</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40208,7 +40209,7 @@
         <v>44750</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40286,7 +40287,7 @@
         <v>46029</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40359,7 +40360,7 @@
         <v>44992</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40432,7 +40433,7 @@
         <v>46029</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40505,7 +40506,7 @@
         <v>44929</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40583,7 +40584,7 @@
         <v>45169</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40656,7 +40657,7 @@
         <v>45275</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40729,7 +40730,7 @@
         <v>45252</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40802,7 +40803,7 @@
         <v>46035</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40875,7 +40876,7 @@
         <v>46170</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -40948,7 +40949,7 @@
         <v>45219</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41021,7 +41022,7 @@
         <v>46027</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41094,7 +41095,7 @@
         <v>46171</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41172,7 +41173,7 @@
         <v>46035</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41245,7 +41246,7 @@
         <v>45609</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41318,7 +41319,7 @@
         <v>45176</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41391,7 +41392,7 @@
         <v>45097</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41464,7 +41465,7 @@
         <v>45979</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41537,7 +41538,7 @@
         <v>45595</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41610,7 +41611,7 @@
         <v>45980</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41683,7 +41684,7 @@
         <v>46041</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41756,7 +41757,7 @@
         <v>46041</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41829,7 +41830,7 @@
         <v>45979</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -41902,7 +41903,7 @@
         <v>45982</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -41975,7 +41976,7 @@
         <v>46043</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42048,7 +42049,7 @@
         <v>46043</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42121,7 +42122,7 @@
         <v>46043</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42194,7 +42195,7 @@
         <v>46174</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42267,7 +42268,7 @@
         <v>45034</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42340,7 +42341,7 @@
         <v>46045</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42413,7 +42414,7 @@
         <v>46044</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42486,7 +42487,7 @@
         <v>44846</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42559,7 +42560,7 @@
         <v>46045</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42632,7 +42633,7 @@
         <v>46044</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42705,7 +42706,7 @@
         <v>46049</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42778,7 +42779,7 @@
         <v>46049</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42851,7 +42852,7 @@
         <v>45049</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -42924,7 +42925,7 @@
         <v>46176</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43002,7 +43003,7 @@
         <v>44869</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43080,7 +43081,7 @@
         <v>46051</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43153,7 +43154,7 @@
         <v>46050</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43226,7 +43227,7 @@
         <v>46029</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43299,7 +43300,7 @@
         <v>46055</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43372,7 +43373,7 @@
         <v>46052</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43445,7 +43446,7 @@
         <v>46045</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43518,7 +43519,7 @@
         <v>46056</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43591,7 +43592,7 @@
         <v>45520</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43664,7 +43665,7 @@
         <v>46044</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43737,7 +43738,7 @@
         <v>45537</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43810,7 +43811,7 @@
         <v>46035</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -43883,7 +43884,7 @@
         <v>45357</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -43956,7 +43957,7 @@
         <v>46127</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44029,7 +44030,7 @@
         <v>45264</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44102,7 +44103,7 @@
         <v>46007</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44175,7 +44176,7 @@
         <v>45860</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44248,7 +44249,7 @@
         <v>46035</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44321,7 +44322,7 @@
         <v>45797</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44394,7 +44395,7 @@
         <v>46182</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44467,7 +44468,7 @@
         <v>45979</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44540,7 +44541,7 @@
         <v>45797</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44613,7 +44614,7 @@
         <v>45110</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44686,7 +44687,7 @@
         <v>46071</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44759,7 +44760,7 @@
         <v>46070</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44832,7 +44833,7 @@
         <v>46070</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -44905,7 +44906,7 @@
         <v>45152</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -44978,7 +44979,7 @@
         <v>46126</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45056,7 +45057,7 @@
         <v>46070</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45129,7 +45130,7 @@
         <v>45061</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45202,7 +45203,7 @@
         <v>44918</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45275,7 +45276,7 @@
         <v>46182</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45348,7 +45349,7 @@
         <v>46181</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45426,7 +45427,7 @@
         <v>46072</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45499,7 +45500,7 @@
         <v>46072</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45572,7 +45573,7 @@
         <v>45509</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45645,7 +45646,7 @@
         <v>46072</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45718,7 +45719,7 @@
         <v>46183</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45796,7 +45797,7 @@
         <v>45096</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -45869,7 +45870,7 @@
         <v>45378</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -45942,7 +45943,7 @@
         <v>45415</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46015,7 +46016,7 @@
         <v>45553</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46093,7 +46094,7 @@
         <v>45152</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46166,7 +46167,7 @@
         <v>45050</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46239,7 +46240,7 @@
         <v>45203</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46312,7 +46313,7 @@
         <v>45567</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46390,7 +46391,7 @@
         <v>46185</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46468,7 +46469,7 @@
         <v>46188</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46541,7 +46542,7 @@
         <v>45231</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46614,7 +46615,7 @@
         <v>45257</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46687,7 +46688,7 @@
         <v>45272</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46760,7 +46761,7 @@
         <v>46190</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46838,7 +46839,7 @@
         <v>46092</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -46911,7 +46912,7 @@
         <v>44679</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -46989,7 +46990,7 @@
         <v>46097</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47062,7 +47063,7 @@
         <v>46097</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47135,7 +47136,7 @@
         <v>46097</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47208,7 +47209,7 @@
         <v>45345</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47281,7 +47282,7 @@
         <v>46063</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47354,7 +47355,7 @@
         <v>46191</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47427,7 +47428,7 @@
         <v>46191</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47505,7 +47506,7 @@
         <v>46191</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47578,7 +47579,7 @@
         <v>46196</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47651,7 +47652,7 @@
         <v>46101</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47724,7 +47725,7 @@
         <v>46106</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47802,7 +47803,7 @@
         <v>46106</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -47875,7 +47876,7 @@
         <v>45323</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -47948,7 +47949,7 @@
         <v>46197</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48021,7 +48022,7 @@
         <v>46197</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48099,7 +48100,7 @@
         <v>46241</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48177,7 +48178,7 @@
         <v>45467</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48250,7 +48251,7 @@
         <v>45559</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48323,7 +48324,7 @@
         <v>46197</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48401,7 +48402,7 @@
         <v>46112</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48479,7 +48480,7 @@
         <v>46111</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48557,7 +48558,7 @@
         <v>46111</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48635,7 +48636,7 @@
         <v>45756</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48708,7 +48709,7 @@
         <v>46202</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48781,7 +48782,7 @@
         <v>46111</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48859,7 +48860,7 @@
         <v>45004</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -48932,7 +48933,7 @@
         <v>45035</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49005,7 +49006,7 @@
         <v>46113</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49078,7 +49079,7 @@
         <v>45201</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49151,7 +49152,7 @@
         <v>45727</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49229,7 +49230,7 @@
         <v>46119</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49302,7 +49303,7 @@
         <v>44987</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49375,7 +49376,7 @@
         <v>46121</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49453,7 +49454,7 @@
         <v>45314</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49526,7 +49527,7 @@
         <v>45314</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49599,7 +49600,7 @@
         <v>45544</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49672,7 +49673,7 @@
         <v>46126</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49745,7 +49746,7 @@
         <v>46127</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49823,7 +49824,7 @@
         <v>46127</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -49896,7 +49897,7 @@
         <v>46128</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -49974,7 +49975,7 @@
         <v>46127</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50052,7 +50053,7 @@
         <v>46127</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50130,7 +50131,7 @@
         <v>45199</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50203,7 +50204,7 @@
         <v>45001</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50276,7 +50277,7 @@
         <v>46114</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50354,7 +50355,7 @@
         <v>46132</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50427,7 +50428,7 @@
         <v>46114</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50505,7 +50506,7 @@
         <v>46135</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50583,7 +50584,7 @@
         <v>44792</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50656,7 +50657,7 @@
         <v>46133</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50729,7 +50730,7 @@
         <v>45334</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50807,7 +50808,7 @@
         <v>45607</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50885,7 +50886,7 @@
         <v>44714</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -50963,7 +50964,7 @@
         <v>46247</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51041,7 +51042,7 @@
         <v>46035</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51114,7 +51115,7 @@
         <v>44785</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51187,7 +51188,7 @@
         <v>44985</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51260,7 +51261,7 @@
         <v>46139</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51333,7 +51334,7 @@
         <v>45509</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51406,7 +51407,7 @@
         <v>45093</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51479,7 +51480,7 @@
         <v>45167</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51552,7 +51553,7 @@
         <v>45169</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51625,7 +51626,7 @@
         <v>46246</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51698,7 +51699,7 @@
         <v>44909</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51771,7 +51772,7 @@
         <v>45112</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51844,7 +51845,7 @@
         <v>45558</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -51917,7 +51918,7 @@
         <v>46251</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -51995,7 +51996,7 @@
         <v>45647</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52068,7 +52069,7 @@
         <v>45267</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52141,7 +52142,7 @@
         <v>46248</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52219,7 +52220,7 @@
         <v>46249</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52297,7 +52298,7 @@
         <v>45744</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52370,7 +52371,7 @@
         <v>46251</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52448,7 +52449,7 @@
         <v>45261</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52521,7 +52522,7 @@
         <v>45261</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52594,7 +52595,7 @@
         <v>44967</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52672,7 +52673,7 @@
         <v>44574</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52745,7 +52746,7 @@
         <v>45244</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52818,7 +52819,7 @@
         <v>46252</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52891,7 +52892,7 @@
         <v>46024</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -52964,7 +52965,7 @@
         <v>46252</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53042,7 +53043,7 @@
         <v>46252</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53115,7 +53116,7 @@
         <v>46254</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53188,7 +53189,7 @@
         <v>45231</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53266,7 +53267,7 @@
         <v>46211</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53339,7 +53340,7 @@
         <v>45049</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53412,7 +53413,7 @@
         <v>45109</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53485,7 +53486,7 @@
         <v>45266</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53558,7 +53559,7 @@
         <v>45595</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53631,7 +53632,7 @@
         <v>46211</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53704,7 +53705,7 @@
         <v>46259</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53777,7 +53778,7 @@
         <v>45298</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53850,7 +53851,7 @@
         <v>46216</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -53928,7 +53929,7 @@
         <v>45216</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54001,7 +54002,7 @@
         <v>46259</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54079,7 +54080,7 @@
         <v>46259</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54152,7 +54153,7 @@
         <v>46259</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54225,7 +54226,7 @@
         <v>45076</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54298,7 +54299,7 @@
         <v>46202</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54376,7 +54377,7 @@
         <v>45296</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54449,7 +54450,7 @@
         <v>44890</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54522,7 +54523,7 @@
         <v>45255</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54595,7 +54596,7 @@
         <v>45418</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54668,7 +54669,7 @@
         <v>45293</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54741,7 +54742,7 @@
         <v>45307</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54814,7 +54815,7 @@
         <v>45131</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54887,7 +54888,7 @@
         <v>44643</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -54960,7 +54961,7 @@
         <v>44974</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55033,7 +55034,7 @@
         <v>45216</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55106,7 +55107,7 @@
         <v>45200</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55179,7 +55180,7 @@
         <v>45568</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55252,7 +55253,7 @@
         <v>45727</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55325,7 +55326,7 @@
         <v>44714</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55403,7 +55404,7 @@
         <v>45447</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55476,7 +55477,7 @@
         <v>45266</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55549,7 +55550,7 @@
         <v>45267</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55622,7 +55623,7 @@
         <v>44991</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55695,7 +55696,7 @@
         <v>44991</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55768,7 +55769,7 @@
         <v>45202</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55841,7 +55842,7 @@
         <v>45428</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -55914,7 +55915,7 @@
         <v>46268</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -55987,7 +55988,7 @@
         <v>45776</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56065,7 +56066,7 @@
         <v>46177</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56143,7 +56144,7 @@
         <v>45779</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56216,7 +56217,7 @@
         <v>45170</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56294,7 +56295,7 @@
         <v>45376</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56367,7 +56368,7 @@
         <v>46177</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56445,7 +56446,7 @@
         <v>45646</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56518,7 +56519,7 @@
         <v>46167</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56596,7 +56597,7 @@
         <v>46276</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56669,7 +56670,7 @@
         <v>45266</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56742,7 +56743,7 @@
         <v>45015</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56815,7 +56816,7 @@
         <v>46233</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56893,7 +56894,7 @@
         <v>45350</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -56966,7 +56967,7 @@
         <v>45787</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57039,7 +57040,7 @@
         <v>46233</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57117,7 +57118,7 @@
         <v>45524</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57190,7 +57191,7 @@
         <v>45790</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57263,7 +57264,7 @@
         <v>45596</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57336,7 +57337,7 @@
         <v>45574</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57409,7 +57410,7 @@
         <v>45790</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57482,7 +57483,7 @@
         <v>46281</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57555,7 +57556,7 @@
         <v>46238</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57633,7 +57634,7 @@
         <v>45796</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57706,7 +57707,7 @@
         <v>44971</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57779,7 +57780,7 @@
         <v>46240</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57857,7 +57858,7 @@
         <v>45240</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -57930,7 +57931,7 @@
         <v>46241</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58008,7 +58009,7 @@
         <v>45558</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58081,7 +58082,7 @@
         <v>45114</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58154,7 +58155,7 @@
         <v>44731</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58227,7 +58228,7 @@
         <v>45812</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58305,7 +58306,7 @@
         <v>45813</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58378,7 +58379,7 @@
         <v>45817</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58451,7 +58452,7 @@
         <v>45818</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58524,7 +58525,7 @@
         <v>45818</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58602,7 +58603,7 @@
         <v>45818</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58675,7 +58676,7 @@
         <v>45820</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58748,7 +58749,7 @@
         <v>45825</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58821,7 +58822,7 @@
         <v>45821</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58894,7 +58895,7 @@
         <v>45827</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -58967,7 +58968,7 @@
         <v>45833</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59040,7 +59041,7 @@
         <v>45832</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59113,7 +59114,7 @@
         <v>45835</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59186,7 +59187,7 @@
         <v>45839</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59259,7 +59260,7 @@
         <v>45838</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59337,7 +59338,7 @@
         <v>45847</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59410,7 +59411,7 @@
         <v>45849</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59488,7 +59489,7 @@
         <v>45561</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59566,7 +59567,7 @@
         <v>45849</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59644,7 +59645,7 @@
         <v>45863</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59722,7 +59723,7 @@
         <v>45863</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59795,7 +59796,7 @@
         <v>45881</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59868,7 +59869,7 @@
         <v>45428</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -59941,7 +59942,7 @@
         <v>45882</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60014,7 +60015,7 @@
         <v>45074</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60092,7 +60093,7 @@
         <v>44578</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60165,7 +60166,7 @@
         <v>45257</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60238,7 +60239,7 @@
         <v>45097</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60311,7 +60312,7 @@
         <v>45351</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60389,7 +60390,7 @@
         <v>44809</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60462,7 +60463,7 @@
         <v>45097</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60535,7 +60536,7 @@
         <v>45133</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60608,7 +60609,7 @@
         <v>44652</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60681,7 +60682,7 @@
         <v>45446</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60759,7 +60760,7 @@
         <v>45701</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60837,7 +60838,7 @@
         <v>45701</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60915,7 +60916,7 @@
         <v>45708</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -60993,7 +60994,7 @@
         <v>45727</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61071,7 +61072,7 @@
         <v>45799</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61144,7 +61145,7 @@
         <v>45819</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61217,7 +61218,7 @@
         <v>45824</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61290,7 +61291,7 @@
         <v>45835</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61363,7 +61364,7 @@
         <v>45904</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61436,7 +61437,7 @@
         <v>45943</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61509,7 +61510,7 @@
         <v>45964</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61587,7 +61588,7 @@
         <v>46038</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61665,7 +61666,7 @@
         <v>46043</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61738,7 +61739,7 @@
         <v>46052</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61816,7 +61817,7 @@
         <v>44649</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61889,7 +61890,7 @@
         <v>46066</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -61962,7 +61963,7 @@
         <v>46076</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62035,7 +62036,7 @@
         <v>46133</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62113,7 +62114,7 @@
         <v>46134</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>46013</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1068,7 +1068,7 @@
         <v>45790</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
         <v>46064</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>45835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1994,7 +1994,7 @@
         <v>46047</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2243,7 +2243,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2368,7 +2368,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2491,7 +2491,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2730,7 +2730,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2846,7 +2846,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2966,7 +2966,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3082,7 +3082,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3193,7 +3193,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>45489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45896</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3546,7 +3546,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3660,7 +3660,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3880,7 +3880,7 @@
         <v>46027</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3989,7 +3989,7 @@
         <v>45835</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>46166</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4219,7 +4219,7 @@
         <v>45638</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4328,7 +4328,7 @@
         <v>44475</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>45931</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4657,7 +4657,7 @@
         <v>44869</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4769,7 +4769,7 @@
         <v>44477</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4876,7 +4876,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45637</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>46097</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5210,7 +5210,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5321,7 +5321,7 @@
         <v>45632</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5428,7 +5428,7 @@
         <v>45254</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5534,7 +5534,7 @@
         <v>45274</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>46027</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>45890</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5856,7 +5856,7 @@
         <v>45656</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>45358</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>44602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6183,7 +6183,7 @@
         <v>45812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6289,7 +6289,7 @@
         <v>45028</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>45835</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6505,7 +6505,7 @@
         <v>45849</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6611,7 +6611,7 @@
         <v>45251</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6717,7 +6717,7 @@
         <v>44829</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6827,7 +6827,7 @@
         <v>45251</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>46226</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7048,7 +7048,7 @@
         <v>46283</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7159,7 +7159,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7264,7 +7264,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44735</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7479,7 +7479,7 @@
         <v>44761</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7588,7 +7588,7 @@
         <v>45793</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7693,7 +7693,7 @@
         <v>44973</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7798,7 +7798,7 @@
         <v>45334</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7903,7 +7903,7 @@
         <v>46041</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8008,7 +8008,7 @@
         <v>46069</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8113,7 +8113,7 @@
         <v>45839</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8223,7 +8223,7 @@
         <v>45959</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8332,7 +8332,7 @@
         <v>45960</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8442,7 +8442,7 @@
         <v>46120</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45981</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8652,7 +8652,7 @@
         <v>45228</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8761,7 +8761,7 @@
         <v>44909</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8870,7 +8870,7 @@
         <v>45690</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8979,7 +8979,7 @@
         <v>45988</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>45294</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>45091</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45754</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44992</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9512,7 +9512,7 @@
         <v>44918</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9617,7 +9617,7 @@
         <v>45761</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9722,7 +9722,7 @@
         <v>45127</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9831,7 +9831,7 @@
         <v>46155</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9945,7 +9945,7 @@
         <v>44588</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10050,7 +10050,7 @@
         <v>46202</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10159,7 +10159,7 @@
         <v>45621</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10264,7 +10264,7 @@
         <v>45638</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10373,7 +10373,7 @@
         <v>45061</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10478,7 +10478,7 @@
         <v>46287</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10588,7 +10588,7 @@
         <v>46244</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>45005</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10802,7 +10802,7 @@
         <v>45110</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10907,7 +10907,7 @@
         <v>45016</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11012,7 +11012,7 @@
         <v>45502</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11117,7 +11117,7 @@
         <v>45256</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11222,7 +11222,7 @@
         <v>45181</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11327,7 +11327,7 @@
         <v>45996</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11437,7 +11437,7 @@
         <v>44782</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44491</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11583,7 +11583,7 @@
         <v>44834</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11656,7 +11656,7 @@
         <v>44802</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11734,7 +11734,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11807,7 +11807,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11885,7 +11885,7 @@
         <v>44512</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11958,7 +11958,7 @@
         <v>44869</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12036,7 +12036,7 @@
         <v>44570</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12109,7 +12109,7 @@
         <v>44509</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12187,7 +12187,7 @@
         <v>44670</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44488</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12333,7 +12333,7 @@
         <v>44877</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12406,7 +12406,7 @@
         <v>44539</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12479,7 +12479,7 @@
         <v>44529</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>44824</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12698,7 +12698,7 @@
         <v>44693</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12771,7 +12771,7 @@
         <v>44503</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12844,7 +12844,7 @@
         <v>44533</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
         <v>44851</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12990,7 +12990,7 @@
         <v>44865</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13068,7 +13068,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44690</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13219,7 +13219,7 @@
         <v>44684</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>44543</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13370,7 +13370,7 @@
         <v>44777</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>44651</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44862</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44533</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13662,7 +13662,7 @@
         <v>44797</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13735,7 +13735,7 @@
         <v>44746</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45160</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13881,7 +13881,7 @@
         <v>45334</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13959,7 +13959,7 @@
         <v>45050</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14032,7 +14032,7 @@
         <v>45378</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>45351</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14178,7 +14178,7 @@
         <v>45345</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14251,7 +14251,7 @@
         <v>45397</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>45085</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>45342</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45208</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14553,7 +14553,7 @@
         <v>44867</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14626,7 +14626,7 @@
         <v>45433</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14699,7 +14699,7 @@
         <v>45433</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14772,7 +14772,7 @@
         <v>45749</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14845,7 +14845,7 @@
         <v>45296</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14918,7 +14918,7 @@
         <v>45255</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14991,7 +14991,7 @@
         <v>45558</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15064,7 +15064,7 @@
         <v>45446</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15142,7 +15142,7 @@
         <v>45454</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15215,7 +15215,7 @@
         <v>45418</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>44962</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15361,7 +15361,7 @@
         <v>45334</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15434,7 +15434,7 @@
         <v>45260</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15507,7 +15507,7 @@
         <v>44837</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>44837</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>45453</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15726,7 +15726,7 @@
         <v>45515</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>45490</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15872,7 +15872,7 @@
         <v>45323</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15945,7 +15945,7 @@
         <v>44546</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16018,7 +16018,7 @@
         <v>44546</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
         <v>44971</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16164,7 +16164,7 @@
         <v>46013</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16237,7 +16237,7 @@
         <v>46020</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16310,7 +16310,7 @@
         <v>45261</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16383,7 +16383,7 @@
         <v>46020</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16456,7 +16456,7 @@
         <v>46018</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16529,7 +16529,7 @@
         <v>46021</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>45526</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16675,7 +16675,7 @@
         <v>46021</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>46024</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16821,7 +16821,7 @@
         <v>46027</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16894,7 +16894,7 @@
         <v>46029</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16967,7 +16967,7 @@
         <v>45796</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17040,7 +17040,7 @@
         <v>45497</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17118,7 +17118,7 @@
         <v>45240</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17191,7 +17191,7 @@
         <v>45884</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17264,7 +17264,7 @@
         <v>45334</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17342,7 +17342,7 @@
         <v>46029</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>46029</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17488,7 +17488,7 @@
         <v>45558</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>46027</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17634,7 +17634,7 @@
         <v>45558</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17707,7 +17707,7 @@
         <v>46035</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>45886</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17853,7 +17853,7 @@
         <v>46035</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17926,7 +17926,7 @@
         <v>45890</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>45890</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18077,7 +18077,7 @@
         <v>45890</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18150,7 +18150,7 @@
         <v>45631</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45980</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18296,7 +18296,7 @@
         <v>45727</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45068</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18442,7 +18442,7 @@
         <v>45979</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18515,7 +18515,7 @@
         <v>44978</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45982</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18661,7 +18661,7 @@
         <v>46041</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18734,7 +18734,7 @@
         <v>46041</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45979</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>45275</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18953,7 +18953,7 @@
         <v>46044</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19026,7 +19026,7 @@
         <v>46043</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19099,7 +19099,7 @@
         <v>46043</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>46043</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19245,7 +19245,7 @@
         <v>46044</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45898</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19396,7 +19396,7 @@
         <v>45898</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19474,7 +19474,7 @@
         <v>45898</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19552,7 +19552,7 @@
         <v>46045</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45901</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19703,7 +19703,7 @@
         <v>46045</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>46049</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19849,7 +19849,7 @@
         <v>45903</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19922,7 +19922,7 @@
         <v>46050</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45476</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20068,7 +20068,7 @@
         <v>45049</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20141,7 +20141,7 @@
         <v>46049</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20214,7 +20214,7 @@
         <v>46052</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20287,7 +20287,7 @@
         <v>45202</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20360,7 +20360,7 @@
         <v>46045</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20433,7 +20433,7 @@
         <v>45357</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45216</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20579,7 +20579,7 @@
         <v>46051</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20652,7 +20652,7 @@
         <v>46029</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20725,7 +20725,7 @@
         <v>46056</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44917</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20871,7 +20871,7 @@
         <v>45480</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20944,7 +20944,7 @@
         <v>45912</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45911</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45911</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21168,7 +21168,7 @@
         <v>45912</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21241,7 +21241,7 @@
         <v>45114</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21314,7 +21314,7 @@
         <v>46055</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21387,7 +21387,7 @@
         <v>45912</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21460,7 +21460,7 @@
         <v>44959</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21533,7 +21533,7 @@
         <v>45911</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21606,7 +21606,7 @@
         <v>45098</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21679,7 +21679,7 @@
         <v>45916</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21752,7 +21752,7 @@
         <v>45915</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21825,7 +21825,7 @@
         <v>45741</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21898,7 +21898,7 @@
         <v>45520</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21971,7 +21971,7 @@
         <v>45537</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22044,7 +22044,7 @@
         <v>46044</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22117,7 +22117,7 @@
         <v>45510</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45917</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22263,7 +22263,7 @@
         <v>45919</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45002</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45921</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22482,7 +22482,7 @@
         <v>44966</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22555,7 +22555,7 @@
         <v>45921</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22628,7 +22628,7 @@
         <v>46035</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22701,7 +22701,7 @@
         <v>45860</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45797</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22847,7 +22847,7 @@
         <v>46070</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22920,7 +22920,7 @@
         <v>46070</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -22993,7 +22993,7 @@
         <v>46070</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45979</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23139,7 +23139,7 @@
         <v>45797</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45924</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23285,7 +23285,7 @@
         <v>46007</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23358,7 +23358,7 @@
         <v>45103</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>46071</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23504,7 +23504,7 @@
         <v>46072</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23577,7 +23577,7 @@
         <v>46072</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23650,7 +23650,7 @@
         <v>45925</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23723,7 +23723,7 @@
         <v>45925</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23796,7 +23796,7 @@
         <v>46072</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23869,7 +23869,7 @@
         <v>45675</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45929</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45001</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45152</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24161,7 +24161,7 @@
         <v>45932</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24239,7 +24239,7 @@
         <v>45932</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>44731</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24390,7 +24390,7 @@
         <v>45583</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24463,7 +24463,7 @@
         <v>44974</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24536,7 +24536,7 @@
         <v>45934</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24609,7 +24609,7 @@
         <v>44474</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24682,7 +24682,7 @@
         <v>45630</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24755,7 +24755,7 @@
         <v>45630</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44974</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24901,7 +24901,7 @@
         <v>45937</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45937</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25047,7 +25047,7 @@
         <v>46092</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25120,7 +25120,7 @@
         <v>45198</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25193,7 +25193,7 @@
         <v>45397</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>46097</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25339,7 +25339,7 @@
         <v>45939</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25417,7 +25417,7 @@
         <v>46097</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25490,7 +25490,7 @@
         <v>46097</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25563,7 +25563,7 @@
         <v>45944</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25636,7 +25636,7 @@
         <v>45232</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25709,7 +25709,7 @@
         <v>44750</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45946</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25860,7 +25860,7 @@
         <v>46063</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -25933,7 +25933,7 @@
         <v>46101</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26006,7 +26006,7 @@
         <v>44998</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26079,7 +26079,7 @@
         <v>45559</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26152,7 +26152,7 @@
         <v>45951</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45951</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26308,7 +26308,7 @@
         <v>46106</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45623</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45952</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>46106</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>46111</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26683,7 +26683,7 @@
         <v>45751</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26756,7 +26756,7 @@
         <v>45607</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26834,7 +26834,7 @@
         <v>46111</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>44998</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -26985,7 +26985,7 @@
         <v>45955</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>46112</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45015</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27209,7 +27209,7 @@
         <v>45958</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>46113</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27355,7 +27355,7 @@
         <v>45076</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27428,7 +27428,7 @@
         <v>46119</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27501,7 +27501,7 @@
         <v>45365</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27574,7 +27574,7 @@
         <v>45621</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27647,7 +27647,7 @@
         <v>45961</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45964</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27793,7 +27793,7 @@
         <v>45960</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27866,7 +27866,7 @@
         <v>46121</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45027</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45964</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45961</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28163,7 +28163,7 @@
         <v>45961</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28236,7 +28236,7 @@
         <v>45966</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45966</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45624</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28455,7 +28455,7 @@
         <v>45624</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28528,7 +28528,7 @@
         <v>45965</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45964</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45966</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>45966</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45966</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45966</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -28971,7 +28971,7 @@
         <v>45964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29044,7 +29044,7 @@
         <v>46127</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29122,7 +29122,7 @@
         <v>46127</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29195,7 +29195,7 @@
         <v>45965</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29268,7 +29268,7 @@
         <v>45812</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45971</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45637</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45813</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29565,7 +29565,7 @@
         <v>45972</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29638,7 +29638,7 @@
         <v>45974</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>46127</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>46127</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29867,7 +29867,7 @@
         <v>45818</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -29945,7 +29945,7 @@
         <v>45974</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30018,7 +30018,7 @@
         <v>46126</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30091,7 +30091,7 @@
         <v>45127</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45244</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30237,7 +30237,7 @@
         <v>45978</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>45975</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30388,7 +30388,7 @@
         <v>44993</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30461,7 +30461,7 @@
         <v>46114</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>46128</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>46132</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30690,7 +30690,7 @@
         <v>44714</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30768,7 +30768,7 @@
         <v>44967</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30846,7 +30846,7 @@
         <v>45982</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -30919,7 +30919,7 @@
         <v>46114</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -30997,7 +30997,7 @@
         <v>46133</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31070,7 +31070,7 @@
         <v>45981</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>45986</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31216,7 +31216,7 @@
         <v>45818</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31289,7 +31289,7 @@
         <v>45985</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31362,7 +31362,7 @@
         <v>46114</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31440,7 +31440,7 @@
         <v>45985</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45966</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31586,7 +31586,7 @@
         <v>45985</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31659,7 +31659,7 @@
         <v>45986</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31732,7 +31732,7 @@
         <v>45625</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31805,7 +31805,7 @@
         <v>45985</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31878,7 +31878,7 @@
         <v>45988</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45555</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32049,7 +32049,7 @@
         <v>45988</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32122,7 +32122,7 @@
         <v>45727</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32200,7 +32200,7 @@
         <v>45553</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32278,7 +32278,7 @@
         <v>45803</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32351,7 +32351,7 @@
         <v>45818</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45817</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32497,7 +32497,7 @@
         <v>45903</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32575,7 +32575,7 @@
         <v>45474</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32648,7 +32648,7 @@
         <v>45993</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32721,7 +32721,7 @@
         <v>45509</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32794,7 +32794,7 @@
         <v>45863</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>44820</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -32940,7 +32940,7 @@
         <v>45996</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45995</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>46035</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33159,7 +33159,7 @@
         <v>45183</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45995</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33305,7 +33305,7 @@
         <v>45670</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33378,7 +33378,7 @@
         <v>45125</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33456,7 +33456,7 @@
         <v>45132</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33529,7 +33529,7 @@
         <v>45958</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45834</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45027</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33753,7 +33753,7 @@
         <v>45490</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33826,7 +33826,7 @@
         <v>44987</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33899,7 +33899,7 @@
         <v>46001</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -33972,7 +33972,7 @@
         <v>46002</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>46140</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34118,7 +34118,7 @@
         <v>46106</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34191,7 +34191,7 @@
         <v>46006</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34264,7 +34264,7 @@
         <v>46006</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>46006</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34410,7 +34410,7 @@
         <v>45131</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34483,7 +34483,7 @@
         <v>46006</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34556,7 +34556,7 @@
         <v>45406</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34629,7 +34629,7 @@
         <v>45510</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34702,7 +34702,7 @@
         <v>46007</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34775,7 +34775,7 @@
         <v>45303</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34848,7 +34848,7 @@
         <v>44501</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34921,7 +34921,7 @@
         <v>45820</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -34994,7 +34994,7 @@
         <v>46007</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45705</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35140,7 +35140,7 @@
         <v>45176</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35213,7 +35213,7 @@
         <v>46139</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35286,7 +35286,7 @@
         <v>46010</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35359,7 +35359,7 @@
         <v>46010</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35432,7 +35432,7 @@
         <v>45567</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35505,7 +35505,7 @@
         <v>45267</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35578,7 +35578,7 @@
         <v>45456</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>46036</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35734,7 +35734,7 @@
         <v>45369</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35807,7 +35807,7 @@
         <v>45821</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35880,7 +35880,7 @@
         <v>45782</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -35953,7 +35953,7 @@
         <v>45732</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36026,7 +36026,7 @@
         <v>45199</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36099,7 +36099,7 @@
         <v>45061</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36172,7 +36172,7 @@
         <v>45695</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36245,7 +36245,7 @@
         <v>45567</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>46035</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36396,7 +36396,7 @@
         <v>46064</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36469,7 +36469,7 @@
         <v>46139</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36542,7 +36542,7 @@
         <v>45630</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45203</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36688,7 +36688,7 @@
         <v>45825</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36761,7 +36761,7 @@
         <v>46030</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36834,7 +36834,7 @@
         <v>44574</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36907,7 +36907,7 @@
         <v>45113</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -36980,7 +36980,7 @@
         <v>45827</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37053,7 +37053,7 @@
         <v>45030</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37126,7 +37126,7 @@
         <v>44869</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37204,7 +37204,7 @@
         <v>45567</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>44792</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45112</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>46146</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45625</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37569,7 +37569,7 @@
         <v>45832</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>46147</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37715,7 +37715,7 @@
         <v>46148</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37793,7 +37793,7 @@
         <v>46119</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37866,7 +37866,7 @@
         <v>44875</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45467</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38012,7 +38012,7 @@
         <v>46149</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>46149</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>46149</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38241,7 +38241,7 @@
         <v>44749</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38319,7 +38319,7 @@
         <v>44929</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38397,7 +38397,7 @@
         <v>46092</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>46038</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38543,7 +38543,7 @@
         <v>45994</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>46153</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38694,7 +38694,7 @@
         <v>45877</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38767,7 +38767,7 @@
         <v>45833</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38840,7 +38840,7 @@
         <v>45121</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45455</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -38991,7 +38991,7 @@
         <v>46044</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>46052</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39137,7 +39137,7 @@
         <v>46155</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39215,7 +39215,7 @@
         <v>45896</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39288,7 +39288,7 @@
         <v>46043</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39361,7 +39361,7 @@
         <v>45103</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>46156</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39507,7 +39507,7 @@
         <v>44915</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39580,7 +39580,7 @@
         <v>45061</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39653,7 +39653,7 @@
         <v>46155</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>46156</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39804,7 +39804,7 @@
         <v>45835</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39877,7 +39877,7 @@
         <v>45835</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -39950,7 +39950,7 @@
         <v>45756</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40023,7 +40023,7 @@
         <v>44909</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45231</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40169,7 +40169,7 @@
         <v>45103</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40247,7 +40247,7 @@
         <v>45015</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40320,7 +40320,7 @@
         <v>45561</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40393,7 +40393,7 @@
         <v>45518</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40466,7 +40466,7 @@
         <v>45839</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40539,7 +40539,7 @@
         <v>45621</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40612,7 +40612,7 @@
         <v>46162</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45664</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40758,7 +40758,7 @@
         <v>45561</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45847</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40909,7 +40909,7 @@
         <v>45910</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -40982,7 +40982,7 @@
         <v>45849</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41060,7 +41060,7 @@
         <v>45849</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41138,7 +41138,7 @@
         <v>46167</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44992</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41284,7 +41284,7 @@
         <v>45258</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41357,7 +41357,7 @@
         <v>46168</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41430,7 +41430,7 @@
         <v>45376</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>46168</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41576,7 +41576,7 @@
         <v>45267</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41649,7 +41649,7 @@
         <v>44959</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41722,7 +41722,7 @@
         <v>45447</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41795,7 +41795,7 @@
         <v>45219</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41868,7 +41868,7 @@
         <v>45195</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41941,7 +41941,7 @@
         <v>45559</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>45152</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42087,7 +42087,7 @@
         <v>46171</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42165,7 +42165,7 @@
         <v>44951</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42238,7 +42238,7 @@
         <v>46170</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42311,7 +42311,7 @@
         <v>45863</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>46174</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42457,7 +42457,7 @@
         <v>45863</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>44994</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42608,7 +42608,7 @@
         <v>45004</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42681,7 +42681,7 @@
         <v>45376</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42754,7 +42754,7 @@
         <v>45097</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45110</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45544</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -42973,7 +42973,7 @@
         <v>45317</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>46176</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43124,7 +43124,7 @@
         <v>46127</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43197,7 +43197,7 @@
         <v>44986</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43270,7 +43270,7 @@
         <v>45096</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>46181</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43421,7 +43421,7 @@
         <v>46035</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>46126</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43572,7 +43572,7 @@
         <v>46182</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>46182</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43718,7 +43718,7 @@
         <v>45027</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43791,7 +43791,7 @@
         <v>46183</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43869,7 +43869,7 @@
         <v>44580</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43942,7 +43942,7 @@
         <v>46185</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44020,7 +44020,7 @@
         <v>45595</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44093,7 +44093,7 @@
         <v>46188</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44166,7 +44166,7 @@
         <v>45257</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>46190</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45127</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44390,7 +44390,7 @@
         <v>46191</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44468,7 +44468,7 @@
         <v>46191</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44541,7 +44541,7 @@
         <v>46191</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>46197</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44687,7 +44687,7 @@
         <v>46196</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44760,7 +44760,7 @@
         <v>45609</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44833,7 +44833,7 @@
         <v>45001</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44906,7 +44906,7 @@
         <v>45428</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>46197</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45057,7 +45057,7 @@
         <v>46197</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45135,7 +45135,7 @@
         <v>45362</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45208,7 +45208,7 @@
         <v>45169</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45281,7 +45281,7 @@
         <v>45553</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45359,7 +45359,7 @@
         <v>45608</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45432,7 +45432,7 @@
         <v>45881</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45505,7 +45505,7 @@
         <v>45509</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45578,7 +45578,7 @@
         <v>45608</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45651,7 +45651,7 @@
         <v>44643</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45724,7 +45724,7 @@
         <v>45882</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>46202</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>45727</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45943,7 +45943,7 @@
         <v>45428</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46016,7 +46016,7 @@
         <v>45169</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46089,7 +46089,7 @@
         <v>45198</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46162,7 +46162,7 @@
         <v>45165</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46235,7 +46235,7 @@
         <v>46248</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46313,7 +46313,7 @@
         <v>46249</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46391,7 +46391,7 @@
         <v>46252</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>46252</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46542,7 +46542,7 @@
         <v>46252</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46615,7 +46615,7 @@
         <v>45574</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46688,7 +46688,7 @@
         <v>45608</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46761,7 +46761,7 @@
         <v>45200</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46834,7 +46834,7 @@
         <v>45169</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>46251</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -46985,7 +46985,7 @@
         <v>46251</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>45667</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>46024</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47209,7 +47209,7 @@
         <v>45180</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47282,7 +47282,7 @@
         <v>46211</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47355,7 +47355,7 @@
         <v>46254</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47428,7 +47428,7 @@
         <v>46211</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47501,7 +47501,7 @@
         <v>45351</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47574,7 +47574,7 @@
         <v>45244</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47647,7 +47647,7 @@
         <v>45160</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47720,7 +47720,7 @@
         <v>46202</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47798,7 +47798,7 @@
         <v>45568</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47871,7 +47871,7 @@
         <v>45167</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47944,7 +47944,7 @@
         <v>45415</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48017,7 +48017,7 @@
         <v>46259</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48090,7 +48090,7 @@
         <v>45261</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48163,7 +48163,7 @@
         <v>46259</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48236,7 +48236,7 @@
         <v>45261</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48309,7 +48309,7 @@
         <v>46216</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48387,7 +48387,7 @@
         <v>46259</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48465,7 +48465,7 @@
         <v>46259</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>45707</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48611,7 +48611,7 @@
         <v>45252</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48684,7 +48684,7 @@
         <v>44679</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>45256</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45127</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48908,7 +48908,7 @@
         <v>45127</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -48981,7 +48981,7 @@
         <v>44714</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49059,7 +49059,7 @@
         <v>45110</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49132,7 +49132,7 @@
         <v>45197</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49205,7 +49205,7 @@
         <v>45109</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49278,7 +49278,7 @@
         <v>45314</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45314</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49424,7 +49424,7 @@
         <v>45219</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49497,7 +49497,7 @@
         <v>45219</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>45257</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49648,7 +49648,7 @@
         <v>44846</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49721,7 +49721,7 @@
         <v>46268</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45259</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49867,7 +49867,7 @@
         <v>45264</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45104</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50018,7 +50018,7 @@
         <v>45307</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50091,7 +50091,7 @@
         <v>45446</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50164,7 +50164,7 @@
         <v>45373</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50237,7 +50237,7 @@
         <v>46167</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50315,7 +50315,7 @@
         <v>46177</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45266</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50466,7 +50466,7 @@
         <v>44902</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>45264</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50612,7 +50612,7 @@
         <v>45261</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50685,7 +50685,7 @@
         <v>46177</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45397</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50836,7 +50836,7 @@
         <v>44846</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50909,7 +50909,7 @@
         <v>45272</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50982,7 +50982,7 @@
         <v>45266</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>44785</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>46276</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51201,7 +51201,7 @@
         <v>45747</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51274,7 +51274,7 @@
         <v>45201</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51347,7 +51347,7 @@
         <v>46233</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51425,7 +51425,7 @@
         <v>45037</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51498,7 +51498,7 @@
         <v>45621</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51571,7 +51571,7 @@
         <v>45197</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51644,7 +51644,7 @@
         <v>45298</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51717,7 +51717,7 @@
         <v>45216</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>46233</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51868,7 +51868,7 @@
         <v>46281</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51941,7 +51941,7 @@
         <v>45044</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52014,7 +52014,7 @@
         <v>46238</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52092,7 +52092,7 @@
         <v>45418</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52165,7 +52165,7 @@
         <v>45282</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52238,7 +52238,7 @@
         <v>45552</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52311,7 +52311,7 @@
         <v>45523</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52384,7 +52384,7 @@
         <v>46241</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52462,7 +52462,7 @@
         <v>46241</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52540,7 +52540,7 @@
         <v>45035</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52613,7 +52613,7 @@
         <v>45001</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52686,7 +52686,7 @@
         <v>45478</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52759,7 +52759,7 @@
         <v>46288</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52832,7 +52832,7 @@
         <v>45261</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52905,7 +52905,7 @@
         <v>46154</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52983,7 +52983,7 @@
         <v>46287</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53061,7 +53061,7 @@
         <v>46246</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53134,7 +53134,7 @@
         <v>46286</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53212,7 +53212,7 @@
         <v>46289</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53285,7 +53285,7 @@
         <v>44987</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53358,7 +53358,7 @@
         <v>45308</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53431,7 +53431,7 @@
         <v>46240</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53509,7 +53509,7 @@
         <v>45257</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53582,7 +53582,7 @@
         <v>46135</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53660,7 +53660,7 @@
         <v>45036</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53733,7 +53733,7 @@
         <v>46290</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53811,7 +53811,7 @@
         <v>46286</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53889,7 +53889,7 @@
         <v>46247</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53967,7 +53967,7 @@
         <v>46289</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54045,7 +54045,7 @@
         <v>46290</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54118,7 +54118,7 @@
         <v>45230</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54191,7 +54191,7 @@
         <v>45568</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54264,7 +54264,7 @@
         <v>45618</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54337,7 +54337,7 @@
         <v>44918</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54410,7 +54410,7 @@
         <v>44985</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54483,7 +54483,7 @@
         <v>45637</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54556,7 +54556,7 @@
         <v>44533</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54629,7 +54629,7 @@
         <v>45744</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54702,7 +54702,7 @@
         <v>45112</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54775,7 +54775,7 @@
         <v>45114</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54848,7 +54848,7 @@
         <v>45266</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54921,7 +54921,7 @@
         <v>45104</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54994,7 +54994,7 @@
         <v>44974</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55067,7 +55067,7 @@
         <v>44977</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55140,7 +55140,7 @@
         <v>45203</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55213,7 +55213,7 @@
         <v>45131</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55286,7 +55286,7 @@
         <v>44978</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55359,7 +55359,7 @@
         <v>44991</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55432,7 +55432,7 @@
         <v>44991</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55505,7 +55505,7 @@
         <v>44628</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55578,7 +55578,7 @@
         <v>45667</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55651,7 +55651,7 @@
         <v>45306</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55724,7 +55724,7 @@
         <v>44543</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55802,7 +55802,7 @@
         <v>45293</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55875,7 +55875,7 @@
         <v>45154</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55948,7 +55948,7 @@
         <v>45454</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56021,7 +56021,7 @@
         <v>45518</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56094,7 +56094,7 @@
         <v>44912</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56167,7 +56167,7 @@
         <v>44992</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56240,7 +56240,7 @@
         <v>45022</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56313,7 +56313,7 @@
         <v>45302</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56386,7 +56386,7 @@
         <v>45611</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56459,7 +56459,7 @@
         <v>44890</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56532,7 +56532,7 @@
         <v>45677</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56605,7 +56605,7 @@
         <v>45113</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56678,7 +56678,7 @@
         <v>45151</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56751,7 +56751,7 @@
         <v>44909</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56824,7 +56824,7 @@
         <v>45161</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56897,7 +56897,7 @@
         <v>44993</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -56970,7 +56970,7 @@
         <v>45167</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57043,7 +57043,7 @@
         <v>45567</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57116,7 +57116,7 @@
         <v>45280</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57189,7 +57189,7 @@
         <v>45231</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57267,7 +57267,7 @@
         <v>45554</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57345,7 +57345,7 @@
         <v>44711</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57423,7 +57423,7 @@
         <v>45446</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57501,7 +57501,7 @@
         <v>44974</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57574,7 +57574,7 @@
         <v>45647</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57647,7 +57647,7 @@
         <v>45618</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57720,7 +57720,7 @@
         <v>45408</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57793,7 +57793,7 @@
         <v>45296</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>44719</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57939,7 +57939,7 @@
         <v>45049</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58012,7 +58012,7 @@
         <v>45553</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58090,7 +58090,7 @@
         <v>45509</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58163,7 +58163,7 @@
         <v>45726</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58236,7 +58236,7 @@
         <v>44929</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58314,7 +58314,7 @@
         <v>45726</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58387,7 +58387,7 @@
         <v>45103</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58465,7 +58465,7 @@
         <v>45706</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58538,7 +58538,7 @@
         <v>45034</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58611,7 +58611,7 @@
         <v>45695</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58684,7 +58684,7 @@
         <v>45695</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58757,7 +58757,7 @@
         <v>45425</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58830,7 +58830,7 @@
         <v>45425</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58903,7 +58903,7 @@
         <v>45610</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -58976,7 +58976,7 @@
         <v>44992</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59049,7 +59049,7 @@
         <v>45093</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59122,7 +59122,7 @@
         <v>45429</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59195,7 +59195,7 @@
         <v>45349</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59268,7 +59268,7 @@
         <v>45595</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59341,7 +59341,7 @@
         <v>45776</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59419,7 +59419,7 @@
         <v>45779</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59492,7 +59492,7 @@
         <v>45376</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59565,7 +59565,7 @@
         <v>45170</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59643,7 +59643,7 @@
         <v>45015</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45266</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59789,7 +59789,7 @@
         <v>45646</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59862,7 +59862,7 @@
         <v>45524</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59935,7 +59935,7 @@
         <v>45350</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60008,7 +60008,7 @@
         <v>45787</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60081,7 +60081,7 @@
         <v>45790</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60154,7 +60154,7 @@
         <v>45790</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60227,7 +60227,7 @@
         <v>45574</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60300,7 +60300,7 @@
         <v>45596</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60373,7 +60373,7 @@
         <v>44578</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60446,7 +60446,7 @@
         <v>44652</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60519,7 +60519,7 @@
         <v>45074</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60597,7 +60597,7 @@
         <v>45257</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60670,7 +60670,7 @@
         <v>45097</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60743,7 +60743,7 @@
         <v>45351</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60821,7 +60821,7 @@
         <v>44809</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60894,7 +60894,7 @@
         <v>45097</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60967,7 +60967,7 @@
         <v>45133</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61040,7 +61040,7 @@
         <v>45446</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61118,7 +61118,7 @@
         <v>45701</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61196,7 +61196,7 @@
         <v>45701</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61274,7 +61274,7 @@
         <v>45708</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61352,7 +61352,7 @@
         <v>45727</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61430,7 +61430,7 @@
         <v>45799</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61503,7 +61503,7 @@
         <v>45819</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61576,7 +61576,7 @@
         <v>45824</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61649,7 +61649,7 @@
         <v>45835</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61722,7 +61722,7 @@
         <v>45904</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61795,7 +61795,7 @@
         <v>45943</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45964</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61946,7 +61946,7 @@
         <v>46038</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62024,7 +62024,7 @@
         <v>46043</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62097,7 +62097,7 @@
         <v>46052</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62175,7 +62175,7 @@
         <v>44649</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62248,7 +62248,7 @@
         <v>46066</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62321,7 +62321,7 @@
         <v>46076</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62394,7 +62394,7 @@
         <v>46133</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62472,7 +62472,7 @@
         <v>46134</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1090,7 +1090,7 @@
         <v>5.9</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>7</v>
@@ -1117,13 +1117,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="U5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1146,6 +1146,7 @@
 Vedticka
 Gråspett
 Kransmossa
+Kärrviol
 Linnea
 Spillkråka
 Sälg
@@ -1153,6 +1154,7 @@
 Tofsmes
 Kungsfågel
 Vanlig groda
+Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1213,7 +1215,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1229,7 +1231,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
@@ -1256,13 +1258,13 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="U6" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1285,6 +1287,7 @@
 Vedticka
 Gråspett
 Kransmossa
+Kärrviol
 Linnea
 Spillkråka
 Sälg
@@ -1292,6 +1295,7 @@
 Tofsmes
 Kungsfågel
 Vanlig groda
+Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1352,7 +1356,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1483,7 +1487,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1613,7 +1617,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1743,7 +1747,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1868,7 +1872,7 @@
         <v>46047</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1991,7 +1995,7 @@
         <v>45835</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2118,7 +2122,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2244,7 +2248,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2369,7 +2373,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2492,7 +2496,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2614,7 +2618,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2731,7 +2735,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2847,7 +2851,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2967,7 +2971,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3083,7 +3087,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3194,7 +3198,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3314,7 +3318,7 @@
         <v>45489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3424,7 +3428,7 @@
         <v>45896</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3547,7 +3551,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3661,7 +3665,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3771,7 +3775,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3881,7 +3885,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3990,7 +3994,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4099,7 +4103,7 @@
         <v>45638</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4208,7 +4212,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4317,7 +4321,7 @@
         <v>46166</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4430,7 +4434,7 @@
         <v>45835</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4547,7 +4551,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4660,7 +4664,7 @@
         <v>45931</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4768,7 +4772,7 @@
         <v>45632</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4876,7 +4880,7 @@
         <v>44869</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4988,7 +4992,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5095,7 +5099,7 @@
         <v>45901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5211,7 +5215,7 @@
         <v>46097</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5322,7 +5326,7 @@
         <v>45637</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5429,7 +5433,7 @@
         <v>46237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5540,7 +5544,7 @@
         <v>44829</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5650,7 +5654,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5756,7 +5760,7 @@
         <v>46027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5862,7 +5866,7 @@
         <v>45254</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5968,7 +5972,7 @@
         <v>45812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6074,7 +6078,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6180,7 +6184,7 @@
         <v>45996</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6286,7 +6290,7 @@
         <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6396,7 +6400,7 @@
         <v>45849</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6502,7 +6506,7 @@
         <v>45028</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6608,7 +6612,7 @@
         <v>45358</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6714,7 +6718,7 @@
         <v>45656</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6820,7 +6824,7 @@
         <v>45274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6930,7 +6934,7 @@
         <v>46226</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7041,7 +7045,7 @@
         <v>46283</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7152,7 +7156,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7267,7 +7271,7 @@
         <v>45251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7377,7 +7381,7 @@
         <v>44602</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7492,7 +7496,7 @@
         <v>44536</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7597,7 +7601,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7707,7 +7711,7 @@
         <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7821,7 +7825,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7926,7 +7930,7 @@
         <v>44761</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8035,7 +8039,7 @@
         <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8140,7 +8144,7 @@
         <v>45127</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8249,7 +8253,7 @@
         <v>45256</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8354,7 +8358,7 @@
         <v>45690</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8463,7 +8467,7 @@
         <v>45793</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8568,7 +8572,7 @@
         <v>46041</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8673,7 +8677,7 @@
         <v>46069</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8778,7 +8782,7 @@
         <v>45839</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8888,7 +8892,7 @@
         <v>45959</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8997,7 +9001,7 @@
         <v>45960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9107,7 +9111,7 @@
         <v>45981</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9212,7 +9216,7 @@
         <v>45621</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9317,7 +9321,7 @@
         <v>45228</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9426,7 +9430,7 @@
         <v>46120</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9531,7 +9535,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9636,7 +9640,7 @@
         <v>44909</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9745,7 +9749,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9850,7 +9854,7 @@
         <v>45016</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9955,7 +9959,7 @@
         <v>45294</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10064,7 +10068,7 @@
         <v>45061</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10169,7 +10173,7 @@
         <v>44918</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10274,7 +10278,7 @@
         <v>45638</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10383,7 +10387,7 @@
         <v>46155</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10497,7 +10501,7 @@
         <v>46202</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10606,7 +10610,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10720,7 +10724,7 @@
         <v>44973</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10825,7 +10829,7 @@
         <v>46287</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10935,7 +10939,7 @@
         <v>46244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11040,7 +11044,7 @@
         <v>44992</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11149,7 +11153,7 @@
         <v>45091</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11254,7 +11258,7 @@
         <v>45761</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11359,7 +11363,7 @@
         <v>45005</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11468,7 +11472,7 @@
         <v>45418</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11573,7 +11577,7 @@
         <v>45754</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11678,7 +11682,7 @@
         <v>45502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11783,7 +11787,7 @@
         <v>45181</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11888,7 +11892,7 @@
         <v>45996</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11998,7 +12002,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12071,7 +12075,7 @@
         <v>44491</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12144,7 +12148,7 @@
         <v>44834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12217,7 +12221,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12295,7 +12299,7 @@
         <v>44671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12368,7 +12372,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12446,7 +12450,7 @@
         <v>44512</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12519,7 +12523,7 @@
         <v>44869</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12597,7 +12601,7 @@
         <v>44570</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12670,7 +12674,7 @@
         <v>44670</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12743,7 +12747,7 @@
         <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12816,7 +12820,7 @@
         <v>44877</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12889,7 +12893,7 @@
         <v>44539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12962,7 +12966,7 @@
         <v>44529</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13035,7 +13039,7 @@
         <v>44824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13108,7 +13112,7 @@
         <v>44834</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13181,7 +13185,7 @@
         <v>44693</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13254,7 +13258,7 @@
         <v>44503</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13327,7 +13331,7 @@
         <v>44533</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13400,7 +13404,7 @@
         <v>44851</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13473,7 +13477,7 @@
         <v>44865</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13551,7 +13555,7 @@
         <v>44792</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13624,7 +13628,7 @@
         <v>44690</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13702,7 +13706,7 @@
         <v>44684</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13780,7 +13784,7 @@
         <v>44543</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13853,7 +13857,7 @@
         <v>44777</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13926,7 +13930,7 @@
         <v>44651</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13999,7 +14003,7 @@
         <v>44862</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14072,7 +14076,7 @@
         <v>44533</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14145,7 +14149,7 @@
         <v>44797</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14218,7 +14222,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14291,7 +14295,7 @@
         <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14364,7 +14368,7 @@
         <v>45397</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14437,7 +14441,7 @@
         <v>45561</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14510,7 +14514,7 @@
         <v>45098</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14583,7 +14587,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14656,7 +14660,7 @@
         <v>45362</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14729,7 +14733,7 @@
         <v>45103</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14802,7 +14806,7 @@
         <v>44543</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14880,7 +14884,7 @@
         <v>45637</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14953,7 +14957,7 @@
         <v>45373</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15026,7 +15030,7 @@
         <v>45425</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15099,7 +15103,7 @@
         <v>45266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15172,7 +15176,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15245,7 +15249,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15318,7 +15322,7 @@
         <v>44993</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15391,7 +15395,7 @@
         <v>45518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15464,7 +15468,7 @@
         <v>45257</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15537,7 +15541,7 @@
         <v>45132</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15610,7 +15614,7 @@
         <v>45446</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15688,7 +15692,7 @@
         <v>44533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15761,7 +15765,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15839,7 +15843,7 @@
         <v>44929</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15917,7 +15921,7 @@
         <v>45455</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15995,7 +15999,7 @@
         <v>45127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16068,7 +16072,7 @@
         <v>45261</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16141,7 +16145,7 @@
         <v>45523</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16214,7 +16218,7 @@
         <v>45264</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16287,7 +16291,7 @@
         <v>45256</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16360,7 +16364,7 @@
         <v>45476</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16433,7 +16437,7 @@
         <v>45608</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16506,7 +16510,7 @@
         <v>44711</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16584,7 +16588,7 @@
         <v>45787</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16657,7 +16661,7 @@
         <v>45044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16730,7 +16734,7 @@
         <v>44915</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16803,7 +16807,7 @@
         <v>45302</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16876,7 +16880,7 @@
         <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16949,7 +16953,7 @@
         <v>45015</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17022,7 +17026,7 @@
         <v>45524</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17095,7 +17099,7 @@
         <v>45037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17168,7 +17172,7 @@
         <v>45886</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17241,7 +17245,7 @@
         <v>46002</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17314,7 +17318,7 @@
         <v>44546</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17387,7 +17391,7 @@
         <v>44546</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17460,7 +17464,7 @@
         <v>45518</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17533,7 +17537,7 @@
         <v>46006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17606,7 +17610,7 @@
         <v>46006</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17679,7 +17683,7 @@
         <v>46006</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17752,7 +17756,7 @@
         <v>46006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17825,7 +17829,7 @@
         <v>46007</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17898,7 +17902,7 @@
         <v>46007</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17971,7 +17975,7 @@
         <v>45296</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18044,7 +18048,7 @@
         <v>46010</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18117,7 +18121,7 @@
         <v>46010</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18190,7 +18194,7 @@
         <v>45790</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18263,7 +18267,7 @@
         <v>46013</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18336,7 +18340,7 @@
         <v>45596</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18409,7 +18413,7 @@
         <v>45637</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18482,7 +18486,7 @@
         <v>46018</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18555,7 +18559,7 @@
         <v>46020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18628,7 +18632,7 @@
         <v>45154</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18701,7 +18705,7 @@
         <v>44580</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18774,7 +18778,7 @@
         <v>46021</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18847,7 +18851,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18920,7 +18924,7 @@
         <v>46020</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18993,7 +18997,7 @@
         <v>45454</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19066,7 +19070,7 @@
         <v>46021</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19139,7 +19143,7 @@
         <v>45890</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19212,7 +19216,7 @@
         <v>45446</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19285,7 +19289,7 @@
         <v>45890</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19358,7 +19362,7 @@
         <v>46024</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19431,7 +19435,7 @@
         <v>45230</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19504,7 +19508,7 @@
         <v>46027</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19577,7 +19581,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19650,7 +19654,7 @@
         <v>45574</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19723,7 +19727,7 @@
         <v>46029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19796,7 +19800,7 @@
         <v>46029</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19869,7 +19873,7 @@
         <v>44986</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19942,7 +19946,7 @@
         <v>45515</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20015,7 +20019,7 @@
         <v>45790</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20088,7 +20092,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20166,7 +20170,7 @@
         <v>45898</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20244,7 +20248,7 @@
         <v>45898</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20322,7 +20326,7 @@
         <v>45568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20395,7 +20399,7 @@
         <v>45898</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20473,7 +20477,7 @@
         <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20546,7 +20550,7 @@
         <v>45198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20619,7 +20623,7 @@
         <v>45103</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20697,7 +20701,7 @@
         <v>46027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20770,7 +20774,7 @@
         <v>46035</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20843,7 +20847,7 @@
         <v>44977</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20916,7 +20920,7 @@
         <v>45490</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20989,7 +20993,7 @@
         <v>45903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21062,7 +21066,7 @@
         <v>45376</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21135,7 +21139,7 @@
         <v>45219</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21208,7 +21212,7 @@
         <v>45979</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21281,7 +21285,7 @@
         <v>45103</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21359,7 +21363,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21432,7 +21436,7 @@
         <v>45497</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21510,7 +21514,7 @@
         <v>46041</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21583,7 +21587,7 @@
         <v>46041</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21656,7 +21660,7 @@
         <v>45979</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21729,7 +21733,7 @@
         <v>45982</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21802,7 +21806,7 @@
         <v>46043</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21875,7 +21879,7 @@
         <v>46043</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21948,7 +21952,7 @@
         <v>45911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22021,7 +22025,7 @@
         <v>46043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22094,7 +22098,7 @@
         <v>45911</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22167,7 +22171,7 @@
         <v>45911</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22240,7 +22244,7 @@
         <v>45261</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22313,7 +22317,7 @@
         <v>45796</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22386,7 +22390,7 @@
         <v>44971</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22459,7 +22463,7 @@
         <v>45912</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22537,7 +22541,7 @@
         <v>46045</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22610,7 +22614,7 @@
         <v>45912</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22683,7 +22687,7 @@
         <v>46044</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22756,7 +22760,7 @@
         <v>45915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22829,7 +22833,7 @@
         <v>46045</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22902,7 +22906,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22975,7 +22979,7 @@
         <v>45912</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23048,7 +23052,7 @@
         <v>46049</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23121,7 +23125,7 @@
         <v>45240</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23194,7 +23198,7 @@
         <v>45916</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23267,7 +23271,7 @@
         <v>46049</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23340,7 +23344,7 @@
         <v>45558</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23413,7 +23417,7 @@
         <v>45917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23486,7 +23490,7 @@
         <v>46051</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23559,7 +23563,7 @@
         <v>45919</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23632,7 +23636,7 @@
         <v>46050</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23705,7 +23709,7 @@
         <v>45114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23778,7 +23782,7 @@
         <v>46029</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23851,7 +23855,7 @@
         <v>46055</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23924,7 +23928,7 @@
         <v>46052</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23997,7 +24001,7 @@
         <v>45258</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24070,7 +24074,7 @@
         <v>46045</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24143,7 +24147,7 @@
         <v>45921</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24216,7 +24220,7 @@
         <v>45921</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24289,7 +24293,7 @@
         <v>45480</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24362,7 +24366,7 @@
         <v>45924</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24435,7 +24439,7 @@
         <v>45397</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24508,7 +24512,7 @@
         <v>45925</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24581,7 +24585,7 @@
         <v>45925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24654,7 +24658,7 @@
         <v>45260</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24727,7 +24731,7 @@
         <v>44966</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24800,7 +24804,7 @@
         <v>45183</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24873,7 +24877,7 @@
         <v>46056</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24946,7 +24950,7 @@
         <v>45261</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25019,7 +25023,7 @@
         <v>45520</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25092,7 +25096,7 @@
         <v>45929</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25165,7 +25169,7 @@
         <v>46044</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25238,7 +25242,7 @@
         <v>44867</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25311,7 +25315,7 @@
         <v>45537</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25384,7 +25388,7 @@
         <v>45667</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25457,7 +25461,7 @@
         <v>45932</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25535,7 +25539,7 @@
         <v>45932</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25613,7 +25617,7 @@
         <v>46007</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25686,7 +25690,7 @@
         <v>45860</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25759,7 +25763,7 @@
         <v>46035</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25832,7 +25836,7 @@
         <v>45797</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25905,7 +25909,7 @@
         <v>45934</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25978,7 +25982,7 @@
         <v>45630</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26051,7 +26055,7 @@
         <v>45630</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26124,7 +26128,7 @@
         <v>45939</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26202,7 +26206,7 @@
         <v>45110</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26275,7 +26279,7 @@
         <v>45979</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26348,7 +26352,7 @@
         <v>45937</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26421,7 +26425,7 @@
         <v>45797</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26494,7 +26498,7 @@
         <v>46071</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26567,7 +26571,7 @@
         <v>46070</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26640,7 +26644,7 @@
         <v>45937</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26713,7 +26717,7 @@
         <v>45001</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26786,7 +26790,7 @@
         <v>45015</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26859,7 +26863,7 @@
         <v>46070</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26932,7 +26936,7 @@
         <v>46070</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27005,7 +27009,7 @@
         <v>45232</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27078,7 +27082,7 @@
         <v>46072</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27151,7 +27155,7 @@
         <v>46072</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27224,7 +27228,7 @@
         <v>45376</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27297,7 +27301,7 @@
         <v>46072</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27370,7 +27374,7 @@
         <v>45027</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27443,7 +27447,7 @@
         <v>45944</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27516,7 +27520,7 @@
         <v>45946</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27589,7 +27593,7 @@
         <v>44731</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27662,7 +27666,7 @@
         <v>45951</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27740,7 +27744,7 @@
         <v>45695</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27813,7 +27817,7 @@
         <v>45259</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27886,7 +27890,7 @@
         <v>45151</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27959,7 +27963,7 @@
         <v>45951</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28037,7 +28041,7 @@
         <v>44987</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28110,7 +28114,7 @@
         <v>45952</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28183,7 +28187,7 @@
         <v>45812</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28261,7 +28265,7 @@
         <v>45955</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28334,7 +28338,7 @@
         <v>45813</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28407,7 +28411,7 @@
         <v>45958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28480,7 +28484,7 @@
         <v>45961</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28553,7 +28557,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28626,7 +28630,7 @@
         <v>45960</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28699,7 +28703,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28772,7 +28776,7 @@
         <v>46092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28845,7 +28849,7 @@
         <v>45306</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28918,7 +28922,7 @@
         <v>45965</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28996,7 +29000,7 @@
         <v>45964</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29069,7 +29073,7 @@
         <v>45964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29142,7 +29146,7 @@
         <v>45964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29215,7 +29219,7 @@
         <v>45964</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29288,7 +29292,7 @@
         <v>45965</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29361,7 +29365,7 @@
         <v>45677</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29434,7 +29438,7 @@
         <v>44749</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29512,7 +29516,7 @@
         <v>45966</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29585,7 +29589,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29658,7 +29662,7 @@
         <v>45966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29731,7 +29735,7 @@
         <v>45966</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29804,7 +29808,7 @@
         <v>45966</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29877,7 +29881,7 @@
         <v>45966</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29950,7 +29954,7 @@
         <v>45817</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30023,7 +30027,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30096,7 +30100,7 @@
         <v>46097</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30169,7 +30173,7 @@
         <v>46097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30242,7 +30246,7 @@
         <v>46097</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30315,7 +30319,7 @@
         <v>45001</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30388,7 +30392,7 @@
         <v>46063</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30461,7 +30465,7 @@
         <v>45510</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30534,7 +30538,7 @@
         <v>45624</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30607,7 +30611,7 @@
         <v>45972</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30680,7 +30684,7 @@
         <v>45425</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30753,7 +30757,7 @@
         <v>45351</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30826,7 +30830,7 @@
         <v>45349</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30899,7 +30903,7 @@
         <v>45975</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30977,7 +30981,7 @@
         <v>46101</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31050,7 +31054,7 @@
         <v>45974</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31123,7 +31127,7 @@
         <v>44837</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31196,7 +31200,7 @@
         <v>45974</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31269,7 +31273,7 @@
         <v>45061</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31342,7 +31346,7 @@
         <v>46106</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31420,7 +31424,7 @@
         <v>45574</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31493,7 +31497,7 @@
         <v>46106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31566,7 +31570,7 @@
         <v>45978</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31639,7 +31643,7 @@
         <v>45818</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31712,7 +31716,7 @@
         <v>45611</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31785,7 +31789,7 @@
         <v>45818</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31863,7 +31867,7 @@
         <v>45981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31936,7 +31940,7 @@
         <v>45966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32009,7 +32013,7 @@
         <v>45985</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32082,7 +32086,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32155,7 +32159,7 @@
         <v>45583</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32228,7 +32232,7 @@
         <v>45985</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32301,7 +32305,7 @@
         <v>45818</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32374,7 +32378,7 @@
         <v>46112</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32452,7 +32456,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32525,7 +32529,7 @@
         <v>46111</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32603,7 +32607,7 @@
         <v>45567</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32676,7 +32680,7 @@
         <v>45036</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32749,7 +32753,7 @@
         <v>45820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32822,7 +32826,7 @@
         <v>45982</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32895,7 +32899,7 @@
         <v>45618</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32968,7 +32972,7 @@
         <v>45631</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33041,7 +33045,7 @@
         <v>45986</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33114,7 +33118,7 @@
         <v>46113</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33187,7 +33191,7 @@
         <v>45986</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33260,7 +33264,7 @@
         <v>44501</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33333,7 +33337,7 @@
         <v>45825</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33406,7 +33410,7 @@
         <v>45559</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33479,7 +33483,7 @@
         <v>45821</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33552,7 +33556,7 @@
         <v>45988</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33625,7 +33629,7 @@
         <v>45903</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33703,7 +33707,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33801,7 +33805,7 @@
         <v>46119</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33874,7 +33878,7 @@
         <v>45749</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33947,7 +33951,7 @@
         <v>44962</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34020,7 +34024,7 @@
         <v>46121</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34098,7 +34102,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34171,7 +34175,7 @@
         <v>44974</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34244,7 +34248,7 @@
         <v>44992</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34317,7 +34321,7 @@
         <v>45993</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34390,7 +34394,7 @@
         <v>45995</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34463,7 +34467,7 @@
         <v>45160</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34536,7 +34540,7 @@
         <v>45203</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34609,7 +34613,7 @@
         <v>45995</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34682,7 +34686,7 @@
         <v>45433</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34755,7 +34759,7 @@
         <v>45433</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34828,7 +34832,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34901,7 +34905,7 @@
         <v>45705</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34974,7 +34978,7 @@
         <v>44959</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35047,7 +35051,7 @@
         <v>46127</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35125,7 +35129,7 @@
         <v>45342</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35203,7 +35207,7 @@
         <v>46127</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35276,7 +35280,7 @@
         <v>46128</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35354,7 +35358,7 @@
         <v>46127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35432,7 +35436,7 @@
         <v>46001</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35505,7 +35509,7 @@
         <v>46114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35583,7 +35587,7 @@
         <v>45104</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35656,7 +35660,7 @@
         <v>46132</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35729,7 +35733,7 @@
         <v>45113</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35802,7 +35806,7 @@
         <v>46114</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35880,7 +35884,7 @@
         <v>45114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35953,7 +35957,7 @@
         <v>45833</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36026,7 +36030,7 @@
         <v>45832</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36099,7 +36103,7 @@
         <v>45453</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36172,7 +36176,7 @@
         <v>45553</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36250,7 +36254,7 @@
         <v>45408</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36323,7 +36327,7 @@
         <v>46133</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36396,7 +36400,7 @@
         <v>45195</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36469,7 +36473,7 @@
         <v>45085</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36542,7 +36546,7 @@
         <v>45726</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36615,7 +36619,7 @@
         <v>45835</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36688,7 +36692,7 @@
         <v>45839</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36761,7 +36765,7 @@
         <v>45334</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36834,7 +36838,7 @@
         <v>44993</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36907,7 +36911,7 @@
         <v>46035</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36980,7 +36984,7 @@
         <v>46139</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37053,7 +37057,7 @@
         <v>44951</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37126,7 +37130,7 @@
         <v>45567</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37199,7 +37203,7 @@
         <v>45707</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37272,7 +37276,7 @@
         <v>46106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37345,7 +37349,7 @@
         <v>45104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37423,7 +37427,7 @@
         <v>45751</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37496,7 +37500,7 @@
         <v>45803</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37569,7 +37573,7 @@
         <v>44820</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37642,7 +37646,7 @@
         <v>45474</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37715,7 +37719,7 @@
         <v>45782</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37788,7 +37792,7 @@
         <v>45670</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37861,7 +37865,7 @@
         <v>45847</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37934,7 +37938,7 @@
         <v>45834</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38012,7 +38016,7 @@
         <v>45456</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38090,7 +38094,7 @@
         <v>44994</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38163,7 +38167,7 @@
         <v>45849</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38241,7 +38245,7 @@
         <v>45561</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38319,7 +38323,7 @@
         <v>45849</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38397,7 +38401,7 @@
         <v>44978</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38470,7 +38474,7 @@
         <v>45197</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38543,7 +38547,7 @@
         <v>45732</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38616,7 +38620,7 @@
         <v>45509</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38689,7 +38693,7 @@
         <v>44902</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38762,7 +38766,7 @@
         <v>45555</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38835,7 +38839,7 @@
         <v>45351</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38908,7 +38912,7 @@
         <v>45125</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38986,7 +38990,7 @@
         <v>45308</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39059,7 +39063,7 @@
         <v>45863</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39132,7 +39136,7 @@
         <v>45553</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39210,7 +39214,7 @@
         <v>45625</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39283,7 +39287,7 @@
         <v>46035</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39356,7 +39360,7 @@
         <v>44628</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39429,7 +39433,7 @@
         <v>45558</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39502,7 +39506,7 @@
         <v>46139</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39575,7 +39579,7 @@
         <v>45022</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39648,7 +39652,7 @@
         <v>45630</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39721,7 +39725,7 @@
         <v>45303</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39794,7 +39798,7 @@
         <v>46114</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39872,7 +39876,7 @@
         <v>45334</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39950,7 +39954,7 @@
         <v>44837</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40023,7 +40027,7 @@
         <v>45317</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40096,7 +40100,7 @@
         <v>45002</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40169,7 +40173,7 @@
         <v>45552</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40242,7 +40246,7 @@
         <v>45030</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40315,7 +40319,7 @@
         <v>45695</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40388,7 +40392,7 @@
         <v>45863</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40466,7 +40470,7 @@
         <v>45958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40539,7 +40543,7 @@
         <v>45490</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40612,7 +40616,7 @@
         <v>44959</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40685,7 +40689,7 @@
         <v>45418</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40758,7 +40762,7 @@
         <v>45863</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40831,7 +40835,7 @@
         <v>46064</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40904,7 +40908,7 @@
         <v>45706</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40977,7 +40981,7 @@
         <v>45567</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41050,7 +41054,7 @@
         <v>44998</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41123,7 +41127,7 @@
         <v>44998</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41196,7 +41200,7 @@
         <v>46140</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41269,7 +41273,7 @@
         <v>45621</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41342,7 +41346,7 @@
         <v>45478</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41415,7 +41419,7 @@
         <v>45624</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41488,7 +41492,7 @@
         <v>46030</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41561,7 +41565,7 @@
         <v>45406</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41634,7 +41638,7 @@
         <v>46036</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41712,7 +41716,7 @@
         <v>44992</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41785,7 +41789,7 @@
         <v>45103</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41858,7 +41862,7 @@
         <v>45429</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41931,7 +41935,7 @@
         <v>45618</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42004,7 +42008,7 @@
         <v>45554</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42082,7 +42086,7 @@
         <v>45167</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42155,7 +42159,7 @@
         <v>46146</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42228,7 +42232,7 @@
         <v>44974</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42301,7 +42305,7 @@
         <v>44974</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42374,7 +42378,7 @@
         <v>45675</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42447,7 +42451,7 @@
         <v>46147</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42520,7 +42524,7 @@
         <v>46149</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42593,7 +42597,7 @@
         <v>46119</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42666,7 +42670,7 @@
         <v>46149</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42744,7 +42748,7 @@
         <v>46148</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42822,7 +42826,7 @@
         <v>46149</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42900,7 +42904,7 @@
         <v>45877</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42973,7 +42977,7 @@
         <v>45131</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43046,7 +43050,7 @@
         <v>45112</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43119,7 +43123,7 @@
         <v>46038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43192,7 +43196,7 @@
         <v>45121</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43265,7 +43269,7 @@
         <v>46092</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43338,7 +43342,7 @@
         <v>45835</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43411,7 +43415,7 @@
         <v>45365</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43484,7 +43488,7 @@
         <v>45896</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43557,7 +43561,7 @@
         <v>46155</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43635,7 +43639,7 @@
         <v>46155</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43713,7 +43717,7 @@
         <v>46043</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43786,7 +43790,7 @@
         <v>46052</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43859,7 +43863,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43932,7 +43936,7 @@
         <v>45027</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44005,7 +44009,7 @@
         <v>46044</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44078,7 +44082,7 @@
         <v>45257</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44156,7 +44160,7 @@
         <v>46156</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44229,7 +44233,7 @@
         <v>45165</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44302,7 +44306,7 @@
         <v>46156</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44375,7 +44379,7 @@
         <v>45610</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44448,7 +44452,7 @@
         <v>45397</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44521,7 +44525,7 @@
         <v>45621</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44594,7 +44598,7 @@
         <v>45454</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44667,7 +44671,7 @@
         <v>45169</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44740,7 +44744,7 @@
         <v>46162</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44813,7 +44817,7 @@
         <v>45727</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44886,7 +44890,7 @@
         <v>45180</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44959,7 +44963,7 @@
         <v>46167</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45032,7 +45036,7 @@
         <v>46168</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45105,7 +45109,7 @@
         <v>45621</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45178,7 +45182,7 @@
         <v>46168</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45251,7 +45255,7 @@
         <v>45446</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45329,7 +45333,7 @@
         <v>45910</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45402,7 +45406,7 @@
         <v>45623</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45475,7 +45479,7 @@
         <v>45695</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45548,7 +45552,7 @@
         <v>45113</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45621,7 +45625,7 @@
         <v>46170</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45694,7 +45698,7 @@
         <v>45127</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45767,7 +45771,7 @@
         <v>45127</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45840,7 +45844,7 @@
         <v>45160</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45913,7 +45917,7 @@
         <v>46171</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45991,7 +45995,7 @@
         <v>45881</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46064,7 +46068,7 @@
         <v>45127</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46137,7 +46141,7 @@
         <v>44474</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46210,7 +46214,7 @@
         <v>45428</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46283,7 +46287,7 @@
         <v>45664</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46356,7 +46360,7 @@
         <v>46174</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46429,7 +46433,7 @@
         <v>45882</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46502,7 +46506,7 @@
         <v>45608</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46575,7 +46579,7 @@
         <v>46176</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46653,7 +46657,7 @@
         <v>45667</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46726,7 +46730,7 @@
         <v>45884</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46799,7 +46803,7 @@
         <v>45198</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46872,7 +46876,7 @@
         <v>45625</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46945,7 +46949,7 @@
         <v>44912</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47018,7 +47022,7 @@
         <v>46035</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47091,7 +47095,7 @@
         <v>45747</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47164,7 +47168,7 @@
         <v>46127</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47237,7 +47241,7 @@
         <v>45068</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47310,7 +47314,7 @@
         <v>46182</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47383,7 +47387,7 @@
         <v>46182</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47456,7 +47460,7 @@
         <v>46181</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47534,7 +47538,7 @@
         <v>44746</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47607,7 +47611,7 @@
         <v>44917</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47680,7 +47684,7 @@
         <v>46185</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47758,7 +47762,7 @@
         <v>44909</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47831,7 +47835,7 @@
         <v>45282</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47904,7 +47908,7 @@
         <v>46188</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47977,7 +47981,7 @@
         <v>45257</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48050,7 +48054,7 @@
         <v>45526</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48123,7 +48127,7 @@
         <v>46190</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48201,7 +48205,7 @@
         <v>45369</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48274,7 +48278,7 @@
         <v>45027</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48347,7 +48351,7 @@
         <v>46191</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48420,7 +48424,7 @@
         <v>46191</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48498,7 +48502,7 @@
         <v>45197</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48571,7 +48575,7 @@
         <v>46191</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48644,7 +48648,7 @@
         <v>45608</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48717,7 +48721,7 @@
         <v>46196</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48790,7 +48794,7 @@
         <v>45741</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48863,7 +48867,7 @@
         <v>46197</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48936,7 +48940,7 @@
         <v>46197</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49014,7 +49018,7 @@
         <v>46197</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49092,7 +49096,7 @@
         <v>45280</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49165,7 +49169,7 @@
         <v>46202</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49238,7 +49242,7 @@
         <v>44875</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49311,7 +49315,7 @@
         <v>44992</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49384,7 +49388,7 @@
         <v>44929</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49462,7 +49466,7 @@
         <v>45169</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49535,7 +49539,7 @@
         <v>45275</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49608,7 +49612,7 @@
         <v>45252</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49681,7 +49685,7 @@
         <v>45219</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49754,7 +49758,7 @@
         <v>45609</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49827,7 +49831,7 @@
         <v>45176</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49900,7 +49904,7 @@
         <v>46024</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49973,7 +49977,7 @@
         <v>45097</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50046,7 +50050,7 @@
         <v>45595</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50119,7 +50123,7 @@
         <v>46211</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50192,7 +50196,7 @@
         <v>46211</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50265,7 +50269,7 @@
         <v>45034</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50338,7 +50342,7 @@
         <v>46259</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50411,7 +50415,7 @@
         <v>46216</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50489,7 +50493,7 @@
         <v>44846</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50562,7 +50566,7 @@
         <v>46259</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50640,7 +50644,7 @@
         <v>46259</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50713,7 +50717,7 @@
         <v>46259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50786,7 +50790,7 @@
         <v>46202</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50864,7 +50868,7 @@
         <v>45049</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50937,7 +50941,7 @@
         <v>44869</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51015,7 +51019,7 @@
         <v>45357</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51088,7 +51092,7 @@
         <v>45264</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51161,7 +51165,7 @@
         <v>45110</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51234,7 +51238,7 @@
         <v>45152</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51307,7 +51311,7 @@
         <v>45061</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51380,7 +51384,7 @@
         <v>44918</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51453,7 +51457,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51526,7 +51530,7 @@
         <v>45509</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51599,7 +51603,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51677,7 +51681,7 @@
         <v>45096</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51750,7 +51754,7 @@
         <v>46177</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51828,7 +51832,7 @@
         <v>45378</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51901,7 +51905,7 @@
         <v>45415</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51974,7 +51978,7 @@
         <v>45553</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52052,7 +52056,7 @@
         <v>46167</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52130,7 +52134,7 @@
         <v>46276</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52203,7 +52207,7 @@
         <v>46233</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52281,7 +52285,7 @@
         <v>45152</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52354,7 +52358,7 @@
         <v>46233</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52432,7 +52436,7 @@
         <v>45050</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52505,7 +52509,7 @@
         <v>45203</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52578,7 +52582,7 @@
         <v>45567</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52656,7 +52660,7 @@
         <v>46281</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52729,7 +52733,7 @@
         <v>45231</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52802,7 +52806,7 @@
         <v>46238</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52880,7 +52884,7 @@
         <v>45272</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52953,7 +52957,7 @@
         <v>44679</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53031,7 +53035,7 @@
         <v>45345</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53104,7 +53108,7 @@
         <v>46154</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53182,7 +53186,7 @@
         <v>45323</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53255,7 +53259,7 @@
         <v>46241</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53333,7 +53337,7 @@
         <v>45467</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53406,7 +53410,7 @@
         <v>45559</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53479,7 +53483,7 @@
         <v>46241</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53557,7 +53561,7 @@
         <v>45756</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53630,7 +53634,7 @@
         <v>45004</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53703,7 +53707,7 @@
         <v>45035</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53776,7 +53780,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53854,7 +53858,7 @@
         <v>45201</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53927,7 +53931,7 @@
         <v>45727</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54005,7 +54009,7 @@
         <v>46288</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54078,7 +54082,7 @@
         <v>46289</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54151,7 +54155,7 @@
         <v>44987</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54224,7 +54228,7 @@
         <v>46246</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54297,7 +54301,7 @@
         <v>45314</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54370,7 +54374,7 @@
         <v>45314</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54443,7 +54447,7 @@
         <v>46293</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54516,7 +54520,7 @@
         <v>46293</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54589,7 +54593,7 @@
         <v>45544</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54662,7 +54666,7 @@
         <v>46135</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54740,7 +54744,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54813,7 +54817,7 @@
         <v>46293</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54886,7 +54890,7 @@
         <v>46286</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54964,7 +54968,7 @@
         <v>46290</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55042,7 +55046,7 @@
         <v>46248</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55120,7 +55124,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55193,7 +55197,7 @@
         <v>45199</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55266,7 +55270,7 @@
         <v>46286</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55344,7 +55348,7 @@
         <v>45001</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55417,7 +55421,7 @@
         <v>46240</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55495,7 +55499,7 @@
         <v>46247</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55573,7 +55577,7 @@
         <v>46249</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55651,7 +55655,7 @@
         <v>46127</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55729,7 +55733,7 @@
         <v>44792</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55802,7 +55806,7 @@
         <v>46251</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55880,7 +55884,7 @@
         <v>46294</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55953,7 +55957,7 @@
         <v>45334</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56031,7 +56035,7 @@
         <v>45607</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56109,7 +56113,7 @@
         <v>44714</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56187,7 +56191,7 @@
         <v>44785</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56260,7 +56264,7 @@
         <v>44985</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56333,7 +56337,7 @@
         <v>46252</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56411,7 +56415,7 @@
         <v>46252</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56484,7 +56488,7 @@
         <v>46251</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56562,7 +56566,7 @@
         <v>46294</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56635,7 +56639,7 @@
         <v>45509</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56708,7 +56712,7 @@
         <v>45093</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56781,7 +56785,7 @@
         <v>45167</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56854,7 +56858,7 @@
         <v>46297</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56927,7 +56931,7 @@
         <v>45169</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57000,7 +57004,7 @@
         <v>44909</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57073,7 +57077,7 @@
         <v>45112</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57146,7 +57150,7 @@
         <v>45890</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57224,7 +57228,7 @@
         <v>45558</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57297,7 +57301,7 @@
         <v>46297</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57370,7 +57374,7 @@
         <v>45647</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57443,7 +57447,7 @@
         <v>46254</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57516,7 +57520,7 @@
         <v>46252</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57589,7 +57593,7 @@
         <v>45267</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57662,7 +57666,7 @@
         <v>45744</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57735,7 +57739,7 @@
         <v>45261</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57808,7 +57812,7 @@
         <v>45261</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57881,7 +57885,7 @@
         <v>44967</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57959,7 +57963,7 @@
         <v>44574</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58032,7 +58036,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58105,7 +58109,7 @@
         <v>45231</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58183,7 +58187,7 @@
         <v>45049</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58256,7 +58260,7 @@
         <v>45109</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58329,7 +58333,7 @@
         <v>45266</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58402,7 +58406,7 @@
         <v>45595</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58475,7 +58479,7 @@
         <v>45216</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58548,7 +58552,7 @@
         <v>45076</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58621,7 +58625,7 @@
         <v>45296</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58694,7 +58698,7 @@
         <v>44890</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58767,7 +58771,7 @@
         <v>45255</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58840,7 +58844,7 @@
         <v>45293</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58913,7 +58917,7 @@
         <v>45307</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58986,7 +58990,7 @@
         <v>45131</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59059,7 +59063,7 @@
         <v>44643</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59132,7 +59136,7 @@
         <v>44974</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59205,7 +59209,7 @@
         <v>45216</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59278,7 +59282,7 @@
         <v>45200</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59351,7 +59355,7 @@
         <v>45568</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59424,7 +59428,7 @@
         <v>45727</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59497,7 +59501,7 @@
         <v>44714</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59575,7 +59579,7 @@
         <v>45447</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59648,7 +59652,7 @@
         <v>45266</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59721,7 +59725,7 @@
         <v>45267</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59794,7 +59798,7 @@
         <v>44991</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59867,7 +59871,7 @@
         <v>44991</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59940,7 +59944,7 @@
         <v>45202</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60013,7 +60017,7 @@
         <v>45428</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60086,7 +60090,7 @@
         <v>45776</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60164,7 +60168,7 @@
         <v>45779</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60237,7 +60241,7 @@
         <v>45170</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60315,7 +60319,7 @@
         <v>45376</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60388,7 +60392,7 @@
         <v>45646</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60461,7 +60465,7 @@
         <v>45266</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60534,7 +60538,7 @@
         <v>45015</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60607,7 +60611,7 @@
         <v>45350</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60680,7 +60684,7 @@
         <v>45074</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60758,7 +60762,7 @@
         <v>44578</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60831,7 +60835,7 @@
         <v>45257</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60904,7 +60908,7 @@
         <v>45097</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60977,7 +60981,7 @@
         <v>45351</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61055,7 +61059,7 @@
         <v>44809</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61128,7 +61132,7 @@
         <v>45097</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61201,7 +61205,7 @@
         <v>45133</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61274,7 +61278,7 @@
         <v>44652</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61347,7 +61351,7 @@
         <v>45446</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61425,7 +61429,7 @@
         <v>45701</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61503,7 +61507,7 @@
         <v>45701</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61581,7 +61585,7 @@
         <v>45708</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61659,7 +61663,7 @@
         <v>45727</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61737,7 +61741,7 @@
         <v>45799</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61810,7 +61814,7 @@
         <v>45819</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61883,7 +61887,7 @@
         <v>45824</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61956,7 +61960,7 @@
         <v>45835</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62029,7 +62033,7 @@
         <v>45904</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62102,7 +62106,7 @@
         <v>45943</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62175,7 +62179,7 @@
         <v>45964</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62253,7 +62257,7 @@
         <v>46038</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62331,7 +62335,7 @@
         <v>46043</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62404,7 +62408,7 @@
         <v>46052</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62482,7 +62486,7 @@
         <v>44649</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62555,7 +62559,7 @@
         <v>46066</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62628,7 +62632,7 @@
         <v>46076</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62701,7 +62705,7 @@
         <v>46133</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62779,7 +62783,7 @@
         <v>46134</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1074,7 +1074,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1215,7 +1215,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1487,7 +1487,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1617,7 +1617,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1747,7 +1747,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1872,7 +1872,7 @@
         <v>46047</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1995,7 +1995,7 @@
         <v>45835</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2122,7 +2122,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2618,7 +2618,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2735,7 +2735,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2851,7 +2851,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3087,7 +3087,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3198,7 +3198,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3318,7 +3318,7 @@
         <v>45489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3428,7 +3428,7 @@
         <v>45896</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3551,7 +3551,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3665,7 +3665,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3885,7 +3885,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3994,7 +3994,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>45638</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4212,7 +4212,7 @@
         <v>44475</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>46166</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4434,7 +4434,7 @@
         <v>45835</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>45272</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>45931</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>45632</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4880,7 +4880,7 @@
         <v>44869</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>44477</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5099,7 +5099,7 @@
         <v>45901</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5215,7 +5215,7 @@
         <v>46097</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5326,7 +5326,7 @@
         <v>45637</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>46237</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5544,7 +5544,7 @@
         <v>44829</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5654,7 +5654,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5760,7 +5760,7 @@
         <v>46027</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45254</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5972,7 +5972,7 @@
         <v>45812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6078,7 +6078,7 @@
         <v>45251</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6184,7 +6184,7 @@
         <v>45996</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6290,7 +6290,7 @@
         <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6400,7 +6400,7 @@
         <v>45849</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6506,7 +6506,7 @@
         <v>45028</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6612,7 +6612,7 @@
         <v>45358</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6718,7 +6718,7 @@
         <v>45656</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6824,7 +6824,7 @@
         <v>45274</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6934,7 +6934,7 @@
         <v>46226</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>46283</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7271,7 +7271,7 @@
         <v>45251</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
         <v>44602</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44536</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7601,7 +7601,7 @@
         <v>44869</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7711,7 +7711,7 @@
         <v>44509</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44735</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7930,7 +7930,7 @@
         <v>44761</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45110</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8144,7 +8144,7 @@
         <v>45127</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8253,7 +8253,7 @@
         <v>45256</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>45690</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45793</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8572,7 +8572,7 @@
         <v>46041</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8677,7 +8677,7 @@
         <v>46069</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>45839</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8892,7 +8892,7 @@
         <v>45959</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45960</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9111,7 +9111,7 @@
         <v>45981</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>45621</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9321,7 +9321,7 @@
         <v>45228</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9430,7 +9430,7 @@
         <v>46120</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44588</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9640,7 +9640,7 @@
         <v>44909</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9854,7 +9854,7 @@
         <v>45016</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9959,7 +9959,7 @@
         <v>45294</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10068,7 +10068,7 @@
         <v>45061</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10173,7 +10173,7 @@
         <v>44918</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10278,7 +10278,7 @@
         <v>45638</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>46155</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>46202</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10610,7 +10610,7 @@
         <v>44750</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10724,7 +10724,7 @@
         <v>44973</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10829,7 +10829,7 @@
         <v>46287</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         <v>46244</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11044,7 +11044,7 @@
         <v>44992</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>45091</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11258,7 +11258,7 @@
         <v>45761</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>45005</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>45418</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45754</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45502</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11787,7 +11787,7 @@
         <v>45181</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>45996</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44782</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12075,7 +12075,7 @@
         <v>44491</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>44834</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12221,7 +12221,7 @@
         <v>44802</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44671</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>44872</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44512</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12523,7 +12523,7 @@
         <v>44869</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44570</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12674,7 +12674,7 @@
         <v>44670</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12747,7 +12747,7 @@
         <v>44488</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44877</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12966,7 +12966,7 @@
         <v>44529</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -13039,7 +13039,7 @@
         <v>44824</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44834</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>44693</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13258,7 +13258,7 @@
         <v>44503</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13331,7 +13331,7 @@
         <v>44533</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>44851</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13477,7 +13477,7 @@
         <v>44865</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13555,7 +13555,7 @@
         <v>44792</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13628,7 +13628,7 @@
         <v>44690</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13706,7 +13706,7 @@
         <v>44684</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13784,7 +13784,7 @@
         <v>44543</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13857,7 +13857,7 @@
         <v>44777</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44651</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>44862</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44533</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14149,7 +14149,7 @@
         <v>44797</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14222,7 +14222,7 @@
         <v>44719</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14295,7 +14295,7 @@
         <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14368,7 +14368,7 @@
         <v>45397</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14441,7 +14441,7 @@
         <v>45561</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>45098</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14587,7 +14587,7 @@
         <v>45219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14660,7 +14660,7 @@
         <v>45362</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45103</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14806,7 +14806,7 @@
         <v>44543</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45637</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14957,7 +14957,7 @@
         <v>45373</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -15030,7 +15030,7 @@
         <v>45425</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15103,7 +15103,7 @@
         <v>45266</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>45510</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15249,7 +15249,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15322,7 +15322,7 @@
         <v>44993</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15395,7 +15395,7 @@
         <v>45518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15468,7 +15468,7 @@
         <v>45257</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>45132</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15614,7 +15614,7 @@
         <v>45446</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15692,7 +15692,7 @@
         <v>44533</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>45208</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15843,7 +15843,7 @@
         <v>44929</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15921,7 +15921,7 @@
         <v>45455</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15999,7 +15999,7 @@
         <v>45127</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16072,7 +16072,7 @@
         <v>45261</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>45523</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16218,7 +16218,7 @@
         <v>45264</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16291,7 +16291,7 @@
         <v>45256</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16364,7 +16364,7 @@
         <v>45476</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>45608</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16510,7 +16510,7 @@
         <v>44711</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16588,7 +16588,7 @@
         <v>45787</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>45044</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>44915</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16807,7 +16807,7 @@
         <v>45302</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16880,7 +16880,7 @@
         <v>44978</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>45015</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45524</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17099,7 +17099,7 @@
         <v>45037</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17172,7 +17172,7 @@
         <v>45886</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17245,7 +17245,7 @@
         <v>46002</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>44546</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17391,7 +17391,7 @@
         <v>44546</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17464,7 +17464,7 @@
         <v>45518</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17537,7 +17537,7 @@
         <v>46006</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17610,7 +17610,7 @@
         <v>46006</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17683,7 +17683,7 @@
         <v>46006</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17756,7 +17756,7 @@
         <v>46006</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>46007</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17902,7 +17902,7 @@
         <v>46007</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45296</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -18048,7 +18048,7 @@
         <v>46010</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18121,7 +18121,7 @@
         <v>46010</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45790</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>46013</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18340,7 +18340,7 @@
         <v>45596</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45637</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18486,7 +18486,7 @@
         <v>46018</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18559,7 +18559,7 @@
         <v>46020</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18632,7 +18632,7 @@
         <v>45154</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18705,7 +18705,7 @@
         <v>44580</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18778,7 +18778,7 @@
         <v>46021</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18851,7 +18851,7 @@
         <v>45244</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18924,7 +18924,7 @@
         <v>46020</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18997,7 +18997,7 @@
         <v>45454</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19070,7 +19070,7 @@
         <v>46021</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19143,7 +19143,7 @@
         <v>45890</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45446</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19289,7 +19289,7 @@
         <v>45890</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19362,7 +19362,7 @@
         <v>46024</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19435,7 +19435,7 @@
         <v>45230</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19508,7 +19508,7 @@
         <v>46027</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>46029</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45574</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>46029</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19800,7 +19800,7 @@
         <v>46029</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19873,7 +19873,7 @@
         <v>44986</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19946,7 +19946,7 @@
         <v>45515</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -20019,7 +20019,7 @@
         <v>45790</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20092,7 +20092,7 @@
         <v>45901</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20170,7 +20170,7 @@
         <v>45898</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20248,7 +20248,7 @@
         <v>45898</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20326,7 +20326,7 @@
         <v>45568</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45898</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>46035</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20550,7 +20550,7 @@
         <v>45198</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20623,7 +20623,7 @@
         <v>45103</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>46027</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20774,7 +20774,7 @@
         <v>46035</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>44977</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45490</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20993,7 +20993,7 @@
         <v>45903</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21066,7 +21066,7 @@
         <v>45376</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21139,7 +21139,7 @@
         <v>45219</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45979</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>45103</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21363,7 +21363,7 @@
         <v>45980</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21436,7 +21436,7 @@
         <v>45497</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>46041</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21587,7 +21587,7 @@
         <v>46041</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21660,7 +21660,7 @@
         <v>45979</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21733,7 +21733,7 @@
         <v>45982</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21806,7 +21806,7 @@
         <v>46043</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21879,7 +21879,7 @@
         <v>46043</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45911</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>46043</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22098,7 +22098,7 @@
         <v>45911</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22171,7 +22171,7 @@
         <v>45911</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22244,7 +22244,7 @@
         <v>45261</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45796</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22390,7 +22390,7 @@
         <v>44971</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22463,7 +22463,7 @@
         <v>45912</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22541,7 +22541,7 @@
         <v>46045</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45912</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22687,7 +22687,7 @@
         <v>46044</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22760,7 +22760,7 @@
         <v>45915</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>46045</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>46044</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22979,7 +22979,7 @@
         <v>45912</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>46049</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23125,7 +23125,7 @@
         <v>45240</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23198,7 +23198,7 @@
         <v>45916</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23271,7 +23271,7 @@
         <v>46049</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23344,7 +23344,7 @@
         <v>45558</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23417,7 +23417,7 @@
         <v>45917</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>46051</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23563,7 +23563,7 @@
         <v>45919</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>46050</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23709,7 +23709,7 @@
         <v>45114</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>46029</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23855,7 +23855,7 @@
         <v>46055</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23928,7 +23928,7 @@
         <v>46052</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -24001,7 +24001,7 @@
         <v>45258</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24074,7 +24074,7 @@
         <v>46045</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24147,7 +24147,7 @@
         <v>45921</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24220,7 +24220,7 @@
         <v>45921</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45480</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>45924</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24439,7 +24439,7 @@
         <v>45397</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24512,7 +24512,7 @@
         <v>45925</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45925</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24658,7 +24658,7 @@
         <v>45260</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44966</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45183</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24877,7 +24877,7 @@
         <v>46056</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24950,7 +24950,7 @@
         <v>45261</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25023,7 +25023,7 @@
         <v>45520</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25096,7 +25096,7 @@
         <v>45929</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25169,7 +25169,7 @@
         <v>46044</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25242,7 +25242,7 @@
         <v>44867</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45537</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25388,7 +25388,7 @@
         <v>45667</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25461,7 +25461,7 @@
         <v>45932</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>45932</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>46007</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25690,7 +25690,7 @@
         <v>45860</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25763,7 +25763,7 @@
         <v>46035</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45797</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25909,7 +25909,7 @@
         <v>45934</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25982,7 +25982,7 @@
         <v>45630</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45630</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26128,7 +26128,7 @@
         <v>45939</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26206,7 +26206,7 @@
         <v>45110</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26279,7 +26279,7 @@
         <v>45979</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26352,7 +26352,7 @@
         <v>45937</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26425,7 +26425,7 @@
         <v>45797</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26498,7 +26498,7 @@
         <v>46071</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26571,7 +26571,7 @@
         <v>46070</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45937</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26717,7 +26717,7 @@
         <v>45001</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26790,7 +26790,7 @@
         <v>45015</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26863,7 +26863,7 @@
         <v>46070</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26936,7 +26936,7 @@
         <v>46070</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45232</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>46072</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27155,7 +27155,7 @@
         <v>46072</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27228,7 +27228,7 @@
         <v>45376</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>46072</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27374,7 +27374,7 @@
         <v>45027</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45944</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27520,7 +27520,7 @@
         <v>45946</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27593,7 +27593,7 @@
         <v>44731</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27666,7 +27666,7 @@
         <v>45951</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27744,7 +27744,7 @@
         <v>45695</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27817,7 +27817,7 @@
         <v>45259</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27890,7 +27890,7 @@
         <v>45151</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27963,7 +27963,7 @@
         <v>45951</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28041,7 +28041,7 @@
         <v>44987</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45952</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28187,7 +28187,7 @@
         <v>45812</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28265,7 +28265,7 @@
         <v>45955</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28338,7 +28338,7 @@
         <v>45813</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28411,7 +28411,7 @@
         <v>45958</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45961</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28557,7 +28557,7 @@
         <v>45961</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28630,7 +28630,7 @@
         <v>45960</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28703,7 +28703,7 @@
         <v>45961</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28776,7 +28776,7 @@
         <v>46092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28849,7 +28849,7 @@
         <v>45306</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28922,7 +28922,7 @@
         <v>45965</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -29000,7 +29000,7 @@
         <v>45964</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29073,7 +29073,7 @@
         <v>45964</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45964</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29219,7 +29219,7 @@
         <v>45964</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29292,7 +29292,7 @@
         <v>45965</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29365,7 +29365,7 @@
         <v>45677</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>44749</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29516,7 +29516,7 @@
         <v>45966</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>45966</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29662,7 +29662,7 @@
         <v>45966</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29735,7 +29735,7 @@
         <v>45966</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29808,7 +29808,7 @@
         <v>45966</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29881,7 +29881,7 @@
         <v>45966</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29954,7 +29954,7 @@
         <v>45817</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30027,7 +30027,7 @@
         <v>45971</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>46097</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30173,7 +30173,7 @@
         <v>46097</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30246,7 +30246,7 @@
         <v>46097</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30319,7 +30319,7 @@
         <v>45001</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>46063</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45510</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30538,7 +30538,7 @@
         <v>45624</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30611,7 +30611,7 @@
         <v>45972</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30684,7 +30684,7 @@
         <v>45425</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45351</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30830,7 +30830,7 @@
         <v>45349</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30903,7 +30903,7 @@
         <v>45975</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30981,7 +30981,7 @@
         <v>46101</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31054,7 +31054,7 @@
         <v>45974</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31127,7 +31127,7 @@
         <v>44837</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45974</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31273,7 +31273,7 @@
         <v>45061</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31346,7 +31346,7 @@
         <v>46106</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31424,7 +31424,7 @@
         <v>45574</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31497,7 +31497,7 @@
         <v>46106</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>45978</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31643,7 +31643,7 @@
         <v>45818</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31716,7 +31716,7 @@
         <v>45611</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31789,7 +31789,7 @@
         <v>45818</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31867,7 +31867,7 @@
         <v>45981</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>45966</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -32013,7 +32013,7 @@
         <v>45985</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32086,7 +32086,7 @@
         <v>45985</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32159,7 +32159,7 @@
         <v>45583</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32232,7 +32232,7 @@
         <v>45985</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32305,7 +32305,7 @@
         <v>45818</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>46112</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32456,7 +32456,7 @@
         <v>45985</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32529,7 +32529,7 @@
         <v>46111</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32607,7 +32607,7 @@
         <v>45567</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32680,7 +32680,7 @@
         <v>45036</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45820</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32826,7 +32826,7 @@
         <v>45982</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45618</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45631</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33045,7 +33045,7 @@
         <v>45986</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>46113</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33191,7 +33191,7 @@
         <v>45986</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33264,7 +33264,7 @@
         <v>44501</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33337,7 +33337,7 @@
         <v>45825</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45559</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33483,7 +33483,7 @@
         <v>45821</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33556,7 +33556,7 @@
         <v>45988</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33629,7 +33629,7 @@
         <v>45903</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33707,7 +33707,7 @@
         <v>45988</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33805,7 +33805,7 @@
         <v>46119</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33878,7 +33878,7 @@
         <v>45749</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33951,7 +33951,7 @@
         <v>44962</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -34024,7 +34024,7 @@
         <v>46121</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>45827</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34175,7 +34175,7 @@
         <v>44974</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34248,7 +34248,7 @@
         <v>44992</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45993</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>45995</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>45160</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34540,7 +34540,7 @@
         <v>45203</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34613,7 +34613,7 @@
         <v>45995</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34686,7 +34686,7 @@
         <v>45433</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34759,7 +34759,7 @@
         <v>45433</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34832,7 +34832,7 @@
         <v>46126</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45705</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34978,7 +34978,7 @@
         <v>44959</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35051,7 +35051,7 @@
         <v>46127</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45342</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>46127</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35280,7 +35280,7 @@
         <v>46128</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35358,7 +35358,7 @@
         <v>46127</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35436,7 +35436,7 @@
         <v>46001</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35509,7 +35509,7 @@
         <v>46114</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35587,7 +35587,7 @@
         <v>45104</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35660,7 +35660,7 @@
         <v>46132</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35733,7 +35733,7 @@
         <v>45113</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35806,7 +35806,7 @@
         <v>46114</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45114</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>45833</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -36030,7 +36030,7 @@
         <v>45832</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45453</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36176,7 +36176,7 @@
         <v>45553</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36254,7 +36254,7 @@
         <v>45408</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36327,7 +36327,7 @@
         <v>46133</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36400,7 +36400,7 @@
         <v>45195</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36473,7 +36473,7 @@
         <v>45085</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36546,7 +36546,7 @@
         <v>45726</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36619,7 +36619,7 @@
         <v>45835</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45839</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36765,7 +36765,7 @@
         <v>45334</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>44993</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>46035</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36984,7 +36984,7 @@
         <v>46139</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37057,7 +37057,7 @@
         <v>44951</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37130,7 +37130,7 @@
         <v>45567</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37203,7 +37203,7 @@
         <v>45707</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37276,7 +37276,7 @@
         <v>46106</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37349,7 +37349,7 @@
         <v>45104</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37427,7 +37427,7 @@
         <v>45751</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45803</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37573,7 +37573,7 @@
         <v>44820</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37646,7 +37646,7 @@
         <v>45474</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37719,7 +37719,7 @@
         <v>45782</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37792,7 +37792,7 @@
         <v>45670</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37865,7 +37865,7 @@
         <v>45847</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37938,7 +37938,7 @@
         <v>45834</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -38016,7 +38016,7 @@
         <v>45456</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38094,7 +38094,7 @@
         <v>44994</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>45849</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38245,7 +38245,7 @@
         <v>45561</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45849</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38401,7 +38401,7 @@
         <v>44978</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38474,7 +38474,7 @@
         <v>45197</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38547,7 +38547,7 @@
         <v>45732</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45509</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38693,7 +38693,7 @@
         <v>44902</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38766,7 +38766,7 @@
         <v>45555</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38839,7 +38839,7 @@
         <v>45351</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38912,7 +38912,7 @@
         <v>45125</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38990,7 +38990,7 @@
         <v>45308</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -39063,7 +39063,7 @@
         <v>45863</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39136,7 +39136,7 @@
         <v>45553</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39214,7 +39214,7 @@
         <v>45625</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39287,7 +39287,7 @@
         <v>46035</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39360,7 +39360,7 @@
         <v>44628</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39433,7 +39433,7 @@
         <v>45558</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39506,7 +39506,7 @@
         <v>46139</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39579,7 +39579,7 @@
         <v>45022</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39652,7 +39652,7 @@
         <v>45630</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39725,7 +39725,7 @@
         <v>45303</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39798,7 +39798,7 @@
         <v>46114</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39876,7 +39876,7 @@
         <v>45334</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39954,7 +39954,7 @@
         <v>44837</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -40027,7 +40027,7 @@
         <v>45317</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>45002</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40173,7 +40173,7 @@
         <v>45552</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40246,7 +40246,7 @@
         <v>45030</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40319,7 +40319,7 @@
         <v>45695</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40392,7 +40392,7 @@
         <v>45863</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>45958</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40543,7 +40543,7 @@
         <v>45490</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>44959</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40689,7 +40689,7 @@
         <v>45418</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40762,7 +40762,7 @@
         <v>45863</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40835,7 +40835,7 @@
         <v>46064</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40908,7 +40908,7 @@
         <v>45706</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40981,7 +40981,7 @@
         <v>45567</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41054,7 +41054,7 @@
         <v>44998</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41127,7 +41127,7 @@
         <v>44998</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41200,7 +41200,7 @@
         <v>46140</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41273,7 +41273,7 @@
         <v>45621</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41346,7 +41346,7 @@
         <v>45478</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41419,7 +41419,7 @@
         <v>45624</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41492,7 +41492,7 @@
         <v>46030</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41565,7 +41565,7 @@
         <v>45406</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>46036</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41716,7 +41716,7 @@
         <v>44992</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41789,7 +41789,7 @@
         <v>45103</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41862,7 +41862,7 @@
         <v>45429</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41935,7 +41935,7 @@
         <v>45618</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -42008,7 +42008,7 @@
         <v>45554</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42086,7 +42086,7 @@
         <v>45167</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42159,7 +42159,7 @@
         <v>46146</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42232,7 +42232,7 @@
         <v>44974</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42305,7 +42305,7 @@
         <v>44974</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>45675</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>46147</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42524,7 +42524,7 @@
         <v>46149</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42597,7 +42597,7 @@
         <v>46119</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42670,7 +42670,7 @@
         <v>46149</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42748,7 +42748,7 @@
         <v>46148</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42826,7 +42826,7 @@
         <v>46149</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45877</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42977,7 +42977,7 @@
         <v>45131</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45112</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43123,7 +43123,7 @@
         <v>46038</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43196,7 +43196,7 @@
         <v>45121</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43269,7 +43269,7 @@
         <v>46092</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43342,7 +43342,7 @@
         <v>45835</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43415,7 +43415,7 @@
         <v>45365</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45896</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43561,7 +43561,7 @@
         <v>46155</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43639,7 +43639,7 @@
         <v>46155</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>46043</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43790,7 +43790,7 @@
         <v>46052</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43863,7 +43863,7 @@
         <v>45994</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43936,7 +43936,7 @@
         <v>45027</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -44009,7 +44009,7 @@
         <v>46044</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44082,7 +44082,7 @@
         <v>45257</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44160,7 +44160,7 @@
         <v>46156</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45165</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44306,7 +44306,7 @@
         <v>46156</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44379,7 +44379,7 @@
         <v>45610</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44452,7 +44452,7 @@
         <v>45397</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44525,7 +44525,7 @@
         <v>45621</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44598,7 +44598,7 @@
         <v>45454</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45169</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44744,7 +44744,7 @@
         <v>46162</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44817,7 +44817,7 @@
         <v>45727</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44890,7 +44890,7 @@
         <v>45180</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44963,7 +44963,7 @@
         <v>46167</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>46168</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45109,7 +45109,7 @@
         <v>45621</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45182,7 +45182,7 @@
         <v>46168</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45255,7 +45255,7 @@
         <v>45446</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45333,7 +45333,7 @@
         <v>45910</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45406,7 +45406,7 @@
         <v>45623</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45695</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>45113</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45625,7 +45625,7 @@
         <v>46170</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45698,7 +45698,7 @@
         <v>45127</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45771,7 +45771,7 @@
         <v>45127</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45844,7 +45844,7 @@
         <v>45160</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45917,7 +45917,7 @@
         <v>46171</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45995,7 +45995,7 @@
         <v>45881</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46068,7 +46068,7 @@
         <v>45127</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46141,7 +46141,7 @@
         <v>44474</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46214,7 +46214,7 @@
         <v>45428</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45664</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>46174</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46433,7 +46433,7 @@
         <v>45882</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45608</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46579,7 +46579,7 @@
         <v>46176</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46657,7 +46657,7 @@
         <v>45667</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46730,7 +46730,7 @@
         <v>45884</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46803,7 +46803,7 @@
         <v>45198</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46876,7 +46876,7 @@
         <v>45625</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>44912</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>46035</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47095,7 +47095,7 @@
         <v>45747</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47168,7 +47168,7 @@
         <v>46127</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47241,7 +47241,7 @@
         <v>45068</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47314,7 +47314,7 @@
         <v>46182</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47387,7 +47387,7 @@
         <v>46182</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47460,7 +47460,7 @@
         <v>46181</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47538,7 +47538,7 @@
         <v>44746</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>44917</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47684,7 +47684,7 @@
         <v>46185</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47762,7 +47762,7 @@
         <v>44909</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47835,7 +47835,7 @@
         <v>45282</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47908,7 +47908,7 @@
         <v>46188</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47981,7 +47981,7 @@
         <v>45257</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48054,7 +48054,7 @@
         <v>45526</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48127,7 +48127,7 @@
         <v>46190</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48205,7 +48205,7 @@
         <v>45369</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48278,7 +48278,7 @@
         <v>45027</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48351,7 +48351,7 @@
         <v>46191</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>46191</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48502,7 +48502,7 @@
         <v>45197</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48575,7 +48575,7 @@
         <v>46191</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48648,7 +48648,7 @@
         <v>45608</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>46196</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48794,7 +48794,7 @@
         <v>45741</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>46197</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48940,7 +48940,7 @@
         <v>46197</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49018,7 +49018,7 @@
         <v>46197</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49096,7 +49096,7 @@
         <v>45280</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49169,7 +49169,7 @@
         <v>46202</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49242,7 +49242,7 @@
         <v>44875</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49315,7 +49315,7 @@
         <v>44992</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49388,7 +49388,7 @@
         <v>44929</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45169</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45275</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49612,7 +49612,7 @@
         <v>45252</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49685,7 +49685,7 @@
         <v>45219</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49758,7 +49758,7 @@
         <v>45609</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49831,7 +49831,7 @@
         <v>45176</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49904,7 +49904,7 @@
         <v>46024</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49977,7 +49977,7 @@
         <v>45097</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50050,7 +50050,7 @@
         <v>45595</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>46211</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50196,7 +50196,7 @@
         <v>46211</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50269,7 +50269,7 @@
         <v>45034</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50342,7 +50342,7 @@
         <v>46259</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50415,7 +50415,7 @@
         <v>46216</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50493,7 +50493,7 @@
         <v>44846</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50566,7 +50566,7 @@
         <v>46259</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>46259</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50717,7 +50717,7 @@
         <v>46259</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50790,7 +50790,7 @@
         <v>46202</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50868,7 +50868,7 @@
         <v>45049</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50941,7 +50941,7 @@
         <v>44869</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45357</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>45264</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51165,7 +51165,7 @@
         <v>45110</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51238,7 +51238,7 @@
         <v>45152</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51311,7 +51311,7 @@
         <v>45061</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51384,7 +51384,7 @@
         <v>44918</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51457,7 +51457,7 @@
         <v>46268</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51530,7 +51530,7 @@
         <v>45509</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51603,7 +51603,7 @@
         <v>46177</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51681,7 +51681,7 @@
         <v>45096</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51754,7 +51754,7 @@
         <v>46177</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51832,7 +51832,7 @@
         <v>45378</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45415</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51978,7 +51978,7 @@
         <v>45553</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52056,7 +52056,7 @@
         <v>46167</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52134,7 +52134,7 @@
         <v>46276</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52207,7 +52207,7 @@
         <v>46233</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52285,7 +52285,7 @@
         <v>45152</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52358,7 +52358,7 @@
         <v>46233</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52436,7 +52436,7 @@
         <v>45050</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52509,7 +52509,7 @@
         <v>45203</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52582,7 +52582,7 @@
         <v>45567</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52660,7 +52660,7 @@
         <v>46281</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52733,7 +52733,7 @@
         <v>45231</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52806,7 +52806,7 @@
         <v>46238</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52884,7 +52884,7 @@
         <v>45272</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52957,7 +52957,7 @@
         <v>44679</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -53035,7 +53035,7 @@
         <v>45345</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53108,7 +53108,7 @@
         <v>46154</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53186,7 +53186,7 @@
         <v>45323</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53259,7 +53259,7 @@
         <v>46241</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53337,7 +53337,7 @@
         <v>45467</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53410,7 +53410,7 @@
         <v>45559</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53483,7 +53483,7 @@
         <v>46241</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53561,7 +53561,7 @@
         <v>45756</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53634,7 +53634,7 @@
         <v>45004</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53707,7 +53707,7 @@
         <v>45035</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53780,7 +53780,7 @@
         <v>46287</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53858,7 +53858,7 @@
         <v>45201</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53931,7 +53931,7 @@
         <v>45727</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -54009,7 +54009,7 @@
         <v>46288</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54082,7 +54082,7 @@
         <v>46289</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54155,7 +54155,7 @@
         <v>44987</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54228,7 +54228,7 @@
         <v>46246</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54301,7 +54301,7 @@
         <v>45314</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54374,7 +54374,7 @@
         <v>45314</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54447,7 +54447,7 @@
         <v>46293</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54520,7 +54520,7 @@
         <v>46293</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54593,7 +54593,7 @@
         <v>45544</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54666,7 +54666,7 @@
         <v>46135</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54744,7 +54744,7 @@
         <v>46293</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54817,7 +54817,7 @@
         <v>46293</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54890,7 +54890,7 @@
         <v>46286</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54968,7 +54968,7 @@
         <v>46290</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55046,7 +55046,7 @@
         <v>46248</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55124,7 +55124,7 @@
         <v>46290</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55197,7 +55197,7 @@
         <v>45199</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55270,7 +55270,7 @@
         <v>46286</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55348,7 +55348,7 @@
         <v>45001</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55421,7 +55421,7 @@
         <v>46240</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55499,7 +55499,7 @@
         <v>46247</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55577,7 +55577,7 @@
         <v>46249</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55655,7 +55655,7 @@
         <v>46127</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55733,7 +55733,7 @@
         <v>44792</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55806,7 +55806,7 @@
         <v>46251</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55884,7 +55884,7 @@
         <v>46294</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55957,7 +55957,7 @@
         <v>45334</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -56035,7 +56035,7 @@
         <v>45607</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56113,7 +56113,7 @@
         <v>44714</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56191,7 +56191,7 @@
         <v>44785</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56264,7 +56264,7 @@
         <v>44985</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56337,7 +56337,7 @@
         <v>46252</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56415,7 +56415,7 @@
         <v>46252</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56488,7 +56488,7 @@
         <v>46251</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56566,7 +56566,7 @@
         <v>46294</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56639,7 +56639,7 @@
         <v>45509</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56712,7 +56712,7 @@
         <v>45093</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56785,7 +56785,7 @@
         <v>45167</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56858,7 +56858,7 @@
         <v>46297</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56931,7 +56931,7 @@
         <v>45169</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -57004,7 +57004,7 @@
         <v>44909</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -57077,7 +57077,7 @@
         <v>45112</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57150,7 +57150,7 @@
         <v>45890</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57228,7 +57228,7 @@
         <v>45558</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57301,7 +57301,7 @@
         <v>46297</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57374,7 +57374,7 @@
         <v>45647</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57447,7 +57447,7 @@
         <v>46254</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57520,7 +57520,7 @@
         <v>46252</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57593,7 +57593,7 @@
         <v>45267</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57666,7 +57666,7 @@
         <v>45744</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57739,7 +57739,7 @@
         <v>45261</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57812,7 +57812,7 @@
         <v>45261</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57885,7 +57885,7 @@
         <v>44967</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57963,7 +57963,7 @@
         <v>44574</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -58036,7 +58036,7 @@
         <v>45244</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58109,7 +58109,7 @@
         <v>45231</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58187,7 +58187,7 @@
         <v>45049</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58260,7 +58260,7 @@
         <v>45109</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58333,7 +58333,7 @@
         <v>45266</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58406,7 +58406,7 @@
         <v>45595</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58479,7 +58479,7 @@
         <v>45216</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58552,7 +58552,7 @@
         <v>45076</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58625,7 +58625,7 @@
         <v>45296</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58698,7 +58698,7 @@
         <v>44890</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58771,7 +58771,7 @@
         <v>45255</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58844,7 +58844,7 @@
         <v>45293</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58917,7 +58917,7 @@
         <v>45307</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58990,7 +58990,7 @@
         <v>45131</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -59063,7 +59063,7 @@
         <v>44643</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59136,7 +59136,7 @@
         <v>44974</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59209,7 +59209,7 @@
         <v>45216</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59282,7 +59282,7 @@
         <v>45200</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59355,7 +59355,7 @@
         <v>45568</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59428,7 +59428,7 @@
         <v>45727</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59501,7 +59501,7 @@
         <v>44714</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59579,7 +59579,7 @@
         <v>45447</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59652,7 +59652,7 @@
         <v>45266</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59725,7 +59725,7 @@
         <v>45267</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59798,7 +59798,7 @@
         <v>44991</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59871,7 +59871,7 @@
         <v>44991</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59944,7 +59944,7 @@
         <v>45202</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -60017,7 +60017,7 @@
         <v>45428</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60090,7 +60090,7 @@
         <v>45776</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60168,7 +60168,7 @@
         <v>45779</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60241,7 +60241,7 @@
         <v>45170</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60319,7 +60319,7 @@
         <v>45376</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60392,7 +60392,7 @@
         <v>45646</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60465,7 +60465,7 @@
         <v>45266</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60538,7 +60538,7 @@
         <v>45015</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45350</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60684,7 +60684,7 @@
         <v>45074</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60762,7 +60762,7 @@
         <v>44578</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60835,7 +60835,7 @@
         <v>45257</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60908,7 +60908,7 @@
         <v>45097</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60981,7 +60981,7 @@
         <v>45351</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61059,7 +61059,7 @@
         <v>44809</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61132,7 +61132,7 @@
         <v>45097</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61205,7 +61205,7 @@
         <v>45133</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61278,7 +61278,7 @@
         <v>44652</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61351,7 +61351,7 @@
         <v>45446</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61429,7 +61429,7 @@
         <v>45701</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>45701</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61585,7 +61585,7 @@
         <v>45708</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61663,7 +61663,7 @@
         <v>45727</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61741,7 +61741,7 @@
         <v>45799</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61814,7 +61814,7 @@
         <v>45819</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61887,7 +61887,7 @@
         <v>45824</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61960,7 +61960,7 @@
         <v>45835</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -62033,7 +62033,7 @@
         <v>45904</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62106,7 +62106,7 @@
         <v>45943</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62179,7 +62179,7 @@
         <v>45964</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62257,7 +62257,7 @@
         <v>46038</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62335,7 +62335,7 @@
         <v>46043</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62408,7 +62408,7 @@
         <v>46052</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62486,7 +62486,7 @@
         <v>44649</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
@@ -62559,7 +62559,7 @@
         <v>46066</v>
       </c>
       <c r="E787" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
@@ -62632,7 +62632,7 @@
         <v>46076</v>
       </c>
       <c r="E788" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
@@ -62705,7 +62705,7 @@
         <v>46133</v>
       </c>
       <c r="E789" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>46134</v>
       </c>
       <c r="E790" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>5.9</v>
       </c>
       <c r="J5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
         <v>7</v>
@@ -1118,13 +1118,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T5" t="n">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="U5" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1147,7 +1147,6 @@
 Vedticka
 Gråspett
 Kransmossa
-Kärrviol
 Linnea
 Spillkråka
 Sälg
@@ -1155,7 +1154,6 @@
 Tofsmes
 Kungsfågel
 Vanlig groda
-Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1216,7 +1214,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1232,7 +1230,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
@@ -1259,13 +1257,13 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="T6" t="n">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="U6" t="n">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1288,7 +1286,6 @@
 Vedticka
 Gråspett
 Kransmossa
-Kärrviol
 Linnea
 Spillkråka
 Sälg
@@ -1296,7 +1293,6 @@
 Tofsmes
 Kungsfågel
 Vanlig groda
-Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1357,7 +1353,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1484,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1618,7 +1614,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1744,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1869,7 @@
         <v>45835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2000,7 +1996,7 @@
         <v>46047</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2123,7 +2119,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2249,7 +2245,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2374,7 +2370,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2497,7 +2493,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2619,7 +2615,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2736,7 +2732,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2852,7 +2848,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2972,7 +2968,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3088,7 +3084,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3199,7 +3195,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3319,7 +3315,7 @@
         <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3429,7 +3425,7 @@
         <v>45489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3539,7 +3535,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3662,7 +3658,7 @@
         <v>45614</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3776,7 +3772,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3886,7 +3882,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3995,7 +3991,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4104,7 +4100,7 @@
         <v>45638</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4213,7 +4209,7 @@
         <v>46166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4326,7 +4322,7 @@
         <v>45835</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4443,7 +4439,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4556,7 +4552,7 @@
         <v>45931</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4664,7 +4660,7 @@
         <v>45632</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4772,7 +4768,7 @@
         <v>44869</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4884,7 +4880,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5000,7 +4996,7 @@
         <v>45637</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5107,7 +5103,7 @@
         <v>46097</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5218,7 +5214,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5329,7 +5325,7 @@
         <v>45254</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5435,7 +5431,7 @@
         <v>44829</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5545,7 +5541,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5647,7 @@
         <v>45274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5761,7 +5757,7 @@
         <v>45890</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5867,7 +5863,7 @@
         <v>45656</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5973,7 +5969,7 @@
         <v>45358</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6079,7 +6075,7 @@
         <v>44602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6194,7 +6190,7 @@
         <v>45812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6300,7 +6296,7 @@
         <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6410,7 +6406,7 @@
         <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6520,7 +6516,7 @@
         <v>45849</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6626,7 +6622,7 @@
         <v>45028</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6732,7 +6728,7 @@
         <v>45996</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6838,7 +6834,7 @@
         <v>46027</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6944,7 +6940,7 @@
         <v>46226</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7055,7 +7051,7 @@
         <v>46283</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7166,7 +7162,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7281,7 +7277,7 @@
         <v>44536</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7386,7 +7382,7 @@
         <v>44869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7496,7 +7492,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7610,7 +7606,7 @@
         <v>44735</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7715,7 +7711,7 @@
         <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7820,7 +7816,7 @@
         <v>44761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7929,7 +7925,7 @@
         <v>45418</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8034,7 +8030,7 @@
         <v>44992</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8143,7 +8139,7 @@
         <v>45016</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8248,7 +8244,7 @@
         <v>44973</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8353,7 +8349,7 @@
         <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8458,7 +8454,7 @@
         <v>45761</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8563,7 +8559,7 @@
         <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8668,7 +8664,7 @@
         <v>45127</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8777,7 +8773,7 @@
         <v>45256</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8882,7 +8878,7 @@
         <v>45793</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8987,7 +8983,7 @@
         <v>44588</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9092,7 +9088,7 @@
         <v>45621</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9197,7 +9193,7 @@
         <v>44750</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9311,7 +9307,7 @@
         <v>45638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9420,7 +9416,7 @@
         <v>45839</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9530,7 +9526,7 @@
         <v>45959</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9639,7 +9635,7 @@
         <v>45960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9749,7 +9745,7 @@
         <v>44918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9854,7 +9850,7 @@
         <v>45690</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9963,7 +9959,7 @@
         <v>45061</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10068,7 +10064,7 @@
         <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10173,7 +10169,7 @@
         <v>45981</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10278,7 +10274,7 @@
         <v>45228</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10387,7 +10383,7 @@
         <v>46120</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10492,7 +10488,7 @@
         <v>44909</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10601,7 +10597,7 @@
         <v>45294</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10710,7 +10706,7 @@
         <v>45005</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10819,7 +10815,7 @@
         <v>46041</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10924,7 +10920,7 @@
         <v>45110</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11029,7 +11025,7 @@
         <v>46069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11134,7 +11130,7 @@
         <v>46155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11248,7 +11244,7 @@
         <v>46202</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11357,7 +11353,7 @@
         <v>46287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11467,7 +11463,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11572,7 +11568,7 @@
         <v>45181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11677,7 +11673,7 @@
         <v>45996</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11787,7 +11783,7 @@
         <v>44782</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11860,7 +11856,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11933,7 +11929,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12006,7 +12002,7 @@
         <v>44802</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12084,7 +12080,7 @@
         <v>44671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12157,7 +12153,7 @@
         <v>44872</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12235,7 +12231,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12308,7 +12304,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12386,7 +12382,7 @@
         <v>44570</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12459,7 +12455,7 @@
         <v>44670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12532,7 +12528,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12605,7 +12601,7 @@
         <v>44877</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12678,7 +12674,7 @@
         <v>44824</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12751,7 +12747,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12824,7 +12820,7 @@
         <v>44539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12897,7 +12893,7 @@
         <v>44865</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12975,7 +12971,7 @@
         <v>44693</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13048,7 +13044,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13121,7 +13117,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13194,7 +13190,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13267,7 +13263,7 @@
         <v>44690</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13345,7 +13341,7 @@
         <v>44777</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13418,7 +13414,7 @@
         <v>44651</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13491,7 +13487,7 @@
         <v>44851</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13564,7 +13560,7 @@
         <v>44684</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13642,7 +13638,7 @@
         <v>44529</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13715,7 +13711,7 @@
         <v>44543</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13788,7 +13784,7 @@
         <v>44862</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13861,7 +13857,7 @@
         <v>44797</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13934,7 +13930,7 @@
         <v>44533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14007,7 +14003,7 @@
         <v>45378</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14080,7 +14076,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14153,7 +14149,7 @@
         <v>44875</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14226,7 +14222,7 @@
         <v>45342</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14304,7 +14300,7 @@
         <v>45667</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14377,7 +14373,7 @@
         <v>45306</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14450,7 +14446,7 @@
         <v>45467</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14523,7 +14519,7 @@
         <v>45397</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14596,7 +14592,7 @@
         <v>44543</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14674,7 +14670,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14752,7 +14748,7 @@
         <v>45208</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14830,7 +14826,7 @@
         <v>45085</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14903,7 +14899,7 @@
         <v>45293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14976,7 +14972,7 @@
         <v>44929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15054,7 +15050,7 @@
         <v>45154</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15127,7 +15123,7 @@
         <v>45454</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15200,7 +15196,7 @@
         <v>44867</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15273,7 +15269,7 @@
         <v>45050</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15346,7 +15342,7 @@
         <v>45518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15419,7 +15415,7 @@
         <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15492,7 +15488,7 @@
         <v>44912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15565,7 +15561,7 @@
         <v>45749</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15638,7 +15634,7 @@
         <v>44992</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15711,7 +15707,7 @@
         <v>45022</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15784,7 +15780,7 @@
         <v>45433</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15857,7 +15853,7 @@
         <v>45433</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15930,7 +15926,7 @@
         <v>45455</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16008,7 +16004,7 @@
         <v>45103</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16081,7 +16077,7 @@
         <v>44915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16154,7 +16150,7 @@
         <v>45061</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16227,7 +16223,7 @@
         <v>45302</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16300,7 +16296,7 @@
         <v>44746</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16373,7 +16369,7 @@
         <v>45611</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16446,7 +16442,7 @@
         <v>44890</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16519,7 +16515,7 @@
         <v>45677</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16592,7 +16588,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16665,7 +16661,7 @@
         <v>45756</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16738,7 +16734,7 @@
         <v>44909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16811,7 +16807,7 @@
         <v>45334</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16889,7 +16885,7 @@
         <v>45231</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16962,7 +16958,7 @@
         <v>45296</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17035,7 +17031,7 @@
         <v>45255</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17108,7 +17104,7 @@
         <v>45113</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17181,7 +17177,7 @@
         <v>45103</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17259,7 +17255,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17332,7 +17328,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17410,7 +17406,7 @@
         <v>45561</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17483,7 +17479,7 @@
         <v>45518</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17556,7 +17552,7 @@
         <v>45558</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17629,7 +17625,7 @@
         <v>45454</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17702,7 +17698,7 @@
         <v>45151</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17775,7 +17771,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17848,7 +17844,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17921,7 +17917,7 @@
         <v>44993</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17994,7 +17990,7 @@
         <v>44962</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18067,7 +18063,7 @@
         <v>45334</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18140,7 +18136,7 @@
         <v>45167</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18213,7 +18209,7 @@
         <v>45567</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18286,7 +18282,7 @@
         <v>44837</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18359,7 +18355,7 @@
         <v>44837</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18432,7 +18428,7 @@
         <v>45345</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18505,7 +18501,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18578,7 +18574,7 @@
         <v>45280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18651,7 +18647,7 @@
         <v>45260</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18724,7 +18720,7 @@
         <v>45231</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18802,7 +18798,7 @@
         <v>45554</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18880,7 +18876,7 @@
         <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18953,7 +18949,7 @@
         <v>45258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19026,7 +19022,7 @@
         <v>45376</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19099,7 +19095,7 @@
         <v>45428</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19172,7 +19168,7 @@
         <v>45267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19245,7 +19241,7 @@
         <v>44711</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19323,7 +19319,7 @@
         <v>45490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19396,7 +19392,7 @@
         <v>45446</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19474,7 +19470,7 @@
         <v>45453</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19547,7 +19543,7 @@
         <v>45515</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19620,7 +19616,7 @@
         <v>44959</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19693,7 +19689,7 @@
         <v>45323</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19766,7 +19762,7 @@
         <v>44546</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19839,7 +19835,7 @@
         <v>44546</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19912,7 +19908,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19985,7 +19981,7 @@
         <v>45647</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20058,7 +20054,7 @@
         <v>45618</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20131,7 +20127,7 @@
         <v>45261</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20204,7 +20200,7 @@
         <v>45884</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20277,7 +20273,7 @@
         <v>45408</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20350,7 +20346,7 @@
         <v>45526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20423,7 +20419,7 @@
         <v>45447</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20496,7 +20492,7 @@
         <v>45219</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20569,7 +20565,7 @@
         <v>45195</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20642,7 +20638,7 @@
         <v>45559</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20715,7 +20711,7 @@
         <v>45152</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20788,7 +20784,7 @@
         <v>45886</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20861,7 +20857,7 @@
         <v>45296</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20934,7 +20930,7 @@
         <v>44951</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21007,7 +21003,7 @@
         <v>44719</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21080,7 +21076,7 @@
         <v>45497</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21158,7 +21154,7 @@
         <v>44994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21231,7 +21227,7 @@
         <v>45004</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21304,7 +21300,7 @@
         <v>45334</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21382,7 +21378,7 @@
         <v>45049</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21455,7 +21451,7 @@
         <v>45553</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21533,7 +21529,7 @@
         <v>45376</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21606,7 +21602,7 @@
         <v>45890</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21679,7 +21675,7 @@
         <v>45890</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21752,7 +21748,7 @@
         <v>45509</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21825,7 +21821,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21903,7 +21899,7 @@
         <v>45898</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21981,7 +21977,7 @@
         <v>45898</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22059,7 +22055,7 @@
         <v>45726</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22132,7 +22128,7 @@
         <v>44929</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22210,7 +22206,7 @@
         <v>45558</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22283,7 +22279,7 @@
         <v>45103</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22361,7 +22357,7 @@
         <v>45706</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22434,7 +22430,7 @@
         <v>45901</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22512,7 +22508,7 @@
         <v>45034</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22585,7 +22581,7 @@
         <v>45097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22658,7 +22654,7 @@
         <v>45110</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22731,7 +22727,7 @@
         <v>45544</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22804,7 +22800,7 @@
         <v>45631</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22877,7 +22873,7 @@
         <v>45695</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22950,7 +22946,7 @@
         <v>45695</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23023,7 +23019,7 @@
         <v>45425</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23096,7 +23092,7 @@
         <v>45425</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23169,7 +23165,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23242,7 +23238,7 @@
         <v>44992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23315,7 +23311,7 @@
         <v>45317</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23388,7 +23384,7 @@
         <v>45727</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23461,7 +23457,7 @@
         <v>45068</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23534,7 +23530,7 @@
         <v>45093</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23607,7 +23603,7 @@
         <v>45903</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23680,7 +23676,7 @@
         <v>44978</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23753,7 +23749,7 @@
         <v>45275</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23826,7 +23822,7 @@
         <v>45429</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23899,7 +23895,7 @@
         <v>45349</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23972,7 +23968,7 @@
         <v>44986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24045,7 +24041,7 @@
         <v>45595</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24118,7 +24114,7 @@
         <v>45096</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24191,7 +24187,7 @@
         <v>45776</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24269,7 +24265,7 @@
         <v>45912</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24347,7 +24343,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24420,7 +24416,7 @@
         <v>45911</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24493,7 +24489,7 @@
         <v>45912</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24566,7 +24562,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24639,7 +24635,7 @@
         <v>45779</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24712,7 +24708,7 @@
         <v>45476</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24785,7 +24781,7 @@
         <v>45049</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24858,7 +24854,7 @@
         <v>45911</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24931,7 +24927,7 @@
         <v>45916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25004,7 +25000,7 @@
         <v>45376</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25077,7 +25073,7 @@
         <v>45027</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25150,7 +25146,7 @@
         <v>45202</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25223,7 +25219,7 @@
         <v>45915</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25296,7 +25292,7 @@
         <v>45170</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25374,7 +25370,7 @@
         <v>45357</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25447,7 +25443,7 @@
         <v>45216</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25520,7 +25516,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25593,7 +25589,7 @@
         <v>44580</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25666,7 +25662,7 @@
         <v>44917</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25739,7 +25735,7 @@
         <v>45480</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25812,7 +25808,7 @@
         <v>45595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25885,7 +25881,7 @@
         <v>45266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25958,7 +25954,7 @@
         <v>45646</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26031,7 +26027,7 @@
         <v>44959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26104,7 +26100,7 @@
         <v>45098</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26177,7 +26173,7 @@
         <v>45917</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26250,7 +26246,7 @@
         <v>45741</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26323,7 +26319,7 @@
         <v>45919</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26396,7 +26392,7 @@
         <v>45524</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26469,7 +26465,7 @@
         <v>45350</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26542,7 +26538,7 @@
         <v>45921</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26615,7 +26611,7 @@
         <v>45510</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26688,7 +26684,7 @@
         <v>45921</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26761,7 +26757,7 @@
         <v>45002</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26834,7 +26830,7 @@
         <v>44966</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26907,7 +26903,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26980,7 +26976,7 @@
         <v>45924</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27053,7 +27049,7 @@
         <v>45787</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27126,7 +27122,7 @@
         <v>45790</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27199,7 +27195,7 @@
         <v>45925</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27272,7 +27268,7 @@
         <v>45103</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27345,7 +27341,7 @@
         <v>45925</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27418,7 +27414,7 @@
         <v>45790</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27491,7 +27487,7 @@
         <v>45609</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27564,7 +27560,7 @@
         <v>45574</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27637,7 +27633,7 @@
         <v>45675</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27710,7 +27706,7 @@
         <v>45596</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27783,7 +27779,7 @@
         <v>45929</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27856,7 +27852,7 @@
         <v>45001</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27929,7 +27925,7 @@
         <v>45428</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28002,7 +27998,7 @@
         <v>45001</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28075,7 +28071,7 @@
         <v>44971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28148,7 +28144,7 @@
         <v>45362</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28221,7 +28217,7 @@
         <v>45152</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28294,7 +28290,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28367,7 +28363,7 @@
         <v>45553</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28445,7 +28441,7 @@
         <v>45796</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28518,7 +28514,7 @@
         <v>45240</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28591,7 +28587,7 @@
         <v>45932</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28669,7 +28665,7 @@
         <v>45932</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28747,7 +28743,7 @@
         <v>45583</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28820,7 +28816,7 @@
         <v>45608</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28893,7 +28889,7 @@
         <v>45509</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28966,7 +28962,7 @@
         <v>44974</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29039,7 +29035,7 @@
         <v>45608</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29112,7 +29108,7 @@
         <v>44974</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29185,7 +29181,7 @@
         <v>44643</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29258,7 +29254,7 @@
         <v>45558</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29331,7 +29327,7 @@
         <v>45727</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29404,7 +29400,7 @@
         <v>45934</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29477,7 +29473,7 @@
         <v>45198</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29550,7 +29546,7 @@
         <v>45630</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29623,7 +29619,7 @@
         <v>45630</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29696,7 +29692,7 @@
         <v>45397</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29769,7 +29765,7 @@
         <v>45169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29842,7 +29838,7 @@
         <v>45114</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29915,7 +29911,7 @@
         <v>45198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29988,7 +29984,7 @@
         <v>45165</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30061,7 +30057,7 @@
         <v>45937</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30134,7 +30130,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30207,7 +30203,7 @@
         <v>45937</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30280,7 +30276,7 @@
         <v>45574</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30353,7 +30349,7 @@
         <v>45608</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30426,7 +30422,7 @@
         <v>45200</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30499,7 +30495,7 @@
         <v>45169</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30572,7 +30568,7 @@
         <v>44998</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30645,7 +30641,7 @@
         <v>45667</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30718,7 +30714,7 @@
         <v>44731</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30791,7 +30787,7 @@
         <v>45559</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30864,7 +30860,7 @@
         <v>45180</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30937,7 +30933,7 @@
         <v>45623</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31010,7 +31006,7 @@
         <v>45939</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31088,7 +31084,7 @@
         <v>45944</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31161,7 +31157,7 @@
         <v>45812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31239,7 +31235,7 @@
         <v>45946</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31312,7 +31308,7 @@
         <v>45751</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31385,7 +31381,7 @@
         <v>45607</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31463,7 +31459,7 @@
         <v>45813</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31536,7 +31532,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31609,7 +31605,7 @@
         <v>45351</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31682,7 +31678,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31760,7 +31756,7 @@
         <v>45244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31833,7 +31829,7 @@
         <v>45818</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31906,7 +31902,7 @@
         <v>45015</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31979,7 +31975,7 @@
         <v>45818</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32052,7 +32048,7 @@
         <v>45817</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32125,7 +32121,7 @@
         <v>45160</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32198,7 +32194,7 @@
         <v>45076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32271,7 +32267,7 @@
         <v>45820</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32344,7 +32340,7 @@
         <v>45365</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32417,7 +32413,7 @@
         <v>45621</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32490,7 +32486,7 @@
         <v>45821</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32563,7 +32559,7 @@
         <v>45027</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32636,7 +32632,7 @@
         <v>45624</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32709,7 +32705,7 @@
         <v>45624</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32782,7 +32778,7 @@
         <v>45568</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32855,7 +32851,7 @@
         <v>45951</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32933,7 +32929,7 @@
         <v>45825</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33006,7 +33002,7 @@
         <v>45167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33079,7 +33075,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33157,7 +33153,7 @@
         <v>45827</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33230,7 +33226,7 @@
         <v>45415</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33303,7 +33299,7 @@
         <v>45261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33376,7 +33372,7 @@
         <v>45261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33449,7 +33445,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33522,7 +33518,7 @@
         <v>45637</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33595,7 +33591,7 @@
         <v>45952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33668,7 +33664,7 @@
         <v>45955</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33741,7 +33737,7 @@
         <v>45958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33814,7 +33810,7 @@
         <v>45961</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33887,7 +33883,7 @@
         <v>45127</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33960,7 +33956,7 @@
         <v>45833</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34033,7 +34029,7 @@
         <v>45244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34106,7 +34102,7 @@
         <v>45707</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34179,7 +34175,7 @@
         <v>45964</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34252,7 +34248,7 @@
         <v>45252</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34325,7 +34321,7 @@
         <v>44679</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34403,7 +34399,7 @@
         <v>45256</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34476,7 +34472,7 @@
         <v>45127</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34549,7 +34545,7 @@
         <v>45127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34622,7 +34618,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34695,7 +34691,7 @@
         <v>45835</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34768,7 +34764,7 @@
         <v>44993</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34841,7 +34837,7 @@
         <v>45964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34914,7 +34910,7 @@
         <v>44714</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34992,7 +34988,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35065,7 +35061,7 @@
         <v>45961</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35138,7 +35134,7 @@
         <v>45966</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35211,7 +35207,7 @@
         <v>45966</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35284,7 +35280,7 @@
         <v>44967</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35362,7 +35358,7 @@
         <v>45965</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35440,7 +35436,7 @@
         <v>45964</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35513,7 +35509,7 @@
         <v>44714</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35591,7 +35587,7 @@
         <v>45966</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35664,7 +35660,7 @@
         <v>45966</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35737,7 +35733,7 @@
         <v>45966</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35810,7 +35806,7 @@
         <v>45966</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35883,7 +35879,7 @@
         <v>45964</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35956,7 +35952,7 @@
         <v>45965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36029,7 +36025,7 @@
         <v>45839</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36102,7 +36098,7 @@
         <v>45110</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36175,7 +36171,7 @@
         <v>45197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36248,7 +36244,7 @@
         <v>45971</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36321,7 +36317,7 @@
         <v>45727</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36399,7 +36395,7 @@
         <v>45972</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36472,7 +36468,7 @@
         <v>45561</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36550,7 +36546,7 @@
         <v>45974</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36623,7 +36619,7 @@
         <v>45847</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36696,7 +36692,7 @@
         <v>45109</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36769,7 +36765,7 @@
         <v>45974</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36842,7 +36838,7 @@
         <v>45314</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36915,7 +36911,7 @@
         <v>45219</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36988,7 +36984,7 @@
         <v>45849</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37066,7 +37062,7 @@
         <v>45849</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37144,7 +37140,7 @@
         <v>45978</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37217,7 +37213,7 @@
         <v>45183</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37290,7 +37286,7 @@
         <v>45219</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37363,7 +37359,7 @@
         <v>45125</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37441,7 +37437,7 @@
         <v>45257</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37519,7 +37515,7 @@
         <v>45132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37592,7 +37588,7 @@
         <v>44846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37665,7 +37661,7 @@
         <v>45863</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37738,7 +37734,7 @@
         <v>45027</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37811,7 +37807,7 @@
         <v>45490</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37884,7 +37880,7 @@
         <v>44987</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37957,7 +37953,7 @@
         <v>45863</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38035,7 +38031,7 @@
         <v>45975</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38113,7 +38109,7 @@
         <v>45259</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38186,7 +38182,7 @@
         <v>45264</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38259,7 +38255,7 @@
         <v>45104</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38337,7 +38333,7 @@
         <v>45131</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38410,7 +38406,7 @@
         <v>45307</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38483,7 +38479,7 @@
         <v>45510</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38556,7 +38552,7 @@
         <v>45446</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38629,7 +38625,7 @@
         <v>44501</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38702,7 +38698,7 @@
         <v>45373</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38775,7 +38771,7 @@
         <v>45705</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38848,7 +38844,7 @@
         <v>45176</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38921,7 +38917,7 @@
         <v>45266</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38994,7 +38990,7 @@
         <v>44902</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39067,7 +39063,7 @@
         <v>45264</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39140,7 +39136,7 @@
         <v>45261</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39213,7 +39209,7 @@
         <v>45267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39286,7 +39282,7 @@
         <v>45369</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39359,7 +39355,7 @@
         <v>45397</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39432,7 +39428,7 @@
         <v>45982</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39505,7 +39501,7 @@
         <v>44846</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39578,7 +39574,7 @@
         <v>45272</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39651,7 +39647,7 @@
         <v>45881</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39724,7 +39720,7 @@
         <v>45266</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39797,7 +39793,7 @@
         <v>44785</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39870,7 +39866,7 @@
         <v>45882</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39943,7 +39939,7 @@
         <v>45199</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40016,7 +40012,7 @@
         <v>46097</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40089,7 +40085,7 @@
         <v>46097</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40162,7 +40158,7 @@
         <v>45747</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40235,7 +40231,7 @@
         <v>45981</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40308,7 +40304,7 @@
         <v>45201</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40381,7 +40377,7 @@
         <v>45061</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40454,7 +40450,7 @@
         <v>45986</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40527,7 +40523,7 @@
         <v>45037</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40600,7 +40596,7 @@
         <v>45621</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40673,7 +40669,7 @@
         <v>45197</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40746,7 +40742,7 @@
         <v>45985</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40819,7 +40815,7 @@
         <v>45567</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40897,7 +40893,7 @@
         <v>45985</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40970,7 +40966,7 @@
         <v>46063</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41043,7 +41039,7 @@
         <v>45216</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41116,7 +41112,7 @@
         <v>45985</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41189,7 +41185,7 @@
         <v>46101</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41262,7 +41258,7 @@
         <v>45203</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41335,7 +41331,7 @@
         <v>45986</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41408,7 +41404,7 @@
         <v>45985</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41481,7 +41477,7 @@
         <v>44574</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41554,7 +41550,7 @@
         <v>45113</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41627,7 +41623,7 @@
         <v>46106</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41705,7 +41701,7 @@
         <v>45044</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41778,7 +41774,7 @@
         <v>45418</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41851,7 +41847,7 @@
         <v>45282</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41924,7 +41920,7 @@
         <v>46106</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41997,7 +41993,7 @@
         <v>45988</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42095,7 +42091,7 @@
         <v>44869</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42173,7 +42169,7 @@
         <v>46111</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42251,7 +42247,7 @@
         <v>45552</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42324,7 +42320,7 @@
         <v>45988</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42397,7 +42393,7 @@
         <v>45567</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42470,7 +42466,7 @@
         <v>44792</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42543,7 +42539,7 @@
         <v>45112</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42616,7 +42612,7 @@
         <v>46112</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42694,7 +42690,7 @@
         <v>45523</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42767,7 +42763,7 @@
         <v>46113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42840,7 +42836,7 @@
         <v>45903</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42918,7 +42914,7 @@
         <v>45625</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42991,7 +42987,7 @@
         <v>45993</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43064,7 +43060,7 @@
         <v>46119</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43137,7 +43133,7 @@
         <v>46121</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43215,7 +43211,7 @@
         <v>45995</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43288,7 +43284,7 @@
         <v>45035</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43361,7 +43357,7 @@
         <v>46127</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43439,7 +43435,7 @@
         <v>46127</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43512,7 +43508,7 @@
         <v>45001</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43585,7 +43581,7 @@
         <v>46001</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43658,7 +43654,7 @@
         <v>46127</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43736,7 +43732,7 @@
         <v>46002</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43809,7 +43805,7 @@
         <v>46126</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43882,7 +43878,7 @@
         <v>45478</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43955,7 +43951,7 @@
         <v>46114</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44033,7 +44029,7 @@
         <v>46128</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44111,7 +44107,7 @@
         <v>46132</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44184,7 +44180,7 @@
         <v>45261</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44257,7 +44253,7 @@
         <v>46006</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44330,7 +44326,7 @@
         <v>46006</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44403,7 +44399,7 @@
         <v>46006</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44476,7 +44472,7 @@
         <v>46006</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44549,7 +44545,7 @@
         <v>46114</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44627,7 +44623,7 @@
         <v>46133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44700,7 +44696,7 @@
         <v>46114</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44778,7 +44774,7 @@
         <v>45625</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44851,7 +44847,7 @@
         <v>46007</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44924,7 +44920,7 @@
         <v>46007</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44997,7 +44993,7 @@
         <v>44987</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45070,7 +45066,7 @@
         <v>45555</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45143,7 +45139,7 @@
         <v>45553</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45221,7 +45217,7 @@
         <v>45308</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45294,7 +45290,7 @@
         <v>45803</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45367,7 +45363,7 @@
         <v>45257</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45440,7 +45436,7 @@
         <v>46010</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45513,7 +45509,7 @@
         <v>46010</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45586,7 +45582,7 @@
         <v>45474</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45659,7 +45655,7 @@
         <v>45509</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45732,7 +45728,7 @@
         <v>45863</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45805,7 +45801,7 @@
         <v>44820</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45878,7 +45874,7 @@
         <v>46013</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45951,7 +45947,7 @@
         <v>46020</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46024,7 +46020,7 @@
         <v>45036</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46097,7 +46093,7 @@
         <v>46020</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46170,7 +46166,7 @@
         <v>46018</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46243,7 +46239,7 @@
         <v>46035</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46316,7 +46312,7 @@
         <v>46021</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46389,7 +46385,7 @@
         <v>46021</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46462,7 +46458,7 @@
         <v>45670</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46535,7 +46531,7 @@
         <v>46024</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46608,7 +46604,7 @@
         <v>46027</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46681,7 +46677,7 @@
         <v>45958</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46754,7 +46750,7 @@
         <v>45834</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46832,7 +46828,7 @@
         <v>45230</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46905,7 +46901,7 @@
         <v>46029</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46978,7 +46974,7 @@
         <v>45568</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47051,7 +47047,7 @@
         <v>46140</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47124,7 +47120,7 @@
         <v>46106</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47197,7 +47193,7 @@
         <v>46029</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47270,7 +47266,7 @@
         <v>46029</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47343,7 +47339,7 @@
         <v>45618</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47416,7 +47412,7 @@
         <v>45406</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47489,7 +47485,7 @@
         <v>46027</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47562,7 +47558,7 @@
         <v>44918</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47635,7 +47631,7 @@
         <v>45303</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47708,7 +47704,7 @@
         <v>46035</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47781,7 +47777,7 @@
         <v>44985</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47854,7 +47850,7 @@
         <v>45637</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47927,7 +47923,7 @@
         <v>46035</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48000,7 +47996,7 @@
         <v>46139</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48073,7 +48069,7 @@
         <v>44533</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48146,7 +48142,7 @@
         <v>45980</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48219,7 +48215,7 @@
         <v>45979</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48292,7 +48288,7 @@
         <v>45744</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48365,7 +48361,7 @@
         <v>45112</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48438,7 +48434,7 @@
         <v>45982</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48511,7 +48507,7 @@
         <v>46041</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48584,7 +48580,7 @@
         <v>46041</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48657,7 +48653,7 @@
         <v>45114</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48730,7 +48726,7 @@
         <v>45266</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48803,7 +48799,7 @@
         <v>45567</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48876,7 +48872,7 @@
         <v>45979</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48949,7 +48945,7 @@
         <v>45456</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49027,7 +49023,7 @@
         <v>46036</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49105,7 +49101,7 @@
         <v>46044</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49178,7 +49174,7 @@
         <v>45104</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49251,7 +49247,7 @@
         <v>46043</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49324,7 +49320,7 @@
         <v>46043</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49397,7 +49393,7 @@
         <v>45782</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49470,7 +49466,7 @@
         <v>46043</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49543,7 +49539,7 @@
         <v>46044</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49616,7 +49612,7 @@
         <v>45732</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49689,7 +49685,7 @@
         <v>44974</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49762,7 +49758,7 @@
         <v>44977</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49835,7 +49831,7 @@
         <v>45203</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49908,7 +49904,7 @@
         <v>46045</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49981,7 +49977,7 @@
         <v>45695</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50054,7 +50050,7 @@
         <v>45131</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50127,7 +50123,7 @@
         <v>46045</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50200,7 +50196,7 @@
         <v>44978</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50273,7 +50269,7 @@
         <v>46035</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50346,7 +50342,7 @@
         <v>46064</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50419,7 +50415,7 @@
         <v>46139</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50492,7 +50488,7 @@
         <v>45630</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50565,7 +50561,7 @@
         <v>44991</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50638,7 +50634,7 @@
         <v>44991</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50711,7 +50707,7 @@
         <v>46050</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50784,7 +50780,7 @@
         <v>46030</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50857,7 +50853,7 @@
         <v>46049</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50930,7 +50926,7 @@
         <v>46052</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51003,7 +50999,7 @@
         <v>46045</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51076,7 +51072,7 @@
         <v>46051</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51149,7 +51145,7 @@
         <v>46029</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51222,7 +51218,7 @@
         <v>46056</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51295,7 +51291,7 @@
         <v>46055</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51368,7 +51364,7 @@
         <v>45030</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51441,7 +51437,7 @@
         <v>45520</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51514,7 +51510,7 @@
         <v>45537</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51587,7 +51583,7 @@
         <v>46044</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51660,7 +51656,7 @@
         <v>46146</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51733,7 +51729,7 @@
         <v>46147</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51806,7 +51802,7 @@
         <v>46148</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51884,7 +51880,7 @@
         <v>46119</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51957,7 +51953,7 @@
         <v>46035</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52030,7 +52026,7 @@
         <v>46149</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52108,7 +52104,7 @@
         <v>46149</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52181,7 +52177,7 @@
         <v>45860</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52254,7 +52250,7 @@
         <v>46149</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52332,7 +52328,7 @@
         <v>45797</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52405,7 +52401,7 @@
         <v>46070</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52478,7 +52474,7 @@
         <v>46070</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52551,7 +52547,7 @@
         <v>46070</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52624,7 +52620,7 @@
         <v>45979</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52697,7 +52693,7 @@
         <v>45797</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52770,7 +52766,7 @@
         <v>46007</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52843,7 +52839,7 @@
         <v>46071</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52916,7 +52912,7 @@
         <v>46072</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52989,7 +52985,7 @@
         <v>46072</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53062,7 +53058,7 @@
         <v>46092</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53135,7 +53131,7 @@
         <v>46038</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53208,7 +53204,7 @@
         <v>46072</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53281,7 +53277,7 @@
         <v>45994</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53354,7 +53350,7 @@
         <v>45877</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53427,7 +53423,7 @@
         <v>45121</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53500,7 +53496,7 @@
         <v>46044</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53573,7 +53569,7 @@
         <v>46052</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53646,7 +53642,7 @@
         <v>46155</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53724,7 +53720,7 @@
         <v>45896</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53797,7 +53793,7 @@
         <v>46043</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53870,7 +53866,7 @@
         <v>46156</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53943,7 +53939,7 @@
         <v>46155</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54021,7 +54017,7 @@
         <v>46156</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54094,7 +54090,7 @@
         <v>45835</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54167,7 +54163,7 @@
         <v>46092</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54240,7 +54236,7 @@
         <v>45621</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54313,7 +54309,7 @@
         <v>46097</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54386,7 +54382,7 @@
         <v>46162</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54459,7 +54455,7 @@
         <v>45910</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54532,7 +54528,7 @@
         <v>46167</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54605,7 +54601,7 @@
         <v>46168</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54678,7 +54674,7 @@
         <v>46168</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54751,7 +54747,7 @@
         <v>46171</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54829,7 +54825,7 @@
         <v>46170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54902,7 +54898,7 @@
         <v>46174</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54975,7 +54971,7 @@
         <v>46176</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55053,7 +55049,7 @@
         <v>46127</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55126,7 +55122,7 @@
         <v>46181</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55204,7 +55200,7 @@
         <v>46035</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55277,7 +55273,7 @@
         <v>46182</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55350,7 +55346,7 @@
         <v>46182</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55423,7 +55419,7 @@
         <v>46185</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55501,7 +55497,7 @@
         <v>45257</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55574,7 +55570,7 @@
         <v>46190</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55652,7 +55648,7 @@
         <v>46191</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55730,7 +55726,7 @@
         <v>46191</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55803,7 +55799,7 @@
         <v>46191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55876,7 +55872,7 @@
         <v>46197</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55949,7 +55945,7 @@
         <v>46196</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56022,7 +56018,7 @@
         <v>46197</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56100,7 +56096,7 @@
         <v>46197</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56178,7 +56174,7 @@
         <v>46202</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56251,7 +56247,7 @@
         <v>46024</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56324,7 +56320,7 @@
         <v>46211</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56397,7 +56393,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56470,7 +56466,7 @@
         <v>46202</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56548,7 +56544,7 @@
         <v>46216</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56626,7 +56622,7 @@
         <v>46268</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56699,7 +56695,7 @@
         <v>46167</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56777,7 +56773,7 @@
         <v>46177</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56855,7 +56851,7 @@
         <v>46177</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56933,7 +56929,7 @@
         <v>46276</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57006,7 +57002,7 @@
         <v>46233</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57084,7 +57080,7 @@
         <v>46233</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57162,7 +57158,7 @@
         <v>46281</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57235,7 +57231,7 @@
         <v>46238</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57313,7 +57309,7 @@
         <v>46241</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57391,7 +57387,7 @@
         <v>46241</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57469,7 +57465,7 @@
         <v>46288</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57542,7 +57538,7 @@
         <v>46154</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57620,7 +57616,7 @@
         <v>46287</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57698,7 +57694,7 @@
         <v>46246</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57771,7 +57767,7 @@
         <v>46286</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57849,7 +57845,7 @@
         <v>46289</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57922,7 +57918,7 @@
         <v>46135</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58000,7 +57996,7 @@
         <v>46290</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58078,7 +58074,7 @@
         <v>46286</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58156,7 +58152,7 @@
         <v>46247</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58234,7 +58230,7 @@
         <v>46290</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58307,7 +58303,7 @@
         <v>46293</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58380,7 +58376,7 @@
         <v>46248</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58458,7 +58454,7 @@
         <v>46293</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58531,7 +58527,7 @@
         <v>46127</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58609,7 +58605,7 @@
         <v>46293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58682,7 +58678,7 @@
         <v>46294</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58755,7 +58751,7 @@
         <v>46293</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58828,7 +58824,7 @@
         <v>46240</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58906,7 +58902,7 @@
         <v>46294</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58979,7 +58975,7 @@
         <v>46249</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59057,7 +59053,7 @@
         <v>46251</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59135,7 +59131,7 @@
         <v>46251</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59213,7 +59209,7 @@
         <v>46252</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59291,7 +59287,7 @@
         <v>46252</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59364,7 +59360,7 @@
         <v>46049</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59437,7 +59433,7 @@
         <v>46297</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59510,7 +59506,7 @@
         <v>46297</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59583,7 +59579,7 @@
         <v>45890</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59661,7 +59657,7 @@
         <v>45966</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59734,7 +59730,7 @@
         <v>46252</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59807,7 +59803,7 @@
         <v>46254</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59880,7 +59876,7 @@
         <v>46259</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59953,7 +59949,7 @@
         <v>46259</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60026,7 +60022,7 @@
         <v>46259</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60104,7 +60100,7 @@
         <v>46259</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60177,7 +60173,7 @@
         <v>46188</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60250,7 +60246,7 @@
         <v>44578</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60323,7 +60319,7 @@
         <v>44652</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60396,7 +60392,7 @@
         <v>45074</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60474,7 +60470,7 @@
         <v>45257</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60547,7 +60543,7 @@
         <v>45097</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60620,7 +60616,7 @@
         <v>45351</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60698,7 +60694,7 @@
         <v>44809</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60771,7 +60767,7 @@
         <v>45097</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60844,7 +60840,7 @@
         <v>45133</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60917,7 +60913,7 @@
         <v>45446</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60995,7 +60991,7 @@
         <v>45701</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61073,7 +61069,7 @@
         <v>45701</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61151,7 +61147,7 @@
         <v>45708</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61229,7 +61225,7 @@
         <v>45799</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61302,7 +61298,7 @@
         <v>45819</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61375,7 +61371,7 @@
         <v>45824</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61448,7 +61444,7 @@
         <v>45835</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61521,7 +61517,7 @@
         <v>45904</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61594,7 +61590,7 @@
         <v>45943</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61667,7 +61663,7 @@
         <v>45964</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61745,7 +61741,7 @@
         <v>46038</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61823,7 +61819,7 @@
         <v>46043</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61896,7 +61892,7 @@
         <v>46052</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61974,7 +61970,7 @@
         <v>44649</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62047,7 +62043,7 @@
         <v>46066</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62120,7 +62116,7 @@
         <v>46076</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62193,7 +62189,7 @@
         <v>46133</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62271,7 +62267,7 @@
         <v>46134</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62344,7 +62340,7 @@
         <v>45727</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1091,7 +1091,7 @@
         <v>5.9</v>
       </c>
       <c r="J5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K5" t="n">
         <v>7</v>
@@ -1118,13 +1118,13 @@
         <v>2</v>
       </c>
       <c r="S5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T5" t="n">
-        <v>152</v>
+        <v>157</v>
       </c>
       <c r="U5" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
@@ -1147,6 +1147,7 @@
 Vedticka
 Gråspett
 Kransmossa
+Kärrviol
 Linnea
 Spillkråka
 Sälg
@@ -1154,6 +1155,7 @@
 Tofsmes
 Kungsfågel
 Vanlig groda
+Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1214,7 +1216,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1230,7 +1232,7 @@
         <v>5</v>
       </c>
       <c r="J6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
@@ -1257,13 +1259,13 @@
         <v>2</v>
       </c>
       <c r="S6" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="T6" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="U6" t="n">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
@@ -1286,6 +1288,7 @@
 Vedticka
 Gråspett
 Kransmossa
+Kärrviol
 Linnea
 Spillkråka
 Sälg
@@ -1293,6 +1296,7 @@
 Tofsmes
 Kungsfågel
 Vanlig groda
+Fläcknycklar
 Revlummer</t>
         </is>
       </c>
@@ -1353,7 +1357,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1484,7 +1488,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1614,7 +1618,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1744,7 +1748,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1869,7 +1873,7 @@
         <v>45835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1996,7 +2000,7 @@
         <v>46047</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2119,7 +2123,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2245,7 +2249,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2370,7 +2374,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2493,7 +2497,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2615,7 +2619,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2732,7 +2736,7 @@
         <v>45827</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2848,7 +2852,7 @@
         <v>45936</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2968,7 +2972,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3084,7 +3088,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3195,7 +3199,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3315,7 +3319,7 @@
         <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3425,7 +3429,7 @@
         <v>45489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3535,7 +3539,7 @@
         <v>45896</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3658,7 +3662,7 @@
         <v>45614</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3772,7 +3776,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3882,7 +3886,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3991,7 +3995,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4100,7 +4104,7 @@
         <v>45638</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4209,7 +4213,7 @@
         <v>46166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4322,7 +4326,7 @@
         <v>45835</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4439,7 +4443,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4552,7 +4556,7 @@
         <v>45931</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4660,7 +4664,7 @@
         <v>45632</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4768,7 +4772,7 @@
         <v>44869</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4880,7 +4884,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4996,7 +5000,7 @@
         <v>45637</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5103,7 +5107,7 @@
         <v>46097</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5214,7 +5218,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5325,7 +5329,7 @@
         <v>45254</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5431,7 +5435,7 @@
         <v>44829</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5541,7 +5545,7 @@
         <v>45251</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5647,7 +5651,7 @@
         <v>45274</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5757,7 +5761,7 @@
         <v>45890</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5863,7 +5867,7 @@
         <v>45656</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5969,7 +5973,7 @@
         <v>45358</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6075,7 +6079,7 @@
         <v>44602</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6190,7 +6194,7 @@
         <v>45812</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6296,7 +6300,7 @@
         <v>45835</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6406,7 +6410,7 @@
         <v>45251</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6516,7 +6520,7 @@
         <v>45849</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6622,7 +6626,7 @@
         <v>45028</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6728,7 +6732,7 @@
         <v>45996</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6834,7 +6838,7 @@
         <v>46027</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6940,7 +6944,7 @@
         <v>46226</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7051,7 +7055,7 @@
         <v>46283</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7162,7 +7166,7 @@
         <v>46289</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7277,7 +7281,7 @@
         <v>44536</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7382,7 +7386,7 @@
         <v>44869</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7492,7 +7496,7 @@
         <v>44509</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7606,7 +7610,7 @@
         <v>44735</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7711,7 +7715,7 @@
         <v>45754</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7816,7 +7820,7 @@
         <v>44761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7925,7 +7929,7 @@
         <v>45418</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8030,7 +8034,7 @@
         <v>44992</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8139,7 +8143,7 @@
         <v>45016</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8244,7 +8248,7 @@
         <v>44973</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8349,7 +8353,7 @@
         <v>45334</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8454,7 +8458,7 @@
         <v>45761</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8559,7 +8563,7 @@
         <v>45502</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8664,7 +8668,7 @@
         <v>45127</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8773,7 +8777,7 @@
         <v>45256</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8878,7 +8882,7 @@
         <v>45793</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8983,7 +8987,7 @@
         <v>44588</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9088,7 +9092,7 @@
         <v>45621</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9193,7 +9197,7 @@
         <v>44750</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9307,7 +9311,7 @@
         <v>45638</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9416,7 +9420,7 @@
         <v>45839</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9526,7 +9530,7 @@
         <v>45959</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9635,7 +9639,7 @@
         <v>45960</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9745,7 +9749,7 @@
         <v>44918</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9850,7 +9854,7 @@
         <v>45690</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9959,7 +9963,7 @@
         <v>45061</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10064,7 +10068,7 @@
         <v>45091</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10169,7 +10173,7 @@
         <v>45981</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10274,7 +10278,7 @@
         <v>45228</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10383,7 +10387,7 @@
         <v>46120</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10488,7 +10492,7 @@
         <v>44909</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10597,7 +10601,7 @@
         <v>45294</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10706,7 +10710,7 @@
         <v>45005</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10815,7 +10819,7 @@
         <v>46041</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10920,7 +10924,7 @@
         <v>45110</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11025,7 +11029,7 @@
         <v>46069</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11130,7 +11134,7 @@
         <v>46155</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11244,7 +11248,7 @@
         <v>46202</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11353,7 +11357,7 @@
         <v>46287</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11463,7 +11467,7 @@
         <v>46244</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11568,7 +11572,7 @@
         <v>45181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11673,7 +11677,7 @@
         <v>45996</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11783,7 +11787,7 @@
         <v>44782</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11856,7 +11860,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11929,7 +11933,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12002,7 +12006,7 @@
         <v>44802</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12080,7 +12084,7 @@
         <v>44671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12153,7 +12157,7 @@
         <v>44872</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12231,7 +12235,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12304,7 +12308,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12382,7 +12386,7 @@
         <v>44570</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12455,7 +12459,7 @@
         <v>44670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12528,7 +12532,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12601,7 +12605,7 @@
         <v>44877</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12674,7 +12678,7 @@
         <v>44824</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12747,7 +12751,7 @@
         <v>44834</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12820,7 +12824,7 @@
         <v>44539</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12893,7 +12897,7 @@
         <v>44865</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12971,7 +12975,7 @@
         <v>44693</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13044,7 +13048,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13117,7 +13121,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13190,7 +13194,7 @@
         <v>44792</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13263,7 +13267,7 @@
         <v>44690</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13341,7 +13345,7 @@
         <v>44777</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13414,7 +13418,7 @@
         <v>44651</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13487,7 +13491,7 @@
         <v>44851</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13560,7 +13564,7 @@
         <v>44684</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13638,7 +13642,7 @@
         <v>44529</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13711,7 +13715,7 @@
         <v>44543</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13784,7 +13788,7 @@
         <v>44862</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13857,7 +13861,7 @@
         <v>44797</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13930,7 +13934,7 @@
         <v>44533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14003,7 +14007,7 @@
         <v>45378</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14076,7 +14080,7 @@
         <v>44628</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14149,7 +14153,7 @@
         <v>44875</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14222,7 +14226,7 @@
         <v>45342</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14300,7 +14304,7 @@
         <v>45667</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14373,7 +14377,7 @@
         <v>45306</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14446,7 +14450,7 @@
         <v>45467</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14519,7 +14523,7 @@
         <v>45397</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14592,7 +14596,7 @@
         <v>44543</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14670,7 +14674,7 @@
         <v>44749</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14748,7 +14752,7 @@
         <v>45208</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14826,7 +14830,7 @@
         <v>45085</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14899,7 +14903,7 @@
         <v>45293</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14972,7 +14976,7 @@
         <v>44929</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15050,7 +15054,7 @@
         <v>45154</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15123,7 +15127,7 @@
         <v>45454</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15196,7 +15200,7 @@
         <v>44867</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15269,7 +15273,7 @@
         <v>45050</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15342,7 +15346,7 @@
         <v>45518</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15415,7 +15419,7 @@
         <v>45351</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15488,7 +15492,7 @@
         <v>44912</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15561,7 +15565,7 @@
         <v>45749</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15634,7 +15638,7 @@
         <v>44992</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15707,7 +15711,7 @@
         <v>45022</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15780,7 +15784,7 @@
         <v>45433</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15853,7 +15857,7 @@
         <v>45433</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15926,7 +15930,7 @@
         <v>45455</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16004,7 +16008,7 @@
         <v>45103</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16077,7 +16081,7 @@
         <v>44915</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16150,7 +16154,7 @@
         <v>45061</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16223,7 +16227,7 @@
         <v>45302</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16296,7 +16300,7 @@
         <v>44746</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16369,7 +16373,7 @@
         <v>45611</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16442,7 +16446,7 @@
         <v>44890</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16515,7 +16519,7 @@
         <v>45677</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16588,7 +16592,7 @@
         <v>45160</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16661,7 +16665,7 @@
         <v>45756</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16734,7 +16738,7 @@
         <v>44909</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16807,7 +16811,7 @@
         <v>45334</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16885,7 +16889,7 @@
         <v>45231</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16958,7 +16962,7 @@
         <v>45296</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17031,7 +17035,7 @@
         <v>45255</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17104,7 +17108,7 @@
         <v>45113</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17177,7 +17181,7 @@
         <v>45103</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17255,7 +17259,7 @@
         <v>45015</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17328,7 +17332,7 @@
         <v>45446</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17406,7 +17410,7 @@
         <v>45561</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17479,7 +17483,7 @@
         <v>45518</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17552,7 +17556,7 @@
         <v>45558</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17625,7 +17629,7 @@
         <v>45454</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17698,7 +17702,7 @@
         <v>45151</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17771,7 +17775,7 @@
         <v>44909</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17844,7 +17848,7 @@
         <v>45161</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17917,7 +17921,7 @@
         <v>44993</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17990,7 +17994,7 @@
         <v>44962</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18063,7 +18067,7 @@
         <v>45334</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18136,7 +18140,7 @@
         <v>45167</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18209,7 +18213,7 @@
         <v>45567</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18282,7 +18286,7 @@
         <v>44837</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18355,7 +18359,7 @@
         <v>44837</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18428,7 +18432,7 @@
         <v>45345</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18501,7 +18505,7 @@
         <v>45664</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18574,7 +18578,7 @@
         <v>45280</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18647,7 +18651,7 @@
         <v>45260</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18720,7 +18724,7 @@
         <v>45231</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18798,7 +18802,7 @@
         <v>45554</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18876,7 +18880,7 @@
         <v>44992</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18949,7 +18953,7 @@
         <v>45258</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19022,7 +19026,7 @@
         <v>45376</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19095,7 +19099,7 @@
         <v>45428</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19168,7 +19172,7 @@
         <v>45267</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19241,7 +19245,7 @@
         <v>44711</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19319,7 +19323,7 @@
         <v>45490</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19392,7 +19396,7 @@
         <v>45446</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19470,7 +19474,7 @@
         <v>45453</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19543,7 +19547,7 @@
         <v>45515</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19616,7 +19620,7 @@
         <v>44959</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19689,7 +19693,7 @@
         <v>45323</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19762,7 +19766,7 @@
         <v>44546</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19835,7 +19839,7 @@
         <v>44546</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19908,7 +19912,7 @@
         <v>44974</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19981,7 +19985,7 @@
         <v>45647</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20054,7 +20058,7 @@
         <v>45618</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20127,7 +20131,7 @@
         <v>45261</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20200,7 +20204,7 @@
         <v>45884</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20273,7 +20277,7 @@
         <v>45408</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20346,7 +20350,7 @@
         <v>45526</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20419,7 +20423,7 @@
         <v>45447</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20492,7 +20496,7 @@
         <v>45219</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20565,7 +20569,7 @@
         <v>45195</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20638,7 +20642,7 @@
         <v>45559</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20711,7 +20715,7 @@
         <v>45152</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20784,7 +20788,7 @@
         <v>45886</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20857,7 +20861,7 @@
         <v>45296</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20930,7 +20934,7 @@
         <v>44951</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -21003,7 +21007,7 @@
         <v>44719</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21076,7 +21080,7 @@
         <v>45497</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21154,7 +21158,7 @@
         <v>44994</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21227,7 +21231,7 @@
         <v>45004</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21300,7 +21304,7 @@
         <v>45334</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21378,7 +21382,7 @@
         <v>45049</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21451,7 +21455,7 @@
         <v>45553</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21529,7 +21533,7 @@
         <v>45376</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21602,7 +21606,7 @@
         <v>45890</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21675,7 +21679,7 @@
         <v>45890</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21748,7 +21752,7 @@
         <v>45509</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21821,7 +21825,7 @@
         <v>45898</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21899,7 +21903,7 @@
         <v>45898</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21977,7 +21981,7 @@
         <v>45898</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22055,7 +22059,7 @@
         <v>45726</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22128,7 +22132,7 @@
         <v>44929</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22206,7 +22210,7 @@
         <v>45558</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22279,7 +22283,7 @@
         <v>45103</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22357,7 +22361,7 @@
         <v>45706</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22430,7 +22434,7 @@
         <v>45901</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22508,7 +22512,7 @@
         <v>45034</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22581,7 +22585,7 @@
         <v>45097</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22654,7 +22658,7 @@
         <v>45110</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22727,7 +22731,7 @@
         <v>45544</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22800,7 +22804,7 @@
         <v>45631</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22873,7 +22877,7 @@
         <v>45695</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22946,7 +22950,7 @@
         <v>45695</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -23019,7 +23023,7 @@
         <v>45425</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23092,7 +23096,7 @@
         <v>45425</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23165,7 +23169,7 @@
         <v>45610</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23238,7 +23242,7 @@
         <v>44992</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23311,7 +23315,7 @@
         <v>45317</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23384,7 +23388,7 @@
         <v>45727</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23457,7 +23461,7 @@
         <v>45068</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23530,7 +23534,7 @@
         <v>45093</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23603,7 +23607,7 @@
         <v>45903</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23676,7 +23680,7 @@
         <v>44978</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23749,7 +23753,7 @@
         <v>45275</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23822,7 +23826,7 @@
         <v>45429</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23895,7 +23899,7 @@
         <v>45349</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23968,7 +23972,7 @@
         <v>44986</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24041,7 +24045,7 @@
         <v>45595</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24114,7 +24118,7 @@
         <v>45096</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24187,7 +24191,7 @@
         <v>45776</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24265,7 +24269,7 @@
         <v>45912</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24343,7 +24347,7 @@
         <v>45911</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24416,7 +24420,7 @@
         <v>45911</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24489,7 +24493,7 @@
         <v>45912</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24562,7 +24566,7 @@
         <v>45912</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24635,7 +24639,7 @@
         <v>45779</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24708,7 +24712,7 @@
         <v>45476</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24781,7 +24785,7 @@
         <v>45049</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24854,7 +24858,7 @@
         <v>45911</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24927,7 +24931,7 @@
         <v>45916</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -25000,7 +25004,7 @@
         <v>45376</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25073,7 +25077,7 @@
         <v>45027</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25146,7 +25150,7 @@
         <v>45202</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25219,7 +25223,7 @@
         <v>45915</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25292,7 +25296,7 @@
         <v>45170</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25370,7 +25374,7 @@
         <v>45357</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25443,7 +25447,7 @@
         <v>45216</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25516,7 +25520,7 @@
         <v>45015</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25589,7 +25593,7 @@
         <v>44580</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25662,7 +25666,7 @@
         <v>44917</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25735,7 +25739,7 @@
         <v>45480</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25808,7 +25812,7 @@
         <v>45595</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25881,7 +25885,7 @@
         <v>45266</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25954,7 +25958,7 @@
         <v>45646</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26027,7 +26031,7 @@
         <v>44959</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26100,7 +26104,7 @@
         <v>45098</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26173,7 +26177,7 @@
         <v>45917</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26246,7 +26250,7 @@
         <v>45741</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26319,7 +26323,7 @@
         <v>45919</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26392,7 +26396,7 @@
         <v>45524</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26465,7 +26469,7 @@
         <v>45350</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26538,7 +26542,7 @@
         <v>45921</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26611,7 +26615,7 @@
         <v>45510</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26684,7 +26688,7 @@
         <v>45921</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26757,7 +26761,7 @@
         <v>45002</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26830,7 +26834,7 @@
         <v>44966</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26903,7 +26907,7 @@
         <v>45127</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26976,7 +26980,7 @@
         <v>45924</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27049,7 +27053,7 @@
         <v>45787</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27122,7 +27126,7 @@
         <v>45790</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27195,7 +27199,7 @@
         <v>45925</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27268,7 +27272,7 @@
         <v>45103</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27341,7 +27345,7 @@
         <v>45925</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27414,7 +27418,7 @@
         <v>45790</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27487,7 +27491,7 @@
         <v>45609</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27560,7 +27564,7 @@
         <v>45574</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27633,7 +27637,7 @@
         <v>45675</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27706,7 +27710,7 @@
         <v>45596</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27779,7 +27783,7 @@
         <v>45929</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27852,7 +27856,7 @@
         <v>45001</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27925,7 +27929,7 @@
         <v>45428</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27998,7 +28002,7 @@
         <v>45001</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28071,7 +28075,7 @@
         <v>44971</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28144,7 +28148,7 @@
         <v>45362</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28217,7 +28221,7 @@
         <v>45152</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28290,7 +28294,7 @@
         <v>45169</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28363,7 +28367,7 @@
         <v>45553</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28441,7 +28445,7 @@
         <v>45796</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28514,7 +28518,7 @@
         <v>45240</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28587,7 +28591,7 @@
         <v>45932</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28665,7 +28669,7 @@
         <v>45932</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28743,7 +28747,7 @@
         <v>45583</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28816,7 +28820,7 @@
         <v>45608</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28889,7 +28893,7 @@
         <v>45509</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28962,7 +28966,7 @@
         <v>44974</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29035,7 +29039,7 @@
         <v>45608</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29108,7 +29112,7 @@
         <v>44974</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29181,7 +29185,7 @@
         <v>44643</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29254,7 +29258,7 @@
         <v>45558</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29327,7 +29331,7 @@
         <v>45727</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29400,7 +29404,7 @@
         <v>45934</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29473,7 +29477,7 @@
         <v>45198</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29546,7 +29550,7 @@
         <v>45630</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29619,7 +29623,7 @@
         <v>45630</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29692,7 +29696,7 @@
         <v>45397</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29765,7 +29769,7 @@
         <v>45169</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29838,7 +29842,7 @@
         <v>45114</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29911,7 +29915,7 @@
         <v>45198</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29984,7 +29988,7 @@
         <v>45165</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30057,7 +30061,7 @@
         <v>45937</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30130,7 +30134,7 @@
         <v>45232</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30203,7 +30207,7 @@
         <v>45937</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30276,7 +30280,7 @@
         <v>45574</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30349,7 +30353,7 @@
         <v>45608</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30422,7 +30426,7 @@
         <v>45200</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30495,7 +30499,7 @@
         <v>45169</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30568,7 +30572,7 @@
         <v>44998</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30641,7 +30645,7 @@
         <v>45667</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30714,7 +30718,7 @@
         <v>44731</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30787,7 +30791,7 @@
         <v>45559</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30860,7 +30864,7 @@
         <v>45180</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30933,7 +30937,7 @@
         <v>45623</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31006,7 +31010,7 @@
         <v>45939</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31084,7 +31088,7 @@
         <v>45944</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31157,7 +31161,7 @@
         <v>45812</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31235,7 +31239,7 @@
         <v>45946</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31308,7 +31312,7 @@
         <v>45751</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31381,7 +31385,7 @@
         <v>45607</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31459,7 +31463,7 @@
         <v>45813</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31532,7 +31536,7 @@
         <v>44998</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31605,7 +31609,7 @@
         <v>45351</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31678,7 +31682,7 @@
         <v>45818</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31756,7 +31760,7 @@
         <v>45244</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31829,7 +31833,7 @@
         <v>45818</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31902,7 +31906,7 @@
         <v>45015</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31975,7 +31979,7 @@
         <v>45818</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32048,7 +32052,7 @@
         <v>45817</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32121,7 +32125,7 @@
         <v>45160</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32194,7 +32198,7 @@
         <v>45076</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32267,7 +32271,7 @@
         <v>45820</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32340,7 +32344,7 @@
         <v>45365</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32413,7 +32417,7 @@
         <v>45621</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32486,7 +32490,7 @@
         <v>45821</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32559,7 +32563,7 @@
         <v>45027</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32632,7 +32636,7 @@
         <v>45624</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32705,7 +32709,7 @@
         <v>45624</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32778,7 +32782,7 @@
         <v>45568</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32851,7 +32855,7 @@
         <v>45951</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32929,7 +32933,7 @@
         <v>45825</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33002,7 +33006,7 @@
         <v>45167</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33075,7 +33079,7 @@
         <v>45951</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33153,7 +33157,7 @@
         <v>45827</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33226,7 +33230,7 @@
         <v>45415</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33299,7 +33303,7 @@
         <v>45261</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33372,7 +33376,7 @@
         <v>45261</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33445,7 +33449,7 @@
         <v>45832</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33518,7 +33522,7 @@
         <v>45637</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33591,7 +33595,7 @@
         <v>45952</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33664,7 +33668,7 @@
         <v>45955</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33737,7 +33741,7 @@
         <v>45958</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33810,7 +33814,7 @@
         <v>45961</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33883,7 +33887,7 @@
         <v>45127</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33956,7 +33960,7 @@
         <v>45833</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34029,7 +34033,7 @@
         <v>45244</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34102,7 +34106,7 @@
         <v>45707</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34175,7 +34179,7 @@
         <v>45964</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34248,7 +34252,7 @@
         <v>45252</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34321,7 +34325,7 @@
         <v>44679</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34399,7 +34403,7 @@
         <v>45256</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34472,7 +34476,7 @@
         <v>45127</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34545,7 +34549,7 @@
         <v>45127</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34618,7 +34622,7 @@
         <v>45960</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34691,7 +34695,7 @@
         <v>45835</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34764,7 +34768,7 @@
         <v>44993</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34837,7 +34841,7 @@
         <v>45964</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34910,7 +34914,7 @@
         <v>44714</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34988,7 +34992,7 @@
         <v>45961</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35061,7 +35065,7 @@
         <v>45961</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35134,7 +35138,7 @@
         <v>45966</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35207,7 +35211,7 @@
         <v>45966</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35280,7 +35284,7 @@
         <v>44967</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35358,7 +35362,7 @@
         <v>45965</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35436,7 +35440,7 @@
         <v>45964</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35509,7 +35513,7 @@
         <v>44714</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35587,7 +35591,7 @@
         <v>45966</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35660,7 +35664,7 @@
         <v>45966</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35733,7 +35737,7 @@
         <v>45966</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35806,7 +35810,7 @@
         <v>45966</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35879,7 +35883,7 @@
         <v>45964</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35952,7 +35956,7 @@
         <v>45965</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36025,7 +36029,7 @@
         <v>45839</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36098,7 +36102,7 @@
         <v>45110</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36171,7 +36175,7 @@
         <v>45197</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36244,7 +36248,7 @@
         <v>45971</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36317,7 +36321,7 @@
         <v>45727</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36395,7 +36399,7 @@
         <v>45972</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36468,7 +36472,7 @@
         <v>45561</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36546,7 +36550,7 @@
         <v>45974</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36619,7 +36623,7 @@
         <v>45847</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36692,7 +36696,7 @@
         <v>45109</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36765,7 +36769,7 @@
         <v>45974</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36838,7 +36842,7 @@
         <v>45314</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36911,7 +36915,7 @@
         <v>45219</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36984,7 +36988,7 @@
         <v>45849</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37062,7 +37066,7 @@
         <v>45849</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37140,7 +37144,7 @@
         <v>45978</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37213,7 +37217,7 @@
         <v>45183</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37286,7 +37290,7 @@
         <v>45219</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37359,7 +37363,7 @@
         <v>45125</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37437,7 +37441,7 @@
         <v>45257</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37515,7 +37519,7 @@
         <v>45132</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37588,7 +37592,7 @@
         <v>44846</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37661,7 +37665,7 @@
         <v>45863</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37734,7 +37738,7 @@
         <v>45027</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37807,7 +37811,7 @@
         <v>45490</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37880,7 +37884,7 @@
         <v>44987</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37953,7 +37957,7 @@
         <v>45863</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38031,7 +38035,7 @@
         <v>45975</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38109,7 +38113,7 @@
         <v>45259</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38182,7 +38186,7 @@
         <v>45264</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38255,7 +38259,7 @@
         <v>45104</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38333,7 +38337,7 @@
         <v>45131</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38406,7 +38410,7 @@
         <v>45307</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38479,7 +38483,7 @@
         <v>45510</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38552,7 +38556,7 @@
         <v>45446</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38625,7 +38629,7 @@
         <v>44501</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38698,7 +38702,7 @@
         <v>45373</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38771,7 +38775,7 @@
         <v>45705</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38844,7 +38848,7 @@
         <v>45176</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38917,7 +38921,7 @@
         <v>45266</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38990,7 +38994,7 @@
         <v>44902</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39063,7 +39067,7 @@
         <v>45264</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39136,7 +39140,7 @@
         <v>45261</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39209,7 +39213,7 @@
         <v>45267</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39282,7 +39286,7 @@
         <v>45369</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39355,7 +39359,7 @@
         <v>45397</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39428,7 +39432,7 @@
         <v>45982</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39501,7 +39505,7 @@
         <v>44846</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39574,7 +39578,7 @@
         <v>45272</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39647,7 +39651,7 @@
         <v>45881</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39720,7 +39724,7 @@
         <v>45266</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39793,7 +39797,7 @@
         <v>44785</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39866,7 +39870,7 @@
         <v>45882</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39939,7 +39943,7 @@
         <v>45199</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40012,7 +40016,7 @@
         <v>46097</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40085,7 +40089,7 @@
         <v>46097</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40158,7 +40162,7 @@
         <v>45747</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40231,7 +40235,7 @@
         <v>45981</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40304,7 +40308,7 @@
         <v>45201</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40377,7 +40381,7 @@
         <v>45061</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40450,7 +40454,7 @@
         <v>45986</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40523,7 +40527,7 @@
         <v>45037</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40596,7 +40600,7 @@
         <v>45621</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40669,7 +40673,7 @@
         <v>45197</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40742,7 +40746,7 @@
         <v>45985</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40815,7 +40819,7 @@
         <v>45567</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40893,7 +40897,7 @@
         <v>45985</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40966,7 +40970,7 @@
         <v>46063</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41039,7 +41043,7 @@
         <v>45216</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41112,7 +41116,7 @@
         <v>45985</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41185,7 +41189,7 @@
         <v>46101</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41258,7 +41262,7 @@
         <v>45203</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41331,7 +41335,7 @@
         <v>45986</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41404,7 +41408,7 @@
         <v>45985</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41477,7 +41481,7 @@
         <v>44574</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41550,7 +41554,7 @@
         <v>45113</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41623,7 +41627,7 @@
         <v>46106</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41701,7 +41705,7 @@
         <v>45044</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41774,7 +41778,7 @@
         <v>45418</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41847,7 +41851,7 @@
         <v>45282</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41920,7 +41924,7 @@
         <v>46106</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41993,7 +41997,7 @@
         <v>45988</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42091,7 +42095,7 @@
         <v>44869</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42169,7 +42173,7 @@
         <v>46111</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42247,7 +42251,7 @@
         <v>45552</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42320,7 +42324,7 @@
         <v>45988</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42393,7 +42397,7 @@
         <v>45567</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42466,7 +42470,7 @@
         <v>44792</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42539,7 +42543,7 @@
         <v>45112</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42612,7 +42616,7 @@
         <v>46112</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42690,7 +42694,7 @@
         <v>45523</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42763,7 +42767,7 @@
         <v>46113</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42836,7 +42840,7 @@
         <v>45903</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42914,7 +42918,7 @@
         <v>45625</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42987,7 +42991,7 @@
         <v>45993</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43060,7 +43064,7 @@
         <v>46119</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43133,7 +43137,7 @@
         <v>46121</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43211,7 +43215,7 @@
         <v>45995</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43284,7 +43288,7 @@
         <v>45035</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43357,7 +43361,7 @@
         <v>46127</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43435,7 +43439,7 @@
         <v>46127</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43508,7 +43512,7 @@
         <v>45001</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43581,7 +43585,7 @@
         <v>46001</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43654,7 +43658,7 @@
         <v>46127</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43732,7 +43736,7 @@
         <v>46002</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43805,7 +43809,7 @@
         <v>46126</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43878,7 +43882,7 @@
         <v>45478</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43951,7 +43955,7 @@
         <v>46114</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44029,7 +44033,7 @@
         <v>46128</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44107,7 +44111,7 @@
         <v>46132</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44180,7 +44184,7 @@
         <v>45261</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44253,7 +44257,7 @@
         <v>46006</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44326,7 +44330,7 @@
         <v>46006</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44399,7 +44403,7 @@
         <v>46006</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44472,7 +44476,7 @@
         <v>46006</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44545,7 +44549,7 @@
         <v>46114</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44623,7 +44627,7 @@
         <v>46133</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44696,7 +44700,7 @@
         <v>46114</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44774,7 +44778,7 @@
         <v>45625</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44847,7 +44851,7 @@
         <v>46007</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44920,7 +44924,7 @@
         <v>46007</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44993,7 +44997,7 @@
         <v>44987</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45066,7 +45070,7 @@
         <v>45555</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45139,7 +45143,7 @@
         <v>45553</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45217,7 +45221,7 @@
         <v>45308</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45290,7 +45294,7 @@
         <v>45803</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45363,7 +45367,7 @@
         <v>45257</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45436,7 +45440,7 @@
         <v>46010</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45509,7 +45513,7 @@
         <v>46010</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45582,7 +45586,7 @@
         <v>45474</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45655,7 +45659,7 @@
         <v>45509</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45728,7 +45732,7 @@
         <v>45863</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45801,7 +45805,7 @@
         <v>44820</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45874,7 +45878,7 @@
         <v>46013</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45947,7 +45951,7 @@
         <v>46020</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46020,7 +46024,7 @@
         <v>45036</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46093,7 +46097,7 @@
         <v>46020</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46166,7 +46170,7 @@
         <v>46018</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46239,7 +46243,7 @@
         <v>46035</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46312,7 +46316,7 @@
         <v>46021</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46385,7 +46389,7 @@
         <v>46021</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46458,7 +46462,7 @@
         <v>45670</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46531,7 +46535,7 @@
         <v>46024</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46604,7 +46608,7 @@
         <v>46027</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46677,7 +46681,7 @@
         <v>45958</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46750,7 +46754,7 @@
         <v>45834</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46828,7 +46832,7 @@
         <v>45230</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46901,7 +46905,7 @@
         <v>46029</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46974,7 +46978,7 @@
         <v>45568</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47047,7 +47051,7 @@
         <v>46140</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47120,7 +47124,7 @@
         <v>46106</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47193,7 +47197,7 @@
         <v>46029</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47266,7 +47270,7 @@
         <v>46029</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47339,7 +47343,7 @@
         <v>45618</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47412,7 +47416,7 @@
         <v>45406</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47485,7 +47489,7 @@
         <v>46027</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47558,7 +47562,7 @@
         <v>44918</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47631,7 +47635,7 @@
         <v>45303</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47704,7 +47708,7 @@
         <v>46035</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47777,7 +47781,7 @@
         <v>44985</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47850,7 +47854,7 @@
         <v>45637</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47923,7 +47927,7 @@
         <v>46035</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47996,7 +48000,7 @@
         <v>46139</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48069,7 +48073,7 @@
         <v>44533</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48142,7 +48146,7 @@
         <v>45980</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48215,7 +48219,7 @@
         <v>45979</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48288,7 +48292,7 @@
         <v>45744</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48361,7 +48365,7 @@
         <v>45112</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48434,7 +48438,7 @@
         <v>45982</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48507,7 +48511,7 @@
         <v>46041</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48580,7 +48584,7 @@
         <v>46041</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48653,7 +48657,7 @@
         <v>45114</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48726,7 +48730,7 @@
         <v>45266</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48799,7 +48803,7 @@
         <v>45567</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48872,7 +48876,7 @@
         <v>45979</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48945,7 +48949,7 @@
         <v>45456</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49023,7 +49027,7 @@
         <v>46036</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49101,7 +49105,7 @@
         <v>46044</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49174,7 +49178,7 @@
         <v>45104</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49247,7 +49251,7 @@
         <v>46043</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49320,7 +49324,7 @@
         <v>46043</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49393,7 +49397,7 @@
         <v>45782</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49466,7 +49470,7 @@
         <v>46043</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49539,7 +49543,7 @@
         <v>46044</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49612,7 +49616,7 @@
         <v>45732</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49685,7 +49689,7 @@
         <v>44974</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49758,7 +49762,7 @@
         <v>44977</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49831,7 +49835,7 @@
         <v>45203</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49904,7 +49908,7 @@
         <v>46045</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49977,7 +49981,7 @@
         <v>45695</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50050,7 +50054,7 @@
         <v>45131</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50123,7 +50127,7 @@
         <v>46045</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50196,7 +50200,7 @@
         <v>44978</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50269,7 +50273,7 @@
         <v>46035</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50342,7 +50346,7 @@
         <v>46064</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50415,7 +50419,7 @@
         <v>46139</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50488,7 +50492,7 @@
         <v>45630</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50561,7 +50565,7 @@
         <v>44991</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50634,7 +50638,7 @@
         <v>44991</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50707,7 +50711,7 @@
         <v>46050</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50780,7 +50784,7 @@
         <v>46030</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50853,7 +50857,7 @@
         <v>46049</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50926,7 +50930,7 @@
         <v>46052</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -50999,7 +51003,7 @@
         <v>46045</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51072,7 +51076,7 @@
         <v>46051</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51145,7 +51149,7 @@
         <v>46029</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51218,7 +51222,7 @@
         <v>46056</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51291,7 +51295,7 @@
         <v>46055</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51364,7 +51368,7 @@
         <v>45030</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51437,7 +51441,7 @@
         <v>45520</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51510,7 +51514,7 @@
         <v>45537</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51583,7 +51587,7 @@
         <v>46044</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51656,7 +51660,7 @@
         <v>46146</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51729,7 +51733,7 @@
         <v>46147</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51802,7 +51806,7 @@
         <v>46148</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51880,7 +51884,7 @@
         <v>46119</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -51953,7 +51957,7 @@
         <v>46035</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52026,7 +52030,7 @@
         <v>46149</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52104,7 +52108,7 @@
         <v>46149</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52177,7 +52181,7 @@
         <v>45860</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52250,7 +52254,7 @@
         <v>46149</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52328,7 +52332,7 @@
         <v>45797</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52401,7 +52405,7 @@
         <v>46070</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52474,7 +52478,7 @@
         <v>46070</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52547,7 +52551,7 @@
         <v>46070</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52620,7 +52624,7 @@
         <v>45979</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52693,7 +52697,7 @@
         <v>45797</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52766,7 +52770,7 @@
         <v>46007</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52839,7 +52843,7 @@
         <v>46071</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52912,7 +52916,7 @@
         <v>46072</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -52985,7 +52989,7 @@
         <v>46072</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53058,7 +53062,7 @@
         <v>46092</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53131,7 +53135,7 @@
         <v>46038</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53204,7 +53208,7 @@
         <v>46072</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53277,7 +53281,7 @@
         <v>45994</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53350,7 +53354,7 @@
         <v>45877</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53423,7 +53427,7 @@
         <v>45121</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53496,7 +53500,7 @@
         <v>46044</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53569,7 +53573,7 @@
         <v>46052</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53642,7 +53646,7 @@
         <v>46155</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53720,7 +53724,7 @@
         <v>45896</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53793,7 +53797,7 @@
         <v>46043</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53866,7 +53870,7 @@
         <v>46156</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -53939,7 +53943,7 @@
         <v>46155</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54017,7 +54021,7 @@
         <v>46156</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54090,7 +54094,7 @@
         <v>45835</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54163,7 +54167,7 @@
         <v>46092</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54236,7 +54240,7 @@
         <v>45621</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54309,7 +54313,7 @@
         <v>46097</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54382,7 +54386,7 @@
         <v>46162</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54455,7 +54459,7 @@
         <v>45910</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54528,7 +54532,7 @@
         <v>46167</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54601,7 +54605,7 @@
         <v>46168</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54674,7 +54678,7 @@
         <v>46168</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54747,7 +54751,7 @@
         <v>46171</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54825,7 +54829,7 @@
         <v>46170</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54898,7 +54902,7 @@
         <v>46174</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -54971,7 +54975,7 @@
         <v>46176</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55049,7 +55053,7 @@
         <v>46127</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55122,7 +55126,7 @@
         <v>46181</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55200,7 +55204,7 @@
         <v>46035</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55273,7 +55277,7 @@
         <v>46182</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55346,7 +55350,7 @@
         <v>46182</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55419,7 +55423,7 @@
         <v>46185</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55497,7 +55501,7 @@
         <v>45257</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55570,7 +55574,7 @@
         <v>46190</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55648,7 +55652,7 @@
         <v>46191</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55726,7 +55730,7 @@
         <v>46191</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55799,7 +55803,7 @@
         <v>46191</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55872,7 +55876,7 @@
         <v>46197</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55945,7 +55949,7 @@
         <v>46196</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56018,7 +56022,7 @@
         <v>46197</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56096,7 +56100,7 @@
         <v>46197</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56174,7 +56178,7 @@
         <v>46202</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56247,7 +56251,7 @@
         <v>46024</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56320,7 +56324,7 @@
         <v>46211</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56393,7 +56397,7 @@
         <v>46211</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56466,7 +56470,7 @@
         <v>46202</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56544,7 +56548,7 @@
         <v>46216</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56622,7 +56626,7 @@
         <v>46268</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56695,7 +56699,7 @@
         <v>46167</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56773,7 +56777,7 @@
         <v>46177</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56851,7 +56855,7 @@
         <v>46177</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56929,7 +56933,7 @@
         <v>46276</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57002,7 +57006,7 @@
         <v>46233</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57080,7 +57084,7 @@
         <v>46233</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57158,7 +57162,7 @@
         <v>46281</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57231,7 +57235,7 @@
         <v>46238</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57309,7 +57313,7 @@
         <v>46241</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57387,7 +57391,7 @@
         <v>46241</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57465,7 +57469,7 @@
         <v>46288</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57538,7 +57542,7 @@
         <v>46154</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57616,7 +57620,7 @@
         <v>46287</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57694,7 +57698,7 @@
         <v>46246</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57767,7 +57771,7 @@
         <v>46286</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57845,7 +57849,7 @@
         <v>46289</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57918,7 +57922,7 @@
         <v>46135</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57996,7 +58000,7 @@
         <v>46290</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58074,7 +58078,7 @@
         <v>46286</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58152,7 +58156,7 @@
         <v>46247</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58230,7 +58234,7 @@
         <v>46290</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58303,7 +58307,7 @@
         <v>46293</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58376,7 +58380,7 @@
         <v>46248</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58454,7 +58458,7 @@
         <v>46293</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58527,7 +58531,7 @@
         <v>46127</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58605,7 +58609,7 @@
         <v>46293</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58678,7 +58682,7 @@
         <v>46294</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58751,7 +58755,7 @@
         <v>46293</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58824,7 +58828,7 @@
         <v>46240</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58902,7 +58906,7 @@
         <v>46294</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58975,7 +58979,7 @@
         <v>46249</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59053,7 +59057,7 @@
         <v>46251</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59131,7 +59135,7 @@
         <v>46251</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59209,7 +59213,7 @@
         <v>46252</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59287,7 +59291,7 @@
         <v>46252</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59360,7 +59364,7 @@
         <v>46049</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59433,7 +59437,7 @@
         <v>46297</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59506,7 +59510,7 @@
         <v>46297</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59579,7 +59583,7 @@
         <v>45890</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59657,7 +59661,7 @@
         <v>45966</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59730,7 +59734,7 @@
         <v>46252</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59803,7 +59807,7 @@
         <v>46254</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59876,7 +59880,7 @@
         <v>46259</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59949,7 +59953,7 @@
         <v>46259</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60022,7 +60026,7 @@
         <v>46259</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60100,7 +60104,7 @@
         <v>46259</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60173,7 +60177,7 @@
         <v>46188</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60246,7 +60250,7 @@
         <v>44578</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60319,7 +60323,7 @@
         <v>44652</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60392,7 +60396,7 @@
         <v>45074</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60470,7 +60474,7 @@
         <v>45257</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60543,7 +60547,7 @@
         <v>45097</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60616,7 +60620,7 @@
         <v>45351</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60694,7 +60698,7 @@
         <v>44809</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60767,7 +60771,7 @@
         <v>45097</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60840,7 +60844,7 @@
         <v>45133</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60913,7 +60917,7 @@
         <v>45446</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60991,7 +60995,7 @@
         <v>45701</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61069,7 +61073,7 @@
         <v>45701</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61147,7 +61151,7 @@
         <v>45708</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61225,7 +61229,7 @@
         <v>45799</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61298,7 +61302,7 @@
         <v>45819</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61371,7 +61375,7 @@
         <v>45824</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61444,7 +61448,7 @@
         <v>45835</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61517,7 +61521,7 @@
         <v>45904</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61590,7 +61594,7 @@
         <v>45943</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61663,7 +61667,7 @@
         <v>45964</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61741,7 +61745,7 @@
         <v>46038</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61819,7 +61823,7 @@
         <v>46043</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61892,7 +61896,7 @@
         <v>46052</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61970,7 +61974,7 @@
         <v>44649</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62043,7 +62047,7 @@
         <v>46066</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62116,7 +62120,7 @@
         <v>46076</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62189,7 +62193,7 @@
         <v>46133</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62267,7 +62271,7 @@
         <v>46134</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62340,7 +62344,7 @@
         <v>45727</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46047</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45835</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45936</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45896</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45638</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>46027</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>46166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45835</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45931</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>45632</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44869</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46097</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45637</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45254</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44829</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>45028</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45358</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45656</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45996</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45274</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>46226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>46283</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45251</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46289</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45812</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45835</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45849</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44536</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45127</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45690</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45294</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45334</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45839</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45061</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45959</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45960</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45981</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45228</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45638</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46041</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>46069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>46155</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46202</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44909</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>46287</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>46244</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45761</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45005</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45418</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>45502</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45256</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45793</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44918</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45996</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44782</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>44802</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44872</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>44570</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>44670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>44877</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>44539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44529</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44824</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>44834</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44693</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>44851</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44865</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44792</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44690</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44684</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44543</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44651</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>44777</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44862</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>44797</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44719</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45561</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45397</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>44993</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45518</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>44533</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45098</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45219</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45362</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45266</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44543</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45637</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45373</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45257</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45132</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45446</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45208</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45455</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45127</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45523</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45256</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>44915</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45302</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45037</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45015</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>44711</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44546</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44546</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45518</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45296</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45637</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45244</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45454</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44986</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45446</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45515</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45568</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45376</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45490</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45219</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45103</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45497</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45261</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45480</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45397</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44867</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45261</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45001</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45015</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45110</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45376</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45695</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44987</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45259</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45151</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45306</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45677</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44749</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45001</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45624</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44837</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45425</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45061</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45574</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45351</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45667</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45349</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45611</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45618</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45583</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45631</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45882</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44820</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45474</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44501</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45559</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45670</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45834</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45456</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45749</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44962</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45732</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45509</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45555</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45884</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45160</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45203</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45433</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45433</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45863</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45553</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45625</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>46035</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45705</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44959</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45342</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45890</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45890</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45104</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46139</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45113</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45114</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45886</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45630</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45898</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45303</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>46114</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45453</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45553</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45898</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45408</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45030</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45695</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45958</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46064</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45567</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46140</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45195</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46030</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45085</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45903</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45726</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45334</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44993</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45406</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>46036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45911</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45911</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45911</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45912</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45912</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44951</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45567</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45707</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45916</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46146</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45104</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45751</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45919</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46147</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45921</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45921</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>44994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45924</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45925</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45925</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44978</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46149</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>46119</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45197</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>46149</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>46148</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>44902</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>46149</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45929</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45877</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45932</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>46038</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45934</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45630</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45630</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45121</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>46092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45351</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45125</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45308</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45939</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44628</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45022</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45334</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>44837</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45944</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45317</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45002</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45552</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45951</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45835</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45490</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45951</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45418</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45896</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>46155</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>46155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>46043</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45952</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46052</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45955</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45994</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45706</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>44998</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44998</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46156</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>46156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45961</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45621</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45478</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45961</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45624</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45961</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45621</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45965</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45964</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45965</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45966</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>45966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45966</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45966</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45971</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44992</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45103</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45429</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45618</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45554</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45167</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45675</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45974</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45978</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45131</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45112</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45981</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45985</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45982</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45365</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45027</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45986</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45986</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>46167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45257</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45165</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45610</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45988</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45903</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45397</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46168</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45454</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45727</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45995</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45180</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45910</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46001</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46170</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45621</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45446</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>46002</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46006</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>46006</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46006</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>46006</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45623</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>46171</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>46007</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>46007</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45695</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>45113</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45127</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45127</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45160</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45127</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46010</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45664</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>46013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46174</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45667</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45198</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>46018</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46020</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45625</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>44912</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46021</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46020</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45747</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46021</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45068</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46024</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>46027</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46029</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>46029</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>46029</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>44746</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>44917</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>46035</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>44909</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45282</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>46027</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46035</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45979</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>45980</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46041</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>46041</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45979</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45982</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>46043</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45526</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46035</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45369</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46127</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46045</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46044</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>46045</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46044</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46049</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>46182</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45027</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46051</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45197</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>46050</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45608</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>46029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46055</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>46052</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46045</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46182</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46181</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46056</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45741</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45520</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>46044</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45537</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45280</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>46007</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45860</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>46035</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>45797</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>44875</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45979</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45797</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46071</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>46070</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>46070</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46072</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46072</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>44992</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>44929</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46072</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45169</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45275</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45252</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45219</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45257</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45609</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45176</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46190</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45097</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45595</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>46092</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45034</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>46191</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>46191</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>46191</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>44846</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>46097</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>46097</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>46097</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>46063</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45049</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44869</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>46101</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>46196</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>46106</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>46106</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>46112</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>46197</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>46111</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46197</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46113</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46197</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>46202</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>46119</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45264</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>46121</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45110</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45152</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>45061</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44918</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>46126</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>46127</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>45509</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>46127</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>46128</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>46127</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45096</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>46132</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>46114</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45378</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45415</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45553</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46133</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45152</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45050</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45203</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45567</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>46035</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46139</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45231</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44679</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>46024</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45345</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>46211</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>46211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45323</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>46216</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>46202</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45467</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45559</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45756</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45004</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45035</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45201</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45727</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>44987</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>46177</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45314</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46177</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45544</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46167</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45199</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45001</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46276</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46233</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>44792</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45334</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44714</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>44785</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>44985</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45509</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45093</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>46281</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>45169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>46238</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>44909</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>45112</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45558</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>45647</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>46154</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>45267</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>45744</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>45261</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>45261</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>44967</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>46241</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>44574</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52085,7 +52085,7 @@
         <v>45244</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>46241</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>46287</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45231</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>46288</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>46289</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45049</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45109</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45266</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45595</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>46246</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>46293</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>46293</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45216</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>46135</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>46293</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>46293</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>46286</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>46248</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>45076</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>46290</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>46286</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45296</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>46240</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>44890</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>46247</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45255</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45293</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45307</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54325,7 +54325,7 @@
         <v>45131</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>46249</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>46127</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>44643</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46251</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>46294</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>44974</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45216</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>46252</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55002,7 +55002,7 @@
         <v>45200</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         <v>46252</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>46251</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46294</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45568</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46297</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45727</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>44714</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>45447</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45266</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45267</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>44991</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>44991</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45890</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>46297</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56112,7 +56112,7 @@
         <v>46254</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>46252</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45202</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45428</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45776</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>45779</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>45170</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>46049</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45376</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45646</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45966</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         <v>45266</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>45015</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45350</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45787</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>46259</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>46259</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45524</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46259</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45790</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45596</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>45574</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45790</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46259</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>46114</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>45796</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>44971</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>46188</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45240</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>45558</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>45114</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46308</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46308</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>44731</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>45812</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45813</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45817</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45818</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45818</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>45818</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>45820</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45825</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45821</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>45827</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46268</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>45833</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45832</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45835</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>45839</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>45847</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>45849</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>45561</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45849</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60036,7 +60036,7 @@
         <v>45863</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>45863</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45881</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60260,7 +60260,7 @@
         <v>45428</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60333,7 +60333,7 @@
         <v>45074</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>44578</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60484,7 +60484,7 @@
         <v>45257</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45097</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>45351</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60708,7 +60708,7 @@
         <v>44809</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45097</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45133</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>44652</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61000,7 +61000,7 @@
         <v>45446</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45701</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45701</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>45708</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45799</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61385,7 +61385,7 @@
         <v>45819</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>45824</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61531,7 +61531,7 @@
         <v>45835</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>45904</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>45943</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45964</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61828,7 +61828,7 @@
         <v>46038</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>46043</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
         <v>46052</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>44649</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>46066</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62203,7 +62203,7 @@
         <v>46076</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>46133</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>46134</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45727</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>44977</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>45841</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>46047</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
         <v>45835</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2123,7 +2123,7 @@
         <v>45854</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2249,7 +2249,7 @@
         <v>45875</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>46237</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45715</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>46286</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>45936</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>45827</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>45272</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>44992</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3199,7 +3199,7 @@
         <v>46178</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45489</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45896</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45334</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3776,7 +3776,7 @@
         <v>45632</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3886,7 +3886,7 @@
         <v>45638</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3995,7 +3995,7 @@
         <v>45988</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4104,7 +4104,7 @@
         <v>46027</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>46166</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4326,7 +4326,7 @@
         <v>45835</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4443,7 +4443,7 @@
         <v>45272</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4556,7 +4556,7 @@
         <v>45931</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4664,7 +4664,7 @@
         <v>45632</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44869</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45901</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>46097</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5111,7 +5111,7 @@
         <v>45637</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5218,7 +5218,7 @@
         <v>46237</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5329,7 +5329,7 @@
         <v>45254</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5435,7 +5435,7 @@
         <v>45251</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5541,7 +5541,7 @@
         <v>44829</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5651,7 +5651,7 @@
         <v>45890</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>45028</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5863,7 +5863,7 @@
         <v>45358</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5969,7 +5969,7 @@
         <v>45656</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         <v>45996</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>46027</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6287,7 +6287,7 @@
         <v>45274</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6397,7 +6397,7 @@
         <v>46226</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6508,7 +6508,7 @@
         <v>46283</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>45251</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44602</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6844,7 +6844,7 @@
         <v>46289</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6959,7 +6959,7 @@
         <v>45754</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7069,7 +7069,7 @@
         <v>45812</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7175,7 +7175,7 @@
         <v>45835</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7285,7 +7285,7 @@
         <v>45849</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>44536</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7496,7 +7496,7 @@
         <v>44869</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7606,7 +7606,7 @@
         <v>44509</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7720,7 +7720,7 @@
         <v>44735</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7825,7 +7825,7 @@
         <v>44761</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7934,7 +7934,7 @@
         <v>45110</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8039,7 +8039,7 @@
         <v>45127</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8148,7 +8148,7 @@
         <v>45690</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>45621</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>44588</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8467,7 +8467,7 @@
         <v>45294</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>45334</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8681,7 +8681,7 @@
         <v>45839</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>45016</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>45061</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
         <v>45959</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9110,7 +9110,7 @@
         <v>45960</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9220,7 +9220,7 @@
         <v>45981</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9325,7 +9325,7 @@
         <v>45228</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9434,7 +9434,7 @@
         <v>45638</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>46041</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9648,7 +9648,7 @@
         <v>46069</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9753,7 +9753,7 @@
         <v>44750</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9867,7 +9867,7 @@
         <v>44973</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9972,7 +9972,7 @@
         <v>46155</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10086,7 +10086,7 @@
         <v>46120</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>46202</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10300,7 +10300,7 @@
         <v>44909</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>44992</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10518,7 +10518,7 @@
         <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10623,7 +10623,7 @@
         <v>46287</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10733,7 +10733,7 @@
         <v>46244</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10838,7 +10838,7 @@
         <v>45761</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>45005</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>45418</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>45502</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11262,7 +11262,7 @@
         <v>45256</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45793</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
         <v>44918</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11577,7 +11577,7 @@
         <v>45181</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11682,7 +11682,7 @@
         <v>45996</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11792,7 +11792,7 @@
         <v>44782</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44491</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11938,7 +11938,7 @@
         <v>44834</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -12011,7 +12011,7 @@
         <v>44802</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44671</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12162,7 +12162,7 @@
         <v>44872</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44512</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>44869</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12391,7 +12391,7 @@
         <v>44570</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12464,7 +12464,7 @@
         <v>44670</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12537,7 +12537,7 @@
         <v>44488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12610,7 +12610,7 @@
         <v>44877</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12683,7 +12683,7 @@
         <v>44539</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12756,7 +12756,7 @@
         <v>44529</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12829,7 +12829,7 @@
         <v>44824</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12902,7 +12902,7 @@
         <v>44834</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12975,7 +12975,7 @@
         <v>44693</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -13048,7 +13048,7 @@
         <v>44503</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13121,7 +13121,7 @@
         <v>44533</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13194,7 +13194,7 @@
         <v>44851</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13267,7 +13267,7 @@
         <v>44865</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13345,7 +13345,7 @@
         <v>44792</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13418,7 +13418,7 @@
         <v>44690</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44684</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13574,7 +13574,7 @@
         <v>44543</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13647,7 +13647,7 @@
         <v>44651</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13720,7 +13720,7 @@
         <v>44777</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13793,7 +13793,7 @@
         <v>44862</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13866,7 +13866,7 @@
         <v>44797</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13939,7 +13939,7 @@
         <v>44533</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -14012,7 +14012,7 @@
         <v>44719</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>45561</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45103</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14231,7 +14231,7 @@
         <v>44846</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45397</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14377,7 +14377,7 @@
         <v>45425</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>44993</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45518</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14596,7 +14596,7 @@
         <v>44533</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14669,7 +14669,7 @@
         <v>45098</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14742,7 +14742,7 @@
         <v>45219</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14815,7 +14815,7 @@
         <v>45362</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14888,7 +14888,7 @@
         <v>45266</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44543</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -15039,7 +15039,7 @@
         <v>45637</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45373</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15185,7 +15185,7 @@
         <v>45161</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15258,7 +15258,7 @@
         <v>45510</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>45257</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15404,7 +15404,7 @@
         <v>45132</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15477,7 +15477,7 @@
         <v>45446</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15555,7 +15555,7 @@
         <v>45208</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15633,7 +15633,7 @@
         <v>44929</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15711,7 +15711,7 @@
         <v>45455</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15789,7 +15789,7 @@
         <v>45127</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15862,7 +15862,7 @@
         <v>45261</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15935,7 +15935,7 @@
         <v>45523</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -16008,7 +16008,7 @@
         <v>45476</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16081,7 +16081,7 @@
         <v>45264</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16154,7 +16154,7 @@
         <v>45256</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16227,7 +16227,7 @@
         <v>45044</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16300,7 +16300,7 @@
         <v>44915</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>45302</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44978</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16519,7 +16519,7 @@
         <v>45037</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16592,7 +16592,7 @@
         <v>45015</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16665,7 +16665,7 @@
         <v>45608</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16738,7 +16738,7 @@
         <v>44711</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16816,7 +16816,7 @@
         <v>44546</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16889,7 +16889,7 @@
         <v>44546</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45518</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -17035,7 +17035,7 @@
         <v>45296</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17108,7 +17108,7 @@
         <v>45637</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17181,7 +17181,7 @@
         <v>45154</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44580</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>45230</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17400,7 +17400,7 @@
         <v>45244</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17473,7 +17473,7 @@
         <v>45454</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>44986</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17619,7 +17619,7 @@
         <v>45446</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17692,7 +17692,7 @@
         <v>45515</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17765,7 +17765,7 @@
         <v>45568</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17838,7 +17838,7 @@
         <v>45376</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17911,7 +17911,7 @@
         <v>45198</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17984,7 +17984,7 @@
         <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -18057,7 +18057,7 @@
         <v>45490</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18130,7 +18130,7 @@
         <v>45103</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>45219</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18281,7 +18281,7 @@
         <v>45103</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18359,7 +18359,7 @@
         <v>45497</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>45261</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>45258</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18583,7 +18583,7 @@
         <v>45480</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18656,7 +18656,7 @@
         <v>45183</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18729,7 +18729,7 @@
         <v>45397</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18802,7 +18802,7 @@
         <v>44867</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18875,7 +18875,7 @@
         <v>45260</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18948,7 +18948,7 @@
         <v>44966</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -19021,7 +19021,7 @@
         <v>45261</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19094,7 +19094,7 @@
         <v>45001</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19167,7 +19167,7 @@
         <v>45015</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45110</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45027</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19386,7 +19386,7 @@
         <v>45376</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19459,7 +19459,7 @@
         <v>45232</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19532,7 +19532,7 @@
         <v>45695</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44987</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19678,7 +19678,7 @@
         <v>45259</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19751,7 +19751,7 @@
         <v>45151</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19824,7 +19824,7 @@
         <v>45306</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45677</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44749</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45001</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45624</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20194,7 +20194,7 @@
         <v>45510</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20267,7 +20267,7 @@
         <v>44837</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20340,7 +20340,7 @@
         <v>45425</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20413,7 +20413,7 @@
         <v>45061</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20486,7 +20486,7 @@
         <v>45574</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20559,7 +20559,7 @@
         <v>45351</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>45667</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>45349</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20778,7 +20778,7 @@
         <v>45611</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20851,7 +20851,7 @@
         <v>45618</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20924,7 +20924,7 @@
         <v>45583</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>45567</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21070,7 +21070,7 @@
         <v>45036</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>45631</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21216,7 +21216,7 @@
         <v>45882</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21289,7 +21289,7 @@
         <v>46106</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21362,7 +21362,7 @@
         <v>45803</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>44820</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21508,7 +21508,7 @@
         <v>45474</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45782</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>44501</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21727,7 +21727,7 @@
         <v>45559</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21800,7 +21800,7 @@
         <v>45670</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21873,7 +21873,7 @@
         <v>45834</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45456</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45749</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>44962</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22175,7 +22175,7 @@
         <v>45732</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22248,7 +22248,7 @@
         <v>45509</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22321,7 +22321,7 @@
         <v>44974</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22394,7 +22394,7 @@
         <v>44992</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22467,7 +22467,7 @@
         <v>45555</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22540,7 +22540,7 @@
         <v>45884</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22613,7 +22613,7 @@
         <v>45160</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22686,7 +22686,7 @@
         <v>45203</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22759,7 +22759,7 @@
         <v>45433</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22832,7 +22832,7 @@
         <v>45433</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22905,7 +22905,7 @@
         <v>45863</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22978,7 +22978,7 @@
         <v>45553</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45625</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23129,7 +23129,7 @@
         <v>46035</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23202,7 +23202,7 @@
         <v>45705</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23275,7 +23275,7 @@
         <v>44959</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45342</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23426,7 +23426,7 @@
         <v>45890</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>45890</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23572,7 +23572,7 @@
         <v>45104</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>46139</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45113</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23791,7 +23791,7 @@
         <v>45114</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23864,7 +23864,7 @@
         <v>45901</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23942,7 +23942,7 @@
         <v>45886</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45630</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24088,7 +24088,7 @@
         <v>45898</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24166,7 +24166,7 @@
         <v>45898</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24244,7 +24244,7 @@
         <v>45303</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24317,7 +24317,7 @@
         <v>46114</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24395,7 +24395,7 @@
         <v>45453</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24468,7 +24468,7 @@
         <v>45553</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24546,7 +24546,7 @@
         <v>45898</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>45408</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24697,7 +24697,7 @@
         <v>45030</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>45695</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>45958</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24916,7 +24916,7 @@
         <v>46064</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45567</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -25062,7 +25062,7 @@
         <v>46140</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25135,7 +25135,7 @@
         <v>45195</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>46030</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25281,7 +25281,7 @@
         <v>45085</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25354,7 +25354,7 @@
         <v>45903</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45726</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25500,7 +25500,7 @@
         <v>45334</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25573,7 +25573,7 @@
         <v>44993</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45406</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25719,7 +25719,7 @@
         <v>46036</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45911</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25870,7 +25870,7 @@
         <v>45911</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>45911</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -26016,7 +26016,7 @@
         <v>45912</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26094,7 +26094,7 @@
         <v>45912</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26167,7 +26167,7 @@
         <v>44951</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45567</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26313,7 +26313,7 @@
         <v>45915</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26386,7 +26386,7 @@
         <v>45912</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26459,7 +26459,7 @@
         <v>45707</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>45916</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45917</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>46146</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26751,7 +26751,7 @@
         <v>45104</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26829,7 +26829,7 @@
         <v>45751</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26902,7 +26902,7 @@
         <v>45919</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26975,7 +26975,7 @@
         <v>46147</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45921</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27121,7 +27121,7 @@
         <v>45921</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27194,7 +27194,7 @@
         <v>44994</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27267,7 +27267,7 @@
         <v>45924</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27340,7 +27340,7 @@
         <v>45925</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27413,7 +27413,7 @@
         <v>45925</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27486,7 +27486,7 @@
         <v>44978</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27559,7 +27559,7 @@
         <v>46149</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27632,7 +27632,7 @@
         <v>46119</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27705,7 +27705,7 @@
         <v>45197</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27778,7 +27778,7 @@
         <v>46149</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>46148</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27934,7 +27934,7 @@
         <v>44902</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -28007,7 +28007,7 @@
         <v>46149</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45929</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28158,7 +28158,7 @@
         <v>45877</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28231,7 +28231,7 @@
         <v>45932</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28309,7 +28309,7 @@
         <v>45932</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28387,7 +28387,7 @@
         <v>46038</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28460,7 +28460,7 @@
         <v>45934</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28533,7 +28533,7 @@
         <v>45630</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28606,7 +28606,7 @@
         <v>45630</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28679,7 +28679,7 @@
         <v>45121</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28752,7 +28752,7 @@
         <v>46092</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28825,7 +28825,7 @@
         <v>45351</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>45125</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28976,7 +28976,7 @@
         <v>45308</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29049,7 +29049,7 @@
         <v>45939</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29127,7 +29127,7 @@
         <v>45937</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45937</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29273,7 +29273,7 @@
         <v>44628</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>45558</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29419,7 +29419,7 @@
         <v>45022</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29492,7 +29492,7 @@
         <v>45334</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>44837</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45944</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45317</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29789,7 +29789,7 @@
         <v>45946</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29862,7 +29862,7 @@
         <v>45002</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29935,7 +29935,7 @@
         <v>45552</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -30008,7 +30008,7 @@
         <v>45951</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30086,7 +30086,7 @@
         <v>45835</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30159,7 +30159,7 @@
         <v>45490</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45951</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30310,7 +30310,7 @@
         <v>44959</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30383,7 +30383,7 @@
         <v>45418</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30456,7 +30456,7 @@
         <v>45896</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>46155</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>46155</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30685,7 +30685,7 @@
         <v>46043</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30758,7 +30758,7 @@
         <v>45952</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30831,7 +30831,7 @@
         <v>46052</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30904,7 +30904,7 @@
         <v>45955</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45994</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>46044</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31123,7 +31123,7 @@
         <v>45706</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31196,7 +31196,7 @@
         <v>44998</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31269,7 +31269,7 @@
         <v>44998</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>46156</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31415,7 +31415,7 @@
         <v>45958</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>46156</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31561,7 +31561,7 @@
         <v>45961</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31634,7 +31634,7 @@
         <v>45621</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31707,7 +31707,7 @@
         <v>45478</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31780,7 +31780,7 @@
         <v>45961</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31853,7 +31853,7 @@
         <v>45624</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31926,7 +31926,7 @@
         <v>45960</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31999,7 +31999,7 @@
         <v>45961</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>45621</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32145,7 +32145,7 @@
         <v>45965</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32223,7 +32223,7 @@
         <v>45964</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32296,7 +32296,7 @@
         <v>45964</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32369,7 +32369,7 @@
         <v>45964</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32442,7 +32442,7 @@
         <v>45964</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32515,7 +32515,7 @@
         <v>45965</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32588,7 +32588,7 @@
         <v>45966</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32661,7 +32661,7 @@
         <v>45966</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32734,7 +32734,7 @@
         <v>45966</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32807,7 +32807,7 @@
         <v>45966</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45966</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32953,7 +32953,7 @@
         <v>45966</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33026,7 +33026,7 @@
         <v>45971</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33099,7 +33099,7 @@
         <v>44992</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33172,7 +33172,7 @@
         <v>45103</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45429</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33318,7 +33318,7 @@
         <v>45618</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45554</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33469,7 +33469,7 @@
         <v>45167</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33542,7 +33542,7 @@
         <v>46162</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33615,7 +33615,7 @@
         <v>45972</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>44974</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33761,7 +33761,7 @@
         <v>44974</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33834,7 +33834,7 @@
         <v>45675</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33907,7 +33907,7 @@
         <v>45975</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45974</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45974</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34131,7 +34131,7 @@
         <v>45978</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34204,7 +34204,7 @@
         <v>45131</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34277,7 +34277,7 @@
         <v>45112</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34350,7 +34350,7 @@
         <v>45981</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45985</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34496,7 +34496,7 @@
         <v>45985</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34569,7 +34569,7 @@
         <v>45985</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34642,7 +34642,7 @@
         <v>45985</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34715,7 +34715,7 @@
         <v>45982</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45365</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34861,7 +34861,7 @@
         <v>45027</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34934,7 +34934,7 @@
         <v>45986</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -35007,7 +35007,7 @@
         <v>45986</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35080,7 +35080,7 @@
         <v>46167</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35153,7 +35153,7 @@
         <v>45257</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35231,7 +35231,7 @@
         <v>45165</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>45610</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45988</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35450,7 +35450,7 @@
         <v>45903</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45988</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35626,7 +35626,7 @@
         <v>45397</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>46168</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35772,7 +35772,7 @@
         <v>45454</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>46168</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35918,7 +35918,7 @@
         <v>45993</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35991,7 +35991,7 @@
         <v>45169</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36064,7 +36064,7 @@
         <v>45727</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36137,7 +36137,7 @@
         <v>45995</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36210,7 +36210,7 @@
         <v>45180</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45910</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>46001</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36429,7 +36429,7 @@
         <v>46170</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>45621</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36575,7 +36575,7 @@
         <v>45446</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36653,7 +36653,7 @@
         <v>46002</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36726,7 +36726,7 @@
         <v>46006</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36799,7 +36799,7 @@
         <v>46006</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36872,7 +36872,7 @@
         <v>46006</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36945,7 +36945,7 @@
         <v>46006</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>45623</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>46171</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37169,7 +37169,7 @@
         <v>46007</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37242,7 +37242,7 @@
         <v>46007</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45695</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37388,7 +37388,7 @@
         <v>45113</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37461,7 +37461,7 @@
         <v>45127</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37534,7 +37534,7 @@
         <v>45127</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37607,7 +37607,7 @@
         <v>45160</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37680,7 +37680,7 @@
         <v>45127</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>46010</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37826,7 +37826,7 @@
         <v>45664</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>46010</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37972,7 +37972,7 @@
         <v>46013</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38045,7 +38045,7 @@
         <v>46174</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45608</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38191,7 +38191,7 @@
         <v>45667</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38264,7 +38264,7 @@
         <v>45198</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38337,7 +38337,7 @@
         <v>46018</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>46020</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>45625</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>44912</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>46021</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46020</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45747</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>46021</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38921,7 +38921,7 @@
         <v>45068</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38994,7 +38994,7 @@
         <v>46024</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39067,7 +39067,7 @@
         <v>46027</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39140,7 +39140,7 @@
         <v>46029</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>46029</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>46029</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39359,7 +39359,7 @@
         <v>44746</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39432,7 +39432,7 @@
         <v>44917</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>46035</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39578,7 +39578,7 @@
         <v>44909</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39651,7 +39651,7 @@
         <v>45282</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39724,7 +39724,7 @@
         <v>46027</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39797,7 +39797,7 @@
         <v>46035</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39870,7 +39870,7 @@
         <v>45979</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39943,7 +39943,7 @@
         <v>45980</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40016,7 +40016,7 @@
         <v>46041</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>46041</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40162,7 +40162,7 @@
         <v>45979</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40235,7 +40235,7 @@
         <v>45982</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40308,7 +40308,7 @@
         <v>46043</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>46043</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40454,7 +40454,7 @@
         <v>46043</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>45526</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40600,7 +40600,7 @@
         <v>46035</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45369</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40746,7 +40746,7 @@
         <v>46127</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40819,7 +40819,7 @@
         <v>46045</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40892,7 +40892,7 @@
         <v>46044</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -40965,7 +40965,7 @@
         <v>46045</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41038,7 +41038,7 @@
         <v>46044</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41111,7 +41111,7 @@
         <v>46049</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41184,7 +41184,7 @@
         <v>46182</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41257,7 +41257,7 @@
         <v>45027</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41330,7 +41330,7 @@
         <v>46051</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41403,7 +41403,7 @@
         <v>45197</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41476,7 +41476,7 @@
         <v>46050</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41549,7 +41549,7 @@
         <v>45608</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41622,7 +41622,7 @@
         <v>46029</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>46055</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41768,7 +41768,7 @@
         <v>46052</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41841,7 +41841,7 @@
         <v>46045</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41914,7 +41914,7 @@
         <v>46182</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -41987,7 +41987,7 @@
         <v>46181</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42065,7 +42065,7 @@
         <v>46056</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>45741</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42211,7 +42211,7 @@
         <v>45520</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>46044</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42357,7 +42357,7 @@
         <v>45537</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42430,7 +42430,7 @@
         <v>45280</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42503,7 +42503,7 @@
         <v>46007</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42576,7 +42576,7 @@
         <v>45860</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42649,7 +42649,7 @@
         <v>46035</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42722,7 +42722,7 @@
         <v>45797</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42795,7 +42795,7 @@
         <v>44875</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42868,7 +42868,7 @@
         <v>45979</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -42941,7 +42941,7 @@
         <v>45797</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>46185</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43092,7 +43092,7 @@
         <v>46071</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43165,7 +43165,7 @@
         <v>46070</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43238,7 +43238,7 @@
         <v>46070</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43311,7 +43311,7 @@
         <v>46070</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43384,7 +43384,7 @@
         <v>46072</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>46072</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43530,7 +43530,7 @@
         <v>44992</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>44929</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43681,7 +43681,7 @@
         <v>46072</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43754,7 +43754,7 @@
         <v>45169</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43827,7 +43827,7 @@
         <v>45275</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43900,7 +43900,7 @@
         <v>45252</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>45219</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44046,7 +44046,7 @@
         <v>45257</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45609</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44192,7 +44192,7 @@
         <v>45176</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44265,7 +44265,7 @@
         <v>46190</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44343,7 +44343,7 @@
         <v>45097</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44416,7 +44416,7 @@
         <v>45595</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44489,7 +44489,7 @@
         <v>46092</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44562,7 +44562,7 @@
         <v>45034</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44635,7 +44635,7 @@
         <v>46191</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44708,7 +44708,7 @@
         <v>46191</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44786,7 +44786,7 @@
         <v>46191</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44859,7 +44859,7 @@
         <v>44846</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -44932,7 +44932,7 @@
         <v>46097</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45005,7 +45005,7 @@
         <v>46097</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>46097</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45151,7 +45151,7 @@
         <v>46063</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45224,7 +45224,7 @@
         <v>45049</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45297,7 +45297,7 @@
         <v>44869</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45375,7 +45375,7 @@
         <v>46101</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45448,7 +45448,7 @@
         <v>46196</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45521,7 +45521,7 @@
         <v>46106</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>46106</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45672,7 +45672,7 @@
         <v>46112</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>46197</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45823,7 +45823,7 @@
         <v>46111</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45901,7 +45901,7 @@
         <v>46197</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -45979,7 +45979,7 @@
         <v>46113</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46052,7 +46052,7 @@
         <v>46197</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46130,7 +46130,7 @@
         <v>45357</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46203,7 +46203,7 @@
         <v>46202</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46276,7 +46276,7 @@
         <v>46119</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>45264</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>46121</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46500,7 +46500,7 @@
         <v>45110</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46573,7 +46573,7 @@
         <v>45152</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46646,7 +46646,7 @@
         <v>45061</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46719,7 +46719,7 @@
         <v>44918</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46792,7 +46792,7 @@
         <v>46126</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46865,7 +46865,7 @@
         <v>46127</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -46943,7 +46943,7 @@
         <v>45509</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47016,7 +47016,7 @@
         <v>46127</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>46128</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47167,7 +47167,7 @@
         <v>46127</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47245,7 +47245,7 @@
         <v>45096</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47318,7 +47318,7 @@
         <v>46132</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>46114</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47469,7 +47469,7 @@
         <v>45378</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47542,7 +47542,7 @@
         <v>45415</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47615,7 +47615,7 @@
         <v>45553</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47693,7 +47693,7 @@
         <v>46133</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47766,7 +47766,7 @@
         <v>45152</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>45050</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47912,7 +47912,7 @@
         <v>45203</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -47985,7 +47985,7 @@
         <v>45567</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48063,7 +48063,7 @@
         <v>46035</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48136,7 +48136,7 @@
         <v>46139</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48209,7 +48209,7 @@
         <v>45231</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48282,7 +48282,7 @@
         <v>45272</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48355,7 +48355,7 @@
         <v>44679</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48433,7 +48433,7 @@
         <v>46024</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48506,7 +48506,7 @@
         <v>45345</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48579,7 +48579,7 @@
         <v>46211</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>46211</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48725,7 +48725,7 @@
         <v>45323</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48798,7 +48798,7 @@
         <v>46216</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>46202</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>45467</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49027,7 +49027,7 @@
         <v>45559</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45756</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49173,7 +49173,7 @@
         <v>45004</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49246,7 +49246,7 @@
         <v>45035</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49319,7 +49319,7 @@
         <v>45201</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49392,7 +49392,7 @@
         <v>45727</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49470,7 +49470,7 @@
         <v>44987</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49543,7 +49543,7 @@
         <v>46177</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49621,7 +49621,7 @@
         <v>45314</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49694,7 +49694,7 @@
         <v>46177</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49772,7 +49772,7 @@
         <v>45544</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49845,7 +49845,7 @@
         <v>46167</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49923,7 +49923,7 @@
         <v>45199</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -49996,7 +49996,7 @@
         <v>45001</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50069,7 +50069,7 @@
         <v>46276</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50142,7 +50142,7 @@
         <v>46233</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50220,7 +50220,7 @@
         <v>44792</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50293,7 +50293,7 @@
         <v>45334</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45607</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50449,7 +50449,7 @@
         <v>44714</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50527,7 +50527,7 @@
         <v>46233</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>44785</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>44985</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50751,7 +50751,7 @@
         <v>45509</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50824,7 +50824,7 @@
         <v>45093</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50897,7 +50897,7 @@
         <v>45167</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50970,7 +50970,7 @@
         <v>46281</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51043,7 +51043,7 @@
         <v>45169</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>46238</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51194,7 +51194,7 @@
         <v>44909</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51267,7 +51267,7 @@
         <v>45112</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45558</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51413,7 +51413,7 @@
         <v>45647</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51486,7 +51486,7 @@
         <v>46154</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51564,7 +51564,7 @@
         <v>45267</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51637,7 +51637,7 @@
         <v>45744</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51710,7 +51710,7 @@
         <v>45261</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51783,7 +51783,7 @@
         <v>45261</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51856,7 +51856,7 @@
         <v>44967</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51934,7 +51934,7 @@
         <v>46241</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52012,7 +52012,7 @@
         <v>44574</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52085,7 +52085,7 @@
         <v>45244</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52158,7 +52158,7 @@
         <v>46241</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52236,7 +52236,7 @@
         <v>46287</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52314,7 +52314,7 @@
         <v>45231</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52392,7 +52392,7 @@
         <v>46288</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52465,7 +52465,7 @@
         <v>46289</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52538,7 +52538,7 @@
         <v>45049</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52611,7 +52611,7 @@
         <v>45109</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52684,7 +52684,7 @@
         <v>45266</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52757,7 +52757,7 @@
         <v>45595</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52830,7 +52830,7 @@
         <v>46246</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52903,7 +52903,7 @@
         <v>46293</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52976,7 +52976,7 @@
         <v>46293</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53049,7 +53049,7 @@
         <v>45216</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53122,7 +53122,7 @@
         <v>46135</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53200,7 +53200,7 @@
         <v>46293</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53273,7 +53273,7 @@
         <v>46293</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53346,7 +53346,7 @@
         <v>46286</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53424,7 +53424,7 @@
         <v>46290</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>46248</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53580,7 +53580,7 @@
         <v>45076</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53653,7 +53653,7 @@
         <v>46290</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53726,7 +53726,7 @@
         <v>46286</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53804,7 +53804,7 @@
         <v>45296</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53877,7 +53877,7 @@
         <v>46240</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53955,7 +53955,7 @@
         <v>44890</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54028,7 +54028,7 @@
         <v>46247</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54106,7 +54106,7 @@
         <v>45255</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45293</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54252,7 +54252,7 @@
         <v>45307</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54325,7 +54325,7 @@
         <v>45131</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54398,7 +54398,7 @@
         <v>46249</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54476,7 +54476,7 @@
         <v>46127</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54554,7 +54554,7 @@
         <v>44643</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54627,7 +54627,7 @@
         <v>46251</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54705,7 +54705,7 @@
         <v>46294</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54778,7 +54778,7 @@
         <v>44974</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54851,7 +54851,7 @@
         <v>45216</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54924,7 +54924,7 @@
         <v>46252</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -55002,7 +55002,7 @@
         <v>45200</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55075,7 +55075,7 @@
         <v>46252</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55148,7 +55148,7 @@
         <v>46251</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55226,7 +55226,7 @@
         <v>46294</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55299,7 +55299,7 @@
         <v>45568</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55372,7 +55372,7 @@
         <v>46297</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55445,7 +55445,7 @@
         <v>45727</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55518,7 +55518,7 @@
         <v>44714</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55596,7 +55596,7 @@
         <v>45447</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55669,7 +55669,7 @@
         <v>45266</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55742,7 +55742,7 @@
         <v>45267</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55815,7 +55815,7 @@
         <v>44991</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55888,7 +55888,7 @@
         <v>44991</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55961,7 +55961,7 @@
         <v>45890</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -56039,7 +56039,7 @@
         <v>46297</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56112,7 +56112,7 @@
         <v>46254</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56185,7 +56185,7 @@
         <v>46252</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56258,7 +56258,7 @@
         <v>45202</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45428</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56404,7 +56404,7 @@
         <v>45776</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56482,7 +56482,7 @@
         <v>45779</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56555,7 +56555,7 @@
         <v>45170</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56633,7 +56633,7 @@
         <v>46049</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56706,7 +56706,7 @@
         <v>45376</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56779,7 +56779,7 @@
         <v>45646</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56852,7 +56852,7 @@
         <v>45966</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56925,7 +56925,7 @@
         <v>45266</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56998,7 +56998,7 @@
         <v>45015</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57071,7 +57071,7 @@
         <v>45350</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57144,7 +57144,7 @@
         <v>45787</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57217,7 +57217,7 @@
         <v>46259</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57290,7 +57290,7 @@
         <v>46259</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57368,7 +57368,7 @@
         <v>45524</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57441,7 +57441,7 @@
         <v>46259</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57514,7 +57514,7 @@
         <v>45790</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57587,7 +57587,7 @@
         <v>45596</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57660,7 +57660,7 @@
         <v>45574</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57733,7 +57733,7 @@
         <v>45790</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57806,7 +57806,7 @@
         <v>46259</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57879,7 +57879,7 @@
         <v>46114</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57957,7 +57957,7 @@
         <v>45796</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -58030,7 +58030,7 @@
         <v>44971</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58103,7 +58103,7 @@
         <v>46188</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45240</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58249,7 +58249,7 @@
         <v>45558</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58322,7 +58322,7 @@
         <v>45114</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58395,7 +58395,7 @@
         <v>46308</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58473,7 +58473,7 @@
         <v>46308</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58551,7 +58551,7 @@
         <v>44731</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58624,7 +58624,7 @@
         <v>45812</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58702,7 +58702,7 @@
         <v>45813</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58775,7 +58775,7 @@
         <v>45817</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58848,7 +58848,7 @@
         <v>45818</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58921,7 +58921,7 @@
         <v>45818</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58999,7 +58999,7 @@
         <v>45818</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59072,7 +59072,7 @@
         <v>45820</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59145,7 +59145,7 @@
         <v>45825</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59218,7 +59218,7 @@
         <v>45821</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59291,7 +59291,7 @@
         <v>45827</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59364,7 +59364,7 @@
         <v>46268</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59437,7 +59437,7 @@
         <v>45833</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59510,7 +59510,7 @@
         <v>45832</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59583,7 +59583,7 @@
         <v>45835</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59656,7 +59656,7 @@
         <v>45839</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59729,7 +59729,7 @@
         <v>45847</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59802,7 +59802,7 @@
         <v>45849</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59880,7 +59880,7 @@
         <v>45561</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59958,7 +59958,7 @@
         <v>45849</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -60036,7 +60036,7 @@
         <v>45863</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60114,7 +60114,7 @@
         <v>45863</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45881</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60260,7 +60260,7 @@
         <v>45428</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60333,7 +60333,7 @@
         <v>45074</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60411,7 +60411,7 @@
         <v>44578</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60484,7 +60484,7 @@
         <v>45257</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60557,7 +60557,7 @@
         <v>45097</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60630,7 +60630,7 @@
         <v>45351</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60708,7 +60708,7 @@
         <v>44809</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60781,7 +60781,7 @@
         <v>45097</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60854,7 +60854,7 @@
         <v>45133</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60927,7 +60927,7 @@
         <v>44652</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -61000,7 +61000,7 @@
         <v>45446</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -61078,7 +61078,7 @@
         <v>45701</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61156,7 +61156,7 @@
         <v>45701</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61234,7 +61234,7 @@
         <v>45708</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61312,7 +61312,7 @@
         <v>45799</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61385,7 +61385,7 @@
         <v>45819</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61458,7 +61458,7 @@
         <v>45824</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61531,7 +61531,7 @@
         <v>45835</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61604,7 +61604,7 @@
         <v>45904</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61677,7 +61677,7 @@
         <v>45943</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61750,7 +61750,7 @@
         <v>45964</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61828,7 +61828,7 @@
         <v>46038</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61906,7 +61906,7 @@
         <v>46043</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61979,7 +61979,7 @@
         <v>46052</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -62057,7 +62057,7 @@
         <v>44649</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62130,7 +62130,7 @@
         <v>46066</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62203,7 +62203,7 @@
         <v>46076</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62276,7 +62276,7 @@
         <v>46133</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>46134</v>
       </c>
       <c r="E785" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
@@ -62427,7 +62427,7 @@
         <v>45727</v>
       </c>
       <c r="E786" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45841</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44977</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>45835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45854</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45875</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45715</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>46286</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>45827</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45936</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>44992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>45896</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45632</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45632</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>46097</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>46237</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45637</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45254</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>46226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>46027</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>46289</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45835</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45849</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45656</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>44829</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45358</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45028</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44735</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45005</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>45110</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45839</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45418</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45959</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45960</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>46155</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45228</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45502</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45256</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45793</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46287</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46041</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>46244</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>46069</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44973</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46120</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>44918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45294</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45690</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44992</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45761</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45127</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45621</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45638</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45061</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45181</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44834</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44802</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44512</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44869</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44570</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44670</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44877</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44539</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44529</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44693</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44503</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44851</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44690</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44684</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44543</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44777</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44651</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44862</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44797</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44533</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45428</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45050</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45351</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45886</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44746</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45160</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45890</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45890</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44987</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45334</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45308</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45257</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>45345</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>45898</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45378</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45901</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45342</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45230</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45912</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45621</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45911</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45568</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45911</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45912</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45912</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45911</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45618</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>46162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45915</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44918</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45919</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45921</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45637</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45910</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45397</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45921</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44533</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45112</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45924</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45114</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46167</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45104</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46168</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45925</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45925</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45929</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45208</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44974</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44977</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45932</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45932</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>46171</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46170</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45203</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45934</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45131</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45630</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45630</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45937</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45937</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>44991</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>44991</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44867</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45939</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45667</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45306</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45749</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45433</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45433</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>44543</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45296</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45293</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45255</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45446</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45558</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46127</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45154</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44962</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45334</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>44837</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44837</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45454</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45518</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44912</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>46181</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44992</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45022</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45951</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45302</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45611</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44890</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45677</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>46182</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45955</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45958</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45151</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44909</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44993</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45961</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45961</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45966</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45966</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45965</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45964</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45167</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45257</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45567</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45965</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45280</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>46191</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45231</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45554</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46197</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45971</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>46196</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45972</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44711</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45974</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45446</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>46197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45974</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44974</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45975</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45647</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45618</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45408</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45982</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45296</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>45981</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45986</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44719</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45985</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45985</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45985</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45049</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45986</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45553</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45490</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45509</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45988</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45726</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>46024</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45988</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45103</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45706</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46211</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45453</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45034</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46211</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45903</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46202</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45993</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45515</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45323</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45695</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45695</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45425</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45425</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45610</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>44992</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45995</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>44546</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44546</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>46216</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45429</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45349</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45595</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>46001</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>46002</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45776</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46006</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>46006</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45779</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46006</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>46177</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45376</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46177</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46007</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45015</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>46007</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>46233</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45646</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45261</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46010</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45524</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45350</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>46233</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46013</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46020</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46020</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46018</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46021</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>46021</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46238</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45787</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>46024</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45526</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>46027</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45790</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>46029</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>46029</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45790</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46027</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45574</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>46241</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45596</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46241</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46035</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46035</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44971</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45980</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45979</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45982</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46041</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>46041</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45979</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45796</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>46044</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46043</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45240</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46043</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>46043</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>46044</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>46288</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45558</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>46045</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>46045</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>46154</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>46287</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>46246</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>46050</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46286</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46049</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45114</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>46052</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>46045</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46289</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>46029</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>46056</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>46055</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>46135</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46290</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>46286</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46247</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44731</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>46290</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45520</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45537</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>46293</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>46248</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>46044</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>46293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>46127</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45812</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>46293</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45818</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46294</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45818</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45860</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45818</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45797</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45817</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>46240</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>46070</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>46070</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45979</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>46294</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45797</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>46007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46071</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>46249</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46072</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45820</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46072</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>46072</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45821</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46251</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46251</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46252</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45825</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46252</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45827</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45832</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46049</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45833</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45497</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46297</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>46297</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45890</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45835</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46092</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45839</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45966</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46097</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>46097</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45334</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>46063</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46252</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>46254</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>46101</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>46259</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45561</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>46259</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45847</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>46106</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45849</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45849</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45558</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46259</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>46259</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>46112</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45863</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46113</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45863</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46119</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>45631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46121</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45727</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46127</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>46127</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45068</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>46127</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>46126</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>46114</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>46308</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>46308</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>44978</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>46128</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>46132</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45881</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45882</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45275</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46133</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>46114</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45476</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45049</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45625</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>45202</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45357</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45216</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>46114</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45555</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>44917</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>46188</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45553</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45480</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45803</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44959</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45474</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45509</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45863</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>44820</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>46035</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45741</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45670</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>46268</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45510</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45958</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45834</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>46140</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>46106</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45002</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>44966</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45406</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45303</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45103</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46316</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>46139</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45125</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45567</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45456</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46036</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46316</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45675</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45782</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45732</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>46149</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45001</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45152</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45695</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>46035</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>46064</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>46139</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45630</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>46276</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45583</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>44974</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>46030</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>44974</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45030</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>46146</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45397</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>46147</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>46148</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45232</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>46119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>46149</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>46149</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>46092</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>46038</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>45994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>44998</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>45877</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>45559</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45121</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45623</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>46044</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>46052</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>46155</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45896</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45751</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46043</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46156</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45607</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>46155</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>46156</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45835</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>44998</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45015</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45076</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45365</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45621</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45027</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>45624</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45624</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45637</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45127</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45244</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>44993</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>44714</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>44967</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45727</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45183</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45132</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45027</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45490</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44987</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45131</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45510</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>44501</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45705</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45176</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45369</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45061</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45567</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45203</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44574</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45113</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>44869</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45567</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>44792</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45112</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>45625</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>44875</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45467</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>44749</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>44929</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45455</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45103</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44915</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45061</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45756</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>44909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45231</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45103</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45015</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45561</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45518</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>45664</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>44992</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45258</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45376</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         <v>44959</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45447</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45219</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45195</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45559</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45152</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>44951</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44994</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45004</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45376</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45097</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>45110</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45544</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45317</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>44986</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45096</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45027</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>44580</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45595</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>45127</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45609</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45001</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45428</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45362</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45169</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45553</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45608</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45509</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>45608</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>44643</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45727</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45169</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45165</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45574</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>45608</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45200</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45169</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45667</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>45180</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45351</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45244</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45160</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45568</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>45167</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45415</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45261</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45261</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45707</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>45252</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         <v>44679</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>45256</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45127</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57162,7 +57162,7 @@
         <v>45127</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57235,7 +57235,7 @@
         <v>44714</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45110</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>45197</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45109</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45314</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>45219</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>45219</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45257</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>44846</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>45259</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>45264</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>45104</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45307</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45446</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58272,7 +58272,7 @@
         <v>45373</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45266</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>44902</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>45264</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58564,7 +58564,7 @@
         <v>45261</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45397</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>44846</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>45272</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45266</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>44785</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45747</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>45201</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>45037</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>45621</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>45197</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>45216</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>45044</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>45418</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>45282</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45552</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>45523</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>45001</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>45478</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>45261</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>44578</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>44652</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45074</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45257</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60394,7 +60394,7 @@
         <v>45097</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60467,7 +60467,7 @@
         <v>45351</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60545,7 +60545,7 @@
         <v>44809</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>45097</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>45133</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45446</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45701</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60920,7 +60920,7 @@
         <v>45701</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60998,7 +60998,7 @@
         <v>45708</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>45799</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45819</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61222,7 +61222,7 @@
         <v>45824</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61295,7 +61295,7 @@
         <v>45835</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>45904</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45943</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61514,7 +61514,7 @@
         <v>45964</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61592,7 +61592,7 @@
         <v>46038</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>46043</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>46052</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61821,7 +61821,7 @@
         <v>44649</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>46066</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61967,7 +61967,7 @@
         <v>46076</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62040,7 +62040,7 @@
         <v>46133</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>46134</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45727</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>

--- a/Översikt LEKSAND.xlsx
+++ b/Översikt LEKSAND.xlsx
@@ -601,7 +601,7 @@
         <v>44876</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>45825</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -932,7 +932,7 @@
         <v>46064</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1075,7 +1075,7 @@
         <v>46013</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
         <v>45790</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>44901</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1488,7 +1488,7 @@
         <v>45841</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1618,7 +1618,7 @@
         <v>44977</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>45274</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>45835</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -2000,7 +2000,7 @@
         <v>45854</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45875</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>46237</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2374,7 +2374,7 @@
         <v>45715</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2496,7 +2496,7 @@
         <v>46286</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2613,7 +2613,7 @@
         <v>45827</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>45936</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2849,7 +2849,7 @@
         <v>45272</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2965,7 +2965,7 @@
         <v>44992</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -3076,7 +3076,7 @@
         <v>46178</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>45896</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3319,7 +3319,7 @@
         <v>45334</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3429,7 +3429,7 @@
         <v>45489</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3539,7 +3539,7 @@
         <v>45614</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>45632</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45638</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45988</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3981,7 +3981,7 @@
         <v>46027</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4090,7 +4090,7 @@
         <v>45835</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -4207,7 +4207,7 @@
         <v>45272</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4320,7 +4320,7 @@
         <v>45931</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         <v>45632</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4536,7 +4536,7 @@
         <v>44869</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>45901</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4764,7 +4764,7 @@
         <v>46097</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4875,7 +4875,7 @@
         <v>46237</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>45637</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
         <v>45890</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5199,7 +5199,7 @@
         <v>45254</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>45996</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>46226</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>46027</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5628,7 +5628,7 @@
         <v>46283</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5739,7 +5739,7 @@
         <v>45274</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5849,7 +5849,7 @@
         <v>46289</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5964,7 +5964,7 @@
         <v>45812</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -6070,7 +6070,7 @@
         <v>45835</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -6180,7 +6180,7 @@
         <v>45849</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6286,7 +6286,7 @@
         <v>45656</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6392,7 +6392,7 @@
         <v>44829</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6502,7 +6502,7 @@
         <v>45358</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6608,7 +6608,7 @@
         <v>44602</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6723,7 +6723,7 @@
         <v>45028</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6829,7 +6829,7 @@
         <v>45754</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>45251</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -7045,7 +7045,7 @@
         <v>45251</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -7155,7 +7155,7 @@
         <v>44536</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44869</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7370,7 +7370,7 @@
         <v>44509</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7484,7 +7484,7 @@
         <v>44735</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7589,7 +7589,7 @@
         <v>44761</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7698,7 +7698,7 @@
         <v>45005</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7807,7 +7807,7 @@
         <v>45110</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>45839</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -8022,7 +8022,7 @@
         <v>45418</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -8127,7 +8127,7 @@
         <v>45959</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
         <v>45960</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8346,7 +8346,7 @@
         <v>46155</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45016</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8565,7 +8565,7 @@
         <v>46202</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8674,7 +8674,7 @@
         <v>45981</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8779,7 +8779,7 @@
         <v>45228</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8888,7 +8888,7 @@
         <v>45502</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8993,7 +8993,7 @@
         <v>45256</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>45793</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>46287</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9313,7 +9313,7 @@
         <v>46041</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9418,7 +9418,7 @@
         <v>46244</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9523,7 +9523,7 @@
         <v>46069</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9628,7 +9628,7 @@
         <v>44973</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9733,7 +9733,7 @@
         <v>45334</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9838,7 +9838,7 @@
         <v>46120</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9943,7 +9943,7 @@
         <v>44918</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -10048,7 +10048,7 @@
         <v>44909</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -10157,7 +10157,7 @@
         <v>45294</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -10266,7 +10266,7 @@
         <v>44750</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -10380,7 +10380,7 @@
         <v>45690</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -10489,7 +10489,7 @@
         <v>45091</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -10594,7 +10594,7 @@
         <v>44992</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10703,7 +10703,7 @@
         <v>45761</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10808,7 +10808,7 @@
         <v>45127</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10917,7 +10917,7 @@
         <v>44588</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -11022,7 +11022,7 @@
         <v>45621</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>45638</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -11236,7 +11236,7 @@
         <v>45061</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -11341,7 +11341,7 @@
         <v>45181</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -11446,7 +11446,7 @@
         <v>45996</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -11556,7 +11556,7 @@
         <v>44782</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>44834</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -11702,7 +11702,7 @@
         <v>44802</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -11780,7 +11780,7 @@
         <v>44671</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -11853,7 +11853,7 @@
         <v>44872</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -11931,7 +11931,7 @@
         <v>44512</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -12004,7 +12004,7 @@
         <v>44869</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>44570</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44670</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -12228,7 +12228,7 @@
         <v>44877</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -12301,7 +12301,7 @@
         <v>44539</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -12374,7 +12374,7 @@
         <v>44529</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -12447,7 +12447,7 @@
         <v>44824</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -12520,7 +12520,7 @@
         <v>44834</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -12593,7 +12593,7 @@
         <v>44693</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -12666,7 +12666,7 @@
         <v>44503</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -12739,7 +12739,7 @@
         <v>44533</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>44851</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -12885,7 +12885,7 @@
         <v>44865</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12963,7 +12963,7 @@
         <v>44792</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>44690</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -13114,7 +13114,7 @@
         <v>44684</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -13192,7 +13192,7 @@
         <v>44543</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -13265,7 +13265,7 @@
         <v>44777</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -13338,7 +13338,7 @@
         <v>44651</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -13411,7 +13411,7 @@
         <v>44862</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -13484,7 +13484,7 @@
         <v>44797</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -13557,7 +13557,7 @@
         <v>44533</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>45428</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>45050</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -13776,7 +13776,7 @@
         <v>45351</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -13849,7 +13849,7 @@
         <v>45886</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>44746</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13995,7 +13995,7 @@
         <v>45160</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45890</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -14141,7 +14141,7 @@
         <v>45890</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -14214,7 +14214,7 @@
         <v>44987</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -14287,7 +14287,7 @@
         <v>45334</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -14365,7 +14365,7 @@
         <v>45308</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -14438,7 +14438,7 @@
         <v>45257</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -14511,7 +14511,7 @@
         <v>45345</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -14584,7 +14584,7 @@
         <v>45898</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -14662,7 +14662,7 @@
         <v>45898</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -14740,7 +14740,7 @@
         <v>45898</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -14818,7 +14818,7 @@
         <v>45378</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14891,7 +14891,7 @@
         <v>45901</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14969,7 +14969,7 @@
         <v>45036</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>45903</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -15115,7 +15115,7 @@
         <v>45884</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -15188,7 +15188,7 @@
         <v>45342</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -15266,7 +15266,7 @@
         <v>45230</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>45912</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -15417,7 +15417,7 @@
         <v>45621</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -15490,7 +15490,7 @@
         <v>45911</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -15563,7 +15563,7 @@
         <v>45568</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -15636,7 +15636,7 @@
         <v>45911</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45912</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -15782,7 +15782,7 @@
         <v>45912</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>45911</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15928,7 +15928,7 @@
         <v>45618</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -16001,7 +16001,7 @@
         <v>45916</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -16074,7 +16074,7 @@
         <v>46162</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -16147,7 +16147,7 @@
         <v>45915</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -16220,7 +16220,7 @@
         <v>44918</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -16293,7 +16293,7 @@
         <v>45917</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -16366,7 +16366,7 @@
         <v>45919</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -16439,7 +16439,7 @@
         <v>44985</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -16512,7 +16512,7 @@
         <v>45921</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -16585,7 +16585,7 @@
         <v>45637</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45910</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -16731,7 +16731,7 @@
         <v>45397</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -16804,7 +16804,7 @@
         <v>45921</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16877,7 +16877,7 @@
         <v>44533</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45744</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>45112</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45924</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -17169,7 +17169,7 @@
         <v>45114</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45266</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46167</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -17388,7 +17388,7 @@
         <v>46168</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -17461,7 +17461,7 @@
         <v>45104</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -17534,7 +17534,7 @@
         <v>46168</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -17607,7 +17607,7 @@
         <v>45925</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45925</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -17753,7 +17753,7 @@
         <v>45929</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -17826,7 +17826,7 @@
         <v>45208</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17904,7 +17904,7 @@
         <v>45085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17977,7 +17977,7 @@
         <v>44974</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -18050,7 +18050,7 @@
         <v>44977</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45932</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -18201,7 +18201,7 @@
         <v>45932</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -18279,7 +18279,7 @@
         <v>46171</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>46170</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -18430,7 +18430,7 @@
         <v>45203</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -18503,7 +18503,7 @@
         <v>46174</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -18576,7 +18576,7 @@
         <v>45934</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -18649,7 +18649,7 @@
         <v>45131</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -18722,7 +18722,7 @@
         <v>45630</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -18795,7 +18795,7 @@
         <v>45630</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18868,7 +18868,7 @@
         <v>44978</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18941,7 +18941,7 @@
         <v>45937</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -19014,7 +19014,7 @@
         <v>45937</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -19087,7 +19087,7 @@
         <v>44991</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>44991</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -19233,7 +19233,7 @@
         <v>44867</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -19306,7 +19306,7 @@
         <v>44628</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -19379,7 +19379,7 @@
         <v>45939</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>45944</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -19530,7 +19530,7 @@
         <v>45667</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -19603,7 +19603,7 @@
         <v>45306</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -19676,7 +19676,7 @@
         <v>45749</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -19749,7 +19749,7 @@
         <v>45433</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>45433</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>44543</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19973,7 +19973,7 @@
         <v>45296</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -20046,7 +20046,7 @@
         <v>45293</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -20119,7 +20119,7 @@
         <v>45255</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45446</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45946</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -20343,7 +20343,7 @@
         <v>45558</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>45454</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -20489,7 +20489,7 @@
         <v>46127</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -20562,7 +20562,7 @@
         <v>45154</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>44962</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -20708,7 +20708,7 @@
         <v>45334</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -20781,7 +20781,7 @@
         <v>44837</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20854,7 +20854,7 @@
         <v>44837</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20927,7 +20927,7 @@
         <v>45454</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>45518</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -21073,7 +21073,7 @@
         <v>44912</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -21146,7 +21146,7 @@
         <v>46181</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -21224,7 +21224,7 @@
         <v>44992</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -21297,7 +21297,7 @@
         <v>45022</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -21370,7 +21370,7 @@
         <v>45951</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
         <v>45302</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>46035</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -21594,7 +21594,7 @@
         <v>45951</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -21672,7 +21672,7 @@
         <v>45611</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>44890</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21818,7 +21818,7 @@
         <v>46182</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21891,7 +21891,7 @@
         <v>45952</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21964,7 +21964,7 @@
         <v>45677</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -22037,7 +22037,7 @@
         <v>46182</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -22110,7 +22110,7 @@
         <v>45955</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -22183,7 +22183,7 @@
         <v>46185</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -22261,7 +22261,7 @@
         <v>45113</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -22334,7 +22334,7 @@
         <v>45958</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -22407,7 +22407,7 @@
         <v>45151</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -22480,7 +22480,7 @@
         <v>45961</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -22553,7 +22553,7 @@
         <v>45964</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>44909</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45960</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22772,7 +22772,7 @@
         <v>45161</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22845,7 +22845,7 @@
         <v>44993</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22918,7 +22918,7 @@
         <v>45964</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
@@ -22991,7 +22991,7 @@
         <v>45961</v>
       </c>
       <c r="E254" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>45961</v>
       </c>
       <c r="E255" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45966</v>
       </c>
       <c r="E256" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
@@ -23210,7 +23210,7 @@
         <v>45966</v>
       </c>
       <c r="E257" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
@@ -23283,7 +23283,7 @@
         <v>45965</v>
       </c>
       <c r="E258" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
@@ -23361,7 +23361,7 @@
         <v>45260</v>
       </c>
       <c r="E259" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45964</v>
       </c>
       <c r="E260" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
@@ -23507,7 +23507,7 @@
         <v>45167</v>
       </c>
       <c r="E261" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45257</v>
       </c>
       <c r="E262" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45567</v>
       </c>
       <c r="E263" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
@@ -23726,7 +23726,7 @@
         <v>45966</v>
       </c>
       <c r="E264" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
@@ -23799,7 +23799,7 @@
         <v>45966</v>
       </c>
       <c r="E265" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45966</v>
       </c>
       <c r="E266" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45966</v>
       </c>
       <c r="E267" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
@@ -24018,7 +24018,7 @@
         <v>45964</v>
       </c>
       <c r="E268" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
@@ -24091,7 +24091,7 @@
         <v>46190</v>
       </c>
       <c r="E269" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
@@ -24169,7 +24169,7 @@
         <v>45965</v>
       </c>
       <c r="E270" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>46191</v>
       </c>
       <c r="E271" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
@@ -24320,7 +24320,7 @@
         <v>45280</v>
       </c>
       <c r="E272" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
@@ -24393,7 +24393,7 @@
         <v>46191</v>
       </c>
       <c r="E273" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
@@ -24466,7 +24466,7 @@
         <v>46191</v>
       </c>
       <c r="E274" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
@@ -24539,7 +24539,7 @@
         <v>45231</v>
       </c>
       <c r="E275" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>45554</v>
       </c>
       <c r="E276" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
@@ -24695,7 +24695,7 @@
         <v>46197</v>
       </c>
       <c r="E277" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
@@ -24768,7 +24768,7 @@
         <v>45971</v>
       </c>
       <c r="E278" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
@@ -24841,7 +24841,7 @@
         <v>46196</v>
       </c>
       <c r="E279" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45972</v>
       </c>
       <c r="E280" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>44711</v>
       </c>
       <c r="E281" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
@@ -25065,7 +25065,7 @@
         <v>45974</v>
       </c>
       <c r="E282" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
@@ -25138,7 +25138,7 @@
         <v>46197</v>
       </c>
       <c r="E283" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -25216,7 +25216,7 @@
         <v>45446</v>
       </c>
       <c r="E284" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
@@ -25294,7 +25294,7 @@
         <v>46197</v>
       </c>
       <c r="E285" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>45974</v>
       </c>
       <c r="E286" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
@@ -25445,7 +25445,7 @@
         <v>45978</v>
       </c>
       <c r="E287" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
@@ -25518,7 +25518,7 @@
         <v>44974</v>
       </c>
       <c r="E288" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
@@ -25591,7 +25591,7 @@
         <v>45975</v>
       </c>
       <c r="E289" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
@@ -25669,7 +25669,7 @@
         <v>45647</v>
       </c>
       <c r="E290" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
@@ -25742,7 +25742,7 @@
         <v>45618</v>
       </c>
       <c r="E291" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F291" t="inlineStr">
         <is>
@@ -25815,7 +25815,7 @@
         <v>45408</v>
       </c>
       <c r="E292" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>46202</v>
       </c>
       <c r="E293" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
@@ -25961,7 +25961,7 @@
         <v>45982</v>
       </c>
       <c r="E294" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
@@ -26034,7 +26034,7 @@
         <v>45296</v>
       </c>
       <c r="E295" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
@@ -26107,7 +26107,7 @@
         <v>45981</v>
       </c>
       <c r="E296" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
@@ -26180,7 +26180,7 @@
         <v>45986</v>
       </c>
       <c r="E297" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
@@ -26253,7 +26253,7 @@
         <v>44719</v>
       </c>
       <c r="E298" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
@@ -26326,7 +26326,7 @@
         <v>45985</v>
       </c>
       <c r="E299" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F299" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45985</v>
       </c>
       <c r="E300" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F300" t="inlineStr">
         <is>
@@ -26472,7 +26472,7 @@
         <v>45985</v>
       </c>
       <c r="E301" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F301" t="inlineStr">
         <is>
@@ -26545,7 +26545,7 @@
         <v>45049</v>
       </c>
       <c r="E302" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F302" t="inlineStr">
         <is>
@@ -26618,7 +26618,7 @@
         <v>45986</v>
       </c>
       <c r="E303" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F303" t="inlineStr">
         <is>
@@ -26691,7 +26691,7 @@
         <v>45553</v>
       </c>
       <c r="E304" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F304" t="inlineStr">
         <is>
@@ -26769,7 +26769,7 @@
         <v>45490</v>
       </c>
       <c r="E305" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F305" t="inlineStr">
         <is>
@@ -26842,7 +26842,7 @@
         <v>45985</v>
       </c>
       <c r="E306" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F306" t="inlineStr">
         <is>
@@ -26915,7 +26915,7 @@
         <v>45509</v>
       </c>
       <c r="E307" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F307" t="inlineStr">
         <is>
@@ -26988,7 +26988,7 @@
         <v>45988</v>
       </c>
       <c r="E308" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F308" t="inlineStr">
         <is>
@@ -27086,7 +27086,7 @@
         <v>45726</v>
       </c>
       <c r="E309" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F309" t="inlineStr">
         <is>
@@ -27159,7 +27159,7 @@
         <v>44929</v>
       </c>
       <c r="E310" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F310" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>46024</v>
       </c>
       <c r="E311" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F311" t="inlineStr">
         <is>
@@ -27310,7 +27310,7 @@
         <v>45988</v>
       </c>
       <c r="E312" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F312" t="inlineStr">
         <is>
@@ -27383,7 +27383,7 @@
         <v>45103</v>
       </c>
       <c r="E313" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F313" t="inlineStr">
         <is>
@@ -27461,7 +27461,7 @@
         <v>45706</v>
       </c>
       <c r="E314" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F314" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>46211</v>
       </c>
       <c r="E315" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F315" t="inlineStr">
         <is>
@@ -27607,7 +27607,7 @@
         <v>45453</v>
       </c>
       <c r="E316" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F316" t="inlineStr">
         <is>
@@ -27680,7 +27680,7 @@
         <v>45034</v>
       </c>
       <c r="E317" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -27753,7 +27753,7 @@
         <v>46211</v>
       </c>
       <c r="E318" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F318" t="inlineStr">
         <is>
@@ -27826,7 +27826,7 @@
         <v>45903</v>
       </c>
       <c r="E319" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F319" t="inlineStr">
         <is>
@@ -27904,7 +27904,7 @@
         <v>46202</v>
       </c>
       <c r="E320" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F320" t="inlineStr">
         <is>
@@ -27982,7 +27982,7 @@
         <v>45993</v>
       </c>
       <c r="E321" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F321" t="inlineStr">
         <is>
@@ -28055,7 +28055,7 @@
         <v>45515</v>
       </c>
       <c r="E322" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F322" t="inlineStr">
         <is>
@@ -28128,7 +28128,7 @@
         <v>45323</v>
       </c>
       <c r="E323" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F323" t="inlineStr">
         <is>
@@ -28201,7 +28201,7 @@
         <v>45695</v>
       </c>
       <c r="E324" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F324" t="inlineStr">
         <is>
@@ -28274,7 +28274,7 @@
         <v>45695</v>
       </c>
       <c r="E325" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F325" t="inlineStr">
         <is>
@@ -28347,7 +28347,7 @@
         <v>45425</v>
       </c>
       <c r="E326" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F326" t="inlineStr">
         <is>
@@ -28420,7 +28420,7 @@
         <v>45425</v>
       </c>
       <c r="E327" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F327" t="inlineStr">
         <is>
@@ -28493,7 +28493,7 @@
         <v>45610</v>
       </c>
       <c r="E328" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F328" t="inlineStr">
         <is>
@@ -28566,7 +28566,7 @@
         <v>44992</v>
       </c>
       <c r="E329" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F329" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45995</v>
       </c>
       <c r="E330" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F330" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45093</v>
       </c>
       <c r="E331" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F331" t="inlineStr">
         <is>
@@ -28785,7 +28785,7 @@
         <v>44546</v>
       </c>
       <c r="E332" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F332" t="inlineStr">
         <is>
@@ -28858,7 +28858,7 @@
         <v>44546</v>
       </c>
       <c r="E333" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F333" t="inlineStr">
         <is>
@@ -28931,7 +28931,7 @@
         <v>46216</v>
       </c>
       <c r="E334" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F334" t="inlineStr">
         <is>
@@ -29009,7 +29009,7 @@
         <v>45429</v>
       </c>
       <c r="E335" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F335" t="inlineStr">
         <is>
@@ -29082,7 +29082,7 @@
         <v>45349</v>
       </c>
       <c r="E336" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F336" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45595</v>
       </c>
       <c r="E337" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F337" t="inlineStr">
         <is>
@@ -29228,7 +29228,7 @@
         <v>46001</v>
       </c>
       <c r="E338" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F338" t="inlineStr">
         <is>
@@ -29301,7 +29301,7 @@
         <v>46002</v>
       </c>
       <c r="E339" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F339" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45776</v>
       </c>
       <c r="E340" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F340" t="inlineStr">
         <is>
@@ -29452,7 +29452,7 @@
         <v>46006</v>
       </c>
       <c r="E341" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F341" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>46006</v>
       </c>
       <c r="E342" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F342" t="inlineStr">
         <is>
@@ -29598,7 +29598,7 @@
         <v>46006</v>
       </c>
       <c r="E343" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F343" t="inlineStr">
         <is>
@@ -29671,7 +29671,7 @@
         <v>45779</v>
       </c>
       <c r="E344" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F344" t="inlineStr">
         <is>
@@ -29744,7 +29744,7 @@
         <v>46006</v>
       </c>
       <c r="E345" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F345" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>46167</v>
       </c>
       <c r="E346" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F346" t="inlineStr">
         <is>
@@ -29895,7 +29895,7 @@
         <v>46177</v>
       </c>
       <c r="E347" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F347" t="inlineStr">
         <is>
@@ -29973,7 +29973,7 @@
         <v>45376</v>
       </c>
       <c r="E348" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F348" t="inlineStr">
         <is>
@@ -30046,7 +30046,7 @@
         <v>45170</v>
       </c>
       <c r="E349" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F349" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>46177</v>
       </c>
       <c r="E350" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F350" t="inlineStr">
         <is>
@@ -30202,7 +30202,7 @@
         <v>46007</v>
       </c>
       <c r="E351" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F351" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45015</v>
       </c>
       <c r="E352" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F352" t="inlineStr">
         <is>
@@ -30348,7 +30348,7 @@
         <v>46007</v>
       </c>
       <c r="E353" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F353" t="inlineStr">
         <is>
@@ -30421,7 +30421,7 @@
         <v>46233</v>
       </c>
       <c r="E354" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F354" t="inlineStr">
         <is>
@@ -30499,7 +30499,7 @@
         <v>45266</v>
       </c>
       <c r="E355" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F355" t="inlineStr">
         <is>
@@ -30572,7 +30572,7 @@
         <v>45646</v>
       </c>
       <c r="E356" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F356" t="inlineStr">
         <is>
@@ -30645,7 +30645,7 @@
         <v>45261</v>
       </c>
       <c r="E357" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F357" t="inlineStr">
         <is>
@@ -30718,7 +30718,7 @@
         <v>46010</v>
       </c>
       <c r="E358" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F358" t="inlineStr">
         <is>
@@ -30791,7 +30791,7 @@
         <v>46010</v>
       </c>
       <c r="E359" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F359" t="inlineStr">
         <is>
@@ -30864,7 +30864,7 @@
         <v>45524</v>
       </c>
       <c r="E360" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F360" t="inlineStr">
         <is>
@@ -30937,7 +30937,7 @@
         <v>45350</v>
       </c>
       <c r="E361" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F361" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>46233</v>
       </c>
       <c r="E362" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F362" t="inlineStr">
         <is>
@@ -31088,7 +31088,7 @@
         <v>46013</v>
       </c>
       <c r="E363" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F363" t="inlineStr">
         <is>
@@ -31161,7 +31161,7 @@
         <v>46020</v>
       </c>
       <c r="E364" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F364" t="inlineStr">
         <is>
@@ -31234,7 +31234,7 @@
         <v>46020</v>
       </c>
       <c r="E365" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F365" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>46018</v>
       </c>
       <c r="E366" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F366" t="inlineStr">
         <is>
@@ -31380,7 +31380,7 @@
         <v>46021</v>
       </c>
       <c r="E367" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F367" t="inlineStr">
         <is>
@@ -31453,7 +31453,7 @@
         <v>46021</v>
       </c>
       <c r="E368" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F368" t="inlineStr">
         <is>
@@ -31526,7 +31526,7 @@
         <v>46281</v>
       </c>
       <c r="E369" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F369" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>46238</v>
       </c>
       <c r="E370" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F370" t="inlineStr">
         <is>
@@ -31677,7 +31677,7 @@
         <v>45787</v>
       </c>
       <c r="E371" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F371" t="inlineStr">
         <is>
@@ -31750,7 +31750,7 @@
         <v>46024</v>
       </c>
       <c r="E372" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F372" t="inlineStr">
         <is>
@@ -31823,7 +31823,7 @@
         <v>45526</v>
       </c>
       <c r="E373" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F373" t="inlineStr">
         <is>
@@ -31896,7 +31896,7 @@
         <v>46027</v>
       </c>
       <c r="E374" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F374" t="inlineStr">
         <is>
@@ -31969,7 +31969,7 @@
         <v>45790</v>
       </c>
       <c r="E375" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F375" t="inlineStr">
         <is>
@@ -32042,7 +32042,7 @@
         <v>46029</v>
       </c>
       <c r="E376" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F376" t="inlineStr">
         <is>
@@ -32115,7 +32115,7 @@
         <v>46029</v>
       </c>
       <c r="E377" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F377" t="inlineStr">
         <is>
@@ -32188,7 +32188,7 @@
         <v>46029</v>
       </c>
       <c r="E378" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F378" t="inlineStr">
         <is>
@@ -32261,7 +32261,7 @@
         <v>45790</v>
       </c>
       <c r="E379" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F379" t="inlineStr">
         <is>
@@ -32334,7 +32334,7 @@
         <v>46027</v>
       </c>
       <c r="E380" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F380" t="inlineStr">
         <is>
@@ -32407,7 +32407,7 @@
         <v>45574</v>
       </c>
       <c r="E381" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F381" t="inlineStr">
         <is>
@@ -32480,7 +32480,7 @@
         <v>46241</v>
       </c>
       <c r="E382" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F382" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45596</v>
       </c>
       <c r="E383" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F383" t="inlineStr">
         <is>
@@ -32631,7 +32631,7 @@
         <v>46241</v>
       </c>
       <c r="E384" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F384" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>46035</v>
       </c>
       <c r="E385" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F385" t="inlineStr">
         <is>
@@ -32782,7 +32782,7 @@
         <v>46035</v>
       </c>
       <c r="E386" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F386" t="inlineStr">
         <is>
@@ -32855,7 +32855,7 @@
         <v>44971</v>
       </c>
       <c r="E387" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F387" t="inlineStr">
         <is>
@@ -32928,7 +32928,7 @@
         <v>45980</v>
       </c>
       <c r="E388" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F388" t="inlineStr">
         <is>
@@ -33001,7 +33001,7 @@
         <v>45979</v>
       </c>
       <c r="E389" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F389" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45982</v>
       </c>
       <c r="E390" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F390" t="inlineStr">
         <is>
@@ -33147,7 +33147,7 @@
         <v>46041</v>
       </c>
       <c r="E391" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F391" t="inlineStr">
         <is>
@@ -33220,7 +33220,7 @@
         <v>46041</v>
       </c>
       <c r="E392" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F392" t="inlineStr">
         <is>
@@ -33293,7 +33293,7 @@
         <v>45979</v>
       </c>
       <c r="E393" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F393" t="inlineStr">
         <is>
@@ -33366,7 +33366,7 @@
         <v>45796</v>
       </c>
       <c r="E394" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F394" t="inlineStr">
         <is>
@@ -33439,7 +33439,7 @@
         <v>46044</v>
       </c>
       <c r="E395" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F395" t="inlineStr">
         <is>
@@ -33512,7 +33512,7 @@
         <v>46043</v>
       </c>
       <c r="E396" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F396" t="inlineStr">
         <is>
@@ -33585,7 +33585,7 @@
         <v>45240</v>
       </c>
       <c r="E397" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F397" t="inlineStr">
         <is>
@@ -33658,7 +33658,7 @@
         <v>46043</v>
       </c>
       <c r="E398" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F398" t="inlineStr">
         <is>
@@ -33731,7 +33731,7 @@
         <v>46043</v>
       </c>
       <c r="E399" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F399" t="inlineStr">
         <is>
@@ -33804,7 +33804,7 @@
         <v>46044</v>
       </c>
       <c r="E400" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F400" t="inlineStr">
         <is>
@@ -33877,7 +33877,7 @@
         <v>46288</v>
       </c>
       <c r="E401" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F401" t="inlineStr">
         <is>
@@ -33950,7 +33950,7 @@
         <v>45558</v>
       </c>
       <c r="E402" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F402" t="inlineStr">
         <is>
@@ -34023,7 +34023,7 @@
         <v>46045</v>
       </c>
       <c r="E403" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F403" t="inlineStr">
         <is>
@@ -34096,7 +34096,7 @@
         <v>46045</v>
       </c>
       <c r="E404" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F404" t="inlineStr">
         <is>
@@ -34169,7 +34169,7 @@
         <v>46154</v>
       </c>
       <c r="E405" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F405" t="inlineStr">
         <is>
@@ -34247,7 +34247,7 @@
         <v>46287</v>
       </c>
       <c r="E406" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F406" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>46246</v>
       </c>
       <c r="E407" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F407" t="inlineStr">
         <is>
@@ -34398,7 +34398,7 @@
         <v>46050</v>
       </c>
       <c r="E408" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F408" t="inlineStr">
         <is>
@@ -34471,7 +34471,7 @@
         <v>46286</v>
       </c>
       <c r="E409" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F409" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>46049</v>
       </c>
       <c r="E410" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F410" t="inlineStr">
         <is>
@@ -34622,7 +34622,7 @@
         <v>45114</v>
       </c>
       <c r="E411" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F411" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>46052</v>
       </c>
       <c r="E412" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F412" t="inlineStr">
         <is>
@@ -34768,7 +34768,7 @@
         <v>46045</v>
       </c>
       <c r="E413" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F413" t="inlineStr">
         <is>
@@ -34841,7 +34841,7 @@
         <v>46289</v>
       </c>
       <c r="E414" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F414" t="inlineStr">
         <is>
@@ -34914,7 +34914,7 @@
         <v>46051</v>
       </c>
       <c r="E415" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F415" t="inlineStr">
         <is>
@@ -34987,7 +34987,7 @@
         <v>46029</v>
       </c>
       <c r="E416" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F416" t="inlineStr">
         <is>
@@ -35060,7 +35060,7 @@
         <v>46056</v>
       </c>
       <c r="E417" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F417" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>46055</v>
       </c>
       <c r="E418" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F418" t="inlineStr">
         <is>
@@ -35206,7 +35206,7 @@
         <v>46135</v>
       </c>
       <c r="E419" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F419" t="inlineStr">
         <is>
@@ -35284,7 +35284,7 @@
         <v>46290</v>
       </c>
       <c r="E420" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F420" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>46286</v>
       </c>
       <c r="E421" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F421" t="inlineStr">
         <is>
@@ -35440,7 +35440,7 @@
         <v>46247</v>
       </c>
       <c r="E422" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F422" t="inlineStr">
         <is>
@@ -35518,7 +35518,7 @@
         <v>44731</v>
       </c>
       <c r="E423" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F423" t="inlineStr">
         <is>
@@ -35591,7 +35591,7 @@
         <v>46290</v>
       </c>
       <c r="E424" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F424" t="inlineStr">
         <is>
@@ -35664,7 +35664,7 @@
         <v>45520</v>
       </c>
       <c r="E425" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F425" t="inlineStr">
         <is>
@@ -35737,7 +35737,7 @@
         <v>45537</v>
       </c>
       <c r="E426" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F426" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>46293</v>
       </c>
       <c r="E427" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F427" t="inlineStr">
         <is>
@@ -35883,7 +35883,7 @@
         <v>46248</v>
       </c>
       <c r="E428" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F428" t="inlineStr">
         <is>
@@ -35961,7 +35961,7 @@
         <v>46044</v>
       </c>
       <c r="E429" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F429" t="inlineStr">
         <is>
@@ -36034,7 +36034,7 @@
         <v>46293</v>
       </c>
       <c r="E430" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F430" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>46127</v>
       </c>
       <c r="E431" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F431" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45812</v>
       </c>
       <c r="E432" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F432" t="inlineStr">
         <is>
@@ -36263,7 +36263,7 @@
         <v>46293</v>
       </c>
       <c r="E433" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F433" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45813</v>
       </c>
       <c r="E434" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F434" t="inlineStr">
         <is>
@@ -36409,7 +36409,7 @@
         <v>45818</v>
       </c>
       <c r="E435" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F435" t="inlineStr">
         <is>
@@ -36487,7 +36487,7 @@
         <v>46294</v>
       </c>
       <c r="E436" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F436" t="inlineStr">
         <is>
@@ -36560,7 +36560,7 @@
         <v>46293</v>
       </c>
       <c r="E437" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F437" t="inlineStr">
         <is>
@@ -36633,7 +36633,7 @@
         <v>46035</v>
       </c>
       <c r="E438" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F438" t="inlineStr">
         <is>
@@ -36706,7 +36706,7 @@
         <v>45818</v>
       </c>
       <c r="E439" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F439" t="inlineStr">
         <is>
@@ -36779,7 +36779,7 @@
         <v>45860</v>
       </c>
       <c r="E440" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F440" t="inlineStr">
         <is>
@@ -36852,7 +36852,7 @@
         <v>45818</v>
       </c>
       <c r="E441" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F441" t="inlineStr">
         <is>
@@ -36925,7 +36925,7 @@
         <v>45797</v>
       </c>
       <c r="E442" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F442" t="inlineStr">
         <is>
@@ -36998,7 +36998,7 @@
         <v>45817</v>
       </c>
       <c r="E443" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F443" t="inlineStr">
         <is>
@@ -37071,7 +37071,7 @@
         <v>46240</v>
       </c>
       <c r="E444" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F444" t="inlineStr">
         <is>
@@ -37149,7 +37149,7 @@
         <v>46070</v>
       </c>
       <c r="E445" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F445" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>46070</v>
       </c>
       <c r="E446" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F446" t="inlineStr">
         <is>
@@ -37295,7 +37295,7 @@
         <v>46070</v>
       </c>
       <c r="E447" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F447" t="inlineStr">
         <is>
@@ -37368,7 +37368,7 @@
         <v>45979</v>
       </c>
       <c r="E448" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F448" t="inlineStr">
         <is>
@@ -37441,7 +37441,7 @@
         <v>46294</v>
       </c>
       <c r="E449" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F449" t="inlineStr">
         <is>
@@ -37514,7 +37514,7 @@
         <v>45797</v>
       </c>
       <c r="E450" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F450" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>46007</v>
       </c>
       <c r="E451" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F451" t="inlineStr">
         <is>
@@ -37660,7 +37660,7 @@
         <v>46071</v>
       </c>
       <c r="E452" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F452" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>46249</v>
       </c>
       <c r="E453" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F453" t="inlineStr">
         <is>
@@ -37811,7 +37811,7 @@
         <v>46072</v>
       </c>
       <c r="E454" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F454" t="inlineStr">
         <is>
@@ -37884,7 +37884,7 @@
         <v>45820</v>
       </c>
       <c r="E455" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F455" t="inlineStr">
         <is>
@@ -37957,7 +37957,7 @@
         <v>46072</v>
       </c>
       <c r="E456" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F456" t="inlineStr">
         <is>
@@ -38030,7 +38030,7 @@
         <v>46072</v>
       </c>
       <c r="E457" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F457" t="inlineStr">
         <is>
@@ -38103,7 +38103,7 @@
         <v>45821</v>
       </c>
       <c r="E458" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F458" t="inlineStr">
         <is>
@@ -38176,7 +38176,7 @@
         <v>46251</v>
       </c>
       <c r="E459" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F459" t="inlineStr">
         <is>
@@ -38254,7 +38254,7 @@
         <v>46251</v>
       </c>
       <c r="E460" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F460" t="inlineStr">
         <is>
@@ -38332,7 +38332,7 @@
         <v>46252</v>
       </c>
       <c r="E461" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F461" t="inlineStr">
         <is>
@@ -38410,7 +38410,7 @@
         <v>45825</v>
       </c>
       <c r="E462" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F462" t="inlineStr">
         <is>
@@ -38483,7 +38483,7 @@
         <v>46252</v>
       </c>
       <c r="E463" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F463" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45827</v>
       </c>
       <c r="E464" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F464" t="inlineStr">
         <is>
@@ -38629,7 +38629,7 @@
         <v>45832</v>
       </c>
       <c r="E465" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F465" t="inlineStr">
         <is>
@@ -38702,7 +38702,7 @@
         <v>46049</v>
       </c>
       <c r="E466" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F466" t="inlineStr">
         <is>
@@ -38775,7 +38775,7 @@
         <v>45833</v>
       </c>
       <c r="E467" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F467" t="inlineStr">
         <is>
@@ -38848,7 +38848,7 @@
         <v>45497</v>
       </c>
       <c r="E468" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F468" t="inlineStr">
         <is>
@@ -38926,7 +38926,7 @@
         <v>46297</v>
       </c>
       <c r="E469" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F469" t="inlineStr">
         <is>
@@ -38999,7 +38999,7 @@
         <v>46297</v>
       </c>
       <c r="E470" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F470" t="inlineStr">
         <is>
@@ -39072,7 +39072,7 @@
         <v>45890</v>
       </c>
       <c r="E471" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F471" t="inlineStr">
         <is>
@@ -39150,7 +39150,7 @@
         <v>45835</v>
       </c>
       <c r="E472" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F472" t="inlineStr">
         <is>
@@ -39223,7 +39223,7 @@
         <v>46092</v>
       </c>
       <c r="E473" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F473" t="inlineStr">
         <is>
@@ -39296,7 +39296,7 @@
         <v>45839</v>
       </c>
       <c r="E474" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F474" t="inlineStr">
         <is>
@@ -39369,7 +39369,7 @@
         <v>46097</v>
       </c>
       <c r="E475" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F475" t="inlineStr">
         <is>
@@ -39442,7 +39442,7 @@
         <v>45966</v>
       </c>
       <c r="E476" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F476" t="inlineStr">
         <is>
@@ -39515,7 +39515,7 @@
         <v>46097</v>
       </c>
       <c r="E477" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F477" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>46097</v>
       </c>
       <c r="E478" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F478" t="inlineStr">
         <is>
@@ -39661,7 +39661,7 @@
         <v>45334</v>
       </c>
       <c r="E479" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F479" t="inlineStr">
         <is>
@@ -39739,7 +39739,7 @@
         <v>46063</v>
       </c>
       <c r="E480" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F480" t="inlineStr">
         <is>
@@ -39812,7 +39812,7 @@
         <v>46252</v>
       </c>
       <c r="E481" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F481" t="inlineStr">
         <is>
@@ -39885,7 +39885,7 @@
         <v>46254</v>
       </c>
       <c r="E482" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F482" t="inlineStr">
         <is>
@@ -39958,7 +39958,7 @@
         <v>46101</v>
       </c>
       <c r="E483" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F483" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>46259</v>
       </c>
       <c r="E484" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F484" t="inlineStr">
         <is>
@@ -40104,7 +40104,7 @@
         <v>45561</v>
       </c>
       <c r="E485" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F485" t="inlineStr">
         <is>
@@ -40182,7 +40182,7 @@
         <v>46259</v>
       </c>
       <c r="E486" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F486" t="inlineStr">
         <is>
@@ -40255,7 +40255,7 @@
         <v>45847</v>
       </c>
       <c r="E487" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F487" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>46106</v>
       </c>
       <c r="E488" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F488" t="inlineStr">
         <is>
@@ -40406,7 +40406,7 @@
         <v>45849</v>
       </c>
       <c r="E489" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F489" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45849</v>
       </c>
       <c r="E490" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F490" t="inlineStr">
         <is>
@@ -40562,7 +40562,7 @@
         <v>45558</v>
       </c>
       <c r="E491" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F491" t="inlineStr">
         <is>
@@ -40635,7 +40635,7 @@
         <v>46259</v>
       </c>
       <c r="E492" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F492" t="inlineStr">
         <is>
@@ -40713,7 +40713,7 @@
         <v>46106</v>
       </c>
       <c r="E493" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F493" t="inlineStr">
         <is>
@@ -40786,7 +40786,7 @@
         <v>46111</v>
       </c>
       <c r="E494" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F494" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>46259</v>
       </c>
       <c r="E495" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F495" t="inlineStr">
         <is>
@@ -40937,7 +40937,7 @@
         <v>46112</v>
       </c>
       <c r="E496" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F496" t="inlineStr">
         <is>
@@ -41015,7 +41015,7 @@
         <v>45863</v>
       </c>
       <c r="E497" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F497" t="inlineStr">
         <is>
@@ -41088,7 +41088,7 @@
         <v>46113</v>
       </c>
       <c r="E498" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F498" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>45863</v>
       </c>
       <c r="E499" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F499" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>46119</v>
       </c>
       <c r="E500" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F500" t="inlineStr">
         <is>
@@ -41312,7 +41312,7 @@
         <v>45631</v>
       </c>
       <c r="E501" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F501" t="inlineStr">
         <is>
@@ -41385,7 +41385,7 @@
         <v>46121</v>
       </c>
       <c r="E502" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F502" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>45727</v>
       </c>
       <c r="E503" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F503" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>46127</v>
       </c>
       <c r="E504" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F504" t="inlineStr">
         <is>
@@ -41614,7 +41614,7 @@
         <v>46127</v>
       </c>
       <c r="E505" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F505" t="inlineStr">
         <is>
@@ -41687,7 +41687,7 @@
         <v>45068</v>
       </c>
       <c r="E506" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F506" t="inlineStr">
         <is>
@@ -41760,7 +41760,7 @@
         <v>46127</v>
       </c>
       <c r="E507" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F507" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>46126</v>
       </c>
       <c r="E508" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F508" t="inlineStr">
         <is>
@@ -41911,7 +41911,7 @@
         <v>46114</v>
       </c>
       <c r="E509" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F509" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>46308</v>
       </c>
       <c r="E510" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F510" t="inlineStr">
         <is>
@@ -42067,7 +42067,7 @@
         <v>46308</v>
       </c>
       <c r="E511" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F511" t="inlineStr">
         <is>
@@ -42145,7 +42145,7 @@
         <v>44978</v>
       </c>
       <c r="E512" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F512" t="inlineStr">
         <is>
@@ -42218,7 +42218,7 @@
         <v>46128</v>
       </c>
       <c r="E513" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F513" t="inlineStr">
         <is>
@@ -42296,7 +42296,7 @@
         <v>46132</v>
       </c>
       <c r="E514" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F514" t="inlineStr">
         <is>
@@ -42369,7 +42369,7 @@
         <v>45881</v>
       </c>
       <c r="E515" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F515" t="inlineStr">
         <is>
@@ -42442,7 +42442,7 @@
         <v>45882</v>
       </c>
       <c r="E516" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F516" t="inlineStr">
         <is>
@@ -42515,7 +42515,7 @@
         <v>45275</v>
       </c>
       <c r="E517" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F517" t="inlineStr">
         <is>
@@ -42588,7 +42588,7 @@
         <v>46133</v>
       </c>
       <c r="E518" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F518" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>46114</v>
       </c>
       <c r="E519" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F519" t="inlineStr">
         <is>
@@ -42739,7 +42739,7 @@
         <v>45476</v>
       </c>
       <c r="E520" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F520" t="inlineStr">
         <is>
@@ -42812,7 +42812,7 @@
         <v>45049</v>
       </c>
       <c r="E521" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F521" t="inlineStr">
         <is>
@@ -42885,7 +42885,7 @@
         <v>45625</v>
       </c>
       <c r="E522" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F522" t="inlineStr">
         <is>
@@ -42958,7 +42958,7 @@
         <v>45202</v>
       </c>
       <c r="E523" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F523" t="inlineStr">
         <is>
@@ -43031,7 +43031,7 @@
         <v>45357</v>
       </c>
       <c r="E524" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F524" t="inlineStr">
         <is>
@@ -43104,7 +43104,7 @@
         <v>45216</v>
       </c>
       <c r="E525" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F525" t="inlineStr">
         <is>
@@ -43177,7 +43177,7 @@
         <v>46114</v>
       </c>
       <c r="E526" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F526" t="inlineStr">
         <is>
@@ -43255,7 +43255,7 @@
         <v>45555</v>
       </c>
       <c r="E527" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F527" t="inlineStr">
         <is>
@@ -43328,7 +43328,7 @@
         <v>44917</v>
       </c>
       <c r="E528" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F528" t="inlineStr">
         <is>
@@ -43401,7 +43401,7 @@
         <v>46188</v>
       </c>
       <c r="E529" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F529" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>45553</v>
       </c>
       <c r="E530" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F530" t="inlineStr">
         <is>
@@ -43552,7 +43552,7 @@
         <v>45480</v>
       </c>
       <c r="E531" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F531" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>45803</v>
       </c>
       <c r="E532" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F532" t="inlineStr">
         <is>
@@ -43698,7 +43698,7 @@
         <v>44959</v>
       </c>
       <c r="E533" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F533" t="inlineStr">
         <is>
@@ -43771,7 +43771,7 @@
         <v>45474</v>
       </c>
       <c r="E534" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F534" t="inlineStr">
         <is>
@@ -43844,7 +43844,7 @@
         <v>45509</v>
       </c>
       <c r="E535" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F535" t="inlineStr">
         <is>
@@ -43917,7 +43917,7 @@
         <v>45098</v>
       </c>
       <c r="E536" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F536" t="inlineStr">
         <is>
@@ -43990,7 +43990,7 @@
         <v>45863</v>
       </c>
       <c r="E537" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F537" t="inlineStr">
         <is>
@@ -44063,7 +44063,7 @@
         <v>44820</v>
       </c>
       <c r="E538" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F538" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>46035</v>
       </c>
       <c r="E539" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F539" t="inlineStr">
         <is>
@@ -44209,7 +44209,7 @@
         <v>45741</v>
       </c>
       <c r="E540" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F540" t="inlineStr">
         <is>
@@ -44282,7 +44282,7 @@
         <v>45670</v>
       </c>
       <c r="E541" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F541" t="inlineStr">
         <is>
@@ -44355,7 +44355,7 @@
         <v>46268</v>
       </c>
       <c r="E542" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F542" t="inlineStr">
         <is>
@@ -44428,7 +44428,7 @@
         <v>45510</v>
       </c>
       <c r="E543" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F543" t="inlineStr">
         <is>
@@ -44501,7 +44501,7 @@
         <v>45958</v>
       </c>
       <c r="E544" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F544" t="inlineStr">
         <is>
@@ -44574,7 +44574,7 @@
         <v>45834</v>
       </c>
       <c r="E545" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F545" t="inlineStr">
         <is>
@@ -44652,7 +44652,7 @@
         <v>46140</v>
       </c>
       <c r="E546" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F546" t="inlineStr">
         <is>
@@ -44725,7 +44725,7 @@
         <v>46106</v>
       </c>
       <c r="E547" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F547" t="inlineStr">
         <is>
@@ -44798,7 +44798,7 @@
         <v>45002</v>
       </c>
       <c r="E548" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F548" t="inlineStr">
         <is>
@@ -44871,7 +44871,7 @@
         <v>44966</v>
       </c>
       <c r="E549" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F549" t="inlineStr">
         <is>
@@ -44944,7 +44944,7 @@
         <v>45406</v>
       </c>
       <c r="E550" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F550" t="inlineStr">
         <is>
@@ -45017,7 +45017,7 @@
         <v>45303</v>
       </c>
       <c r="E551" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F551" t="inlineStr">
         <is>
@@ -45090,7 +45090,7 @@
         <v>45103</v>
       </c>
       <c r="E552" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F552" t="inlineStr">
         <is>
@@ -45163,7 +45163,7 @@
         <v>46316</v>
       </c>
       <c r="E553" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F553" t="inlineStr">
         <is>
@@ -45236,7 +45236,7 @@
         <v>46139</v>
       </c>
       <c r="E554" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F554" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45125</v>
       </c>
       <c r="E555" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F555" t="inlineStr">
         <is>
@@ -45387,7 +45387,7 @@
         <v>45567</v>
       </c>
       <c r="E556" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F556" t="inlineStr">
         <is>
@@ -45460,7 +45460,7 @@
         <v>45456</v>
       </c>
       <c r="E557" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F557" t="inlineStr">
         <is>
@@ -45538,7 +45538,7 @@
         <v>46036</v>
       </c>
       <c r="E558" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F558" t="inlineStr">
         <is>
@@ -45616,7 +45616,7 @@
         <v>46316</v>
       </c>
       <c r="E559" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F559" t="inlineStr">
         <is>
@@ -45689,7 +45689,7 @@
         <v>45675</v>
       </c>
       <c r="E560" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F560" t="inlineStr">
         <is>
@@ -45762,7 +45762,7 @@
         <v>45782</v>
       </c>
       <c r="E561" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F561" t="inlineStr">
         <is>
@@ -45835,7 +45835,7 @@
         <v>45732</v>
       </c>
       <c r="E562" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F562" t="inlineStr">
         <is>
@@ -45908,7 +45908,7 @@
         <v>46149</v>
       </c>
       <c r="E563" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F563" t="inlineStr">
         <is>
@@ -45986,7 +45986,7 @@
         <v>45001</v>
       </c>
       <c r="E564" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F564" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>45152</v>
       </c>
       <c r="E565" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F565" t="inlineStr">
         <is>
@@ -46132,7 +46132,7 @@
         <v>45695</v>
       </c>
       <c r="E566" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F566" t="inlineStr">
         <is>
@@ -46205,7 +46205,7 @@
         <v>46035</v>
       </c>
       <c r="E567" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F567" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>46064</v>
       </c>
       <c r="E568" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F568" t="inlineStr">
         <is>
@@ -46351,7 +46351,7 @@
         <v>46139</v>
       </c>
       <c r="E569" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F569" t="inlineStr">
         <is>
@@ -46424,7 +46424,7 @@
         <v>45630</v>
       </c>
       <c r="E570" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F570" t="inlineStr">
         <is>
@@ -46497,7 +46497,7 @@
         <v>46276</v>
       </c>
       <c r="E571" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F571" t="inlineStr">
         <is>
@@ -46570,7 +46570,7 @@
         <v>45583</v>
       </c>
       <c r="E572" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F572" t="inlineStr">
         <is>
@@ -46643,7 +46643,7 @@
         <v>44974</v>
       </c>
       <c r="E573" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F573" t="inlineStr">
         <is>
@@ -46716,7 +46716,7 @@
         <v>46030</v>
       </c>
       <c r="E574" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F574" t="inlineStr">
         <is>
@@ -46789,7 +46789,7 @@
         <v>44974</v>
       </c>
       <c r="E575" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F575" t="inlineStr">
         <is>
@@ -46862,7 +46862,7 @@
         <v>45030</v>
       </c>
       <c r="E576" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F576" t="inlineStr">
         <is>
@@ -46935,7 +46935,7 @@
         <v>45198</v>
       </c>
       <c r="E577" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F577" t="inlineStr">
         <is>
@@ -47008,7 +47008,7 @@
         <v>46146</v>
       </c>
       <c r="E578" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F578" t="inlineStr">
         <is>
@@ -47081,7 +47081,7 @@
         <v>45397</v>
       </c>
       <c r="E579" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F579" t="inlineStr">
         <is>
@@ -47154,7 +47154,7 @@
         <v>46147</v>
       </c>
       <c r="E580" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F580" t="inlineStr">
         <is>
@@ -47227,7 +47227,7 @@
         <v>46148</v>
       </c>
       <c r="E581" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F581" t="inlineStr">
         <is>
@@ -47305,7 +47305,7 @@
         <v>45232</v>
       </c>
       <c r="E582" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F582" t="inlineStr">
         <is>
@@ -47378,7 +47378,7 @@
         <v>46119</v>
       </c>
       <c r="E583" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F583" t="inlineStr">
         <is>
@@ -47451,7 +47451,7 @@
         <v>46149</v>
       </c>
       <c r="E584" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F584" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>46149</v>
       </c>
       <c r="E585" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F585" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>46092</v>
       </c>
       <c r="E586" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F586" t="inlineStr">
         <is>
@@ -47675,7 +47675,7 @@
         <v>46038</v>
       </c>
       <c r="E587" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F587" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>45994</v>
       </c>
       <c r="E588" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F588" t="inlineStr">
         <is>
@@ -47821,7 +47821,7 @@
         <v>44998</v>
       </c>
       <c r="E589" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F589" t="inlineStr">
         <is>
@@ -47894,7 +47894,7 @@
         <v>45877</v>
       </c>
       <c r="E590" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F590" t="inlineStr">
         <is>
@@ -47967,7 +47967,7 @@
         <v>45559</v>
       </c>
       <c r="E591" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F591" t="inlineStr">
         <is>
@@ -48040,7 +48040,7 @@
         <v>45121</v>
       </c>
       <c r="E592" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F592" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45623</v>
       </c>
       <c r="E593" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
@@ -48186,7 +48186,7 @@
         <v>46044</v>
       </c>
       <c r="E594" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>46052</v>
       </c>
       <c r="E595" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
@@ -48332,7 +48332,7 @@
         <v>46155</v>
       </c>
       <c r="E596" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
@@ -48410,7 +48410,7 @@
         <v>45896</v>
       </c>
       <c r="E597" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F597" t="inlineStr">
         <is>
@@ -48483,7 +48483,7 @@
         <v>45751</v>
       </c>
       <c r="E598" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F598" t="inlineStr">
         <is>
@@ -48556,7 +48556,7 @@
         <v>46043</v>
       </c>
       <c r="E599" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F599" t="inlineStr">
         <is>
@@ -48629,7 +48629,7 @@
         <v>46156</v>
       </c>
       <c r="E600" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F600" t="inlineStr">
         <is>
@@ -48702,7 +48702,7 @@
         <v>45607</v>
       </c>
       <c r="E601" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F601" t="inlineStr">
         <is>
@@ -48780,7 +48780,7 @@
         <v>46155</v>
       </c>
       <c r="E602" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F602" t="inlineStr">
         <is>
@@ -48858,7 +48858,7 @@
         <v>46156</v>
       </c>
       <c r="E603" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F603" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>45835</v>
       </c>
       <c r="E604" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F604" t="inlineStr">
         <is>
@@ -49004,7 +49004,7 @@
         <v>44998</v>
       </c>
       <c r="E605" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F605" t="inlineStr">
         <is>
@@ -49077,7 +49077,7 @@
         <v>45015</v>
       </c>
       <c r="E606" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F606" t="inlineStr">
         <is>
@@ -49150,7 +49150,7 @@
         <v>45076</v>
       </c>
       <c r="E607" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F607" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45365</v>
       </c>
       <c r="E608" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F608" t="inlineStr">
         <is>
@@ -49296,7 +49296,7 @@
         <v>45621</v>
       </c>
       <c r="E609" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F609" t="inlineStr">
         <is>
@@ -49369,7 +49369,7 @@
         <v>45027</v>
       </c>
       <c r="E610" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F610" t="inlineStr">
         <is>
@@ -49442,7 +49442,7 @@
         <v>45624</v>
       </c>
       <c r="E611" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F611" t="inlineStr">
         <is>
@@ -49515,7 +49515,7 @@
         <v>45624</v>
       </c>
       <c r="E612" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F612" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45637</v>
       </c>
       <c r="E613" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F613" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45127</v>
       </c>
       <c r="E614" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F614" t="inlineStr">
         <is>
@@ -49734,7 +49734,7 @@
         <v>45244</v>
       </c>
       <c r="E615" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F615" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>44993</v>
       </c>
       <c r="E616" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F616" t="inlineStr">
         <is>
@@ -49880,7 +49880,7 @@
         <v>44714</v>
       </c>
       <c r="E617" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F617" t="inlineStr">
         <is>
@@ -49958,7 +49958,7 @@
         <v>44967</v>
       </c>
       <c r="E618" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F618" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>45727</v>
       </c>
       <c r="E619" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F619" t="inlineStr">
         <is>
@@ -50114,7 +50114,7 @@
         <v>45183</v>
       </c>
       <c r="E620" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F620" t="inlineStr">
         <is>
@@ -50187,7 +50187,7 @@
         <v>45132</v>
       </c>
       <c r="E621" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F621" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45027</v>
       </c>
       <c r="E622" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F622" t="inlineStr">
         <is>
@@ -50333,7 +50333,7 @@
         <v>45490</v>
       </c>
       <c r="E623" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F623" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>44987</v>
       </c>
       <c r="E624" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F624" t="inlineStr">
         <is>
@@ -50479,7 +50479,7 @@
         <v>45131</v>
       </c>
       <c r="E625" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F625" t="inlineStr">
         <is>
@@ -50552,7 +50552,7 @@
         <v>45510</v>
       </c>
       <c r="E626" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F626" t="inlineStr">
         <is>
@@ -50625,7 +50625,7 @@
         <v>44501</v>
       </c>
       <c r="E627" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F627" t="inlineStr">
         <is>
@@ -50698,7 +50698,7 @@
         <v>45705</v>
       </c>
       <c r="E628" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F628" t="inlineStr">
         <is>
@@ -50771,7 +50771,7 @@
         <v>45176</v>
       </c>
       <c r="E629" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F629" t="inlineStr">
         <is>
@@ -50844,7 +50844,7 @@
         <v>45267</v>
       </c>
       <c r="E630" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F630" t="inlineStr">
         <is>
@@ -50917,7 +50917,7 @@
         <v>45369</v>
       </c>
       <c r="E631" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F631" t="inlineStr">
         <is>
@@ -50990,7 +50990,7 @@
         <v>45199</v>
       </c>
       <c r="E632" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F632" t="inlineStr">
         <is>
@@ -51063,7 +51063,7 @@
         <v>45061</v>
       </c>
       <c r="E633" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F633" t="inlineStr">
         <is>
@@ -51136,7 +51136,7 @@
         <v>45567</v>
       </c>
       <c r="E634" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F634" t="inlineStr">
         <is>
@@ -51214,7 +51214,7 @@
         <v>45203</v>
       </c>
       <c r="E635" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F635" t="inlineStr">
         <is>
@@ -51287,7 +51287,7 @@
         <v>44574</v>
       </c>
       <c r="E636" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F636" t="inlineStr">
         <is>
@@ -51360,7 +51360,7 @@
         <v>45113</v>
       </c>
       <c r="E637" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F637" t="inlineStr">
         <is>
@@ -51433,7 +51433,7 @@
         <v>44869</v>
       </c>
       <c r="E638" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F638" t="inlineStr">
         <is>
@@ -51511,7 +51511,7 @@
         <v>45567</v>
       </c>
       <c r="E639" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F639" t="inlineStr">
         <is>
@@ -51584,7 +51584,7 @@
         <v>44792</v>
       </c>
       <c r="E640" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F640" t="inlineStr">
         <is>
@@ -51657,7 +51657,7 @@
         <v>45112</v>
       </c>
       <c r="E641" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F641" t="inlineStr">
         <is>
@@ -51730,7 +51730,7 @@
         <v>45625</v>
       </c>
       <c r="E642" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F642" t="inlineStr">
         <is>
@@ -51803,7 +51803,7 @@
         <v>44875</v>
       </c>
       <c r="E643" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F643" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45467</v>
       </c>
       <c r="E644" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F644" t="inlineStr">
         <is>
@@ -51949,7 +51949,7 @@
         <v>44749</v>
       </c>
       <c r="E645" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F645" t="inlineStr">
         <is>
@@ -52027,7 +52027,7 @@
         <v>44929</v>
       </c>
       <c r="E646" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F646" t="inlineStr">
         <is>
@@ -52105,7 +52105,7 @@
         <v>45455</v>
       </c>
       <c r="E647" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F647" t="inlineStr">
         <is>
@@ -52183,7 +52183,7 @@
         <v>45103</v>
       </c>
       <c r="E648" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F648" t="inlineStr">
         <is>
@@ -52256,7 +52256,7 @@
         <v>44915</v>
       </c>
       <c r="E649" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F649" t="inlineStr">
         <is>
@@ -52329,7 +52329,7 @@
         <v>45061</v>
       </c>
       <c r="E650" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F650" t="inlineStr">
         <is>
@@ -52402,7 +52402,7 @@
         <v>45756</v>
       </c>
       <c r="E651" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F651" t="inlineStr">
         <is>
@@ -52475,7 +52475,7 @@
         <v>44909</v>
       </c>
       <c r="E652" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F652" t="inlineStr">
         <is>
@@ -52548,7 +52548,7 @@
         <v>45231</v>
       </c>
       <c r="E653" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F653" t="inlineStr">
         <is>
@@ -52621,7 +52621,7 @@
         <v>45103</v>
       </c>
       <c r="E654" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F654" t="inlineStr">
         <is>
@@ -52699,7 +52699,7 @@
         <v>45015</v>
       </c>
       <c r="E655" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F655" t="inlineStr">
         <is>
@@ -52772,7 +52772,7 @@
         <v>45561</v>
       </c>
       <c r="E656" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F656" t="inlineStr">
         <is>
@@ -52845,7 +52845,7 @@
         <v>45518</v>
       </c>
       <c r="E657" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F657" t="inlineStr">
         <is>
@@ -52918,7 +52918,7 @@
         <v>45664</v>
       </c>
       <c r="E658" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F658" t="inlineStr">
         <is>
@@ -52991,7 +52991,7 @@
         <v>44992</v>
       </c>
       <c r="E659" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F659" t="inlineStr">
         <is>
@@ -53064,7 +53064,7 @@
         <v>45258</v>
       </c>
       <c r="E660" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F660" t="inlineStr">
         <is>
@@ -53137,7 +53137,7 @@
         <v>45376</v>
       </c>
       <c r="E661" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F661" t="inlineStr">
         <is>
@@ -53210,7 +53210,7 @@
         <v>45267</v>
       </c>
       <c r="E662" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F662" t="inlineStr">
         <is>
@@ -53283,7 +53283,7 @@
         <v>44959</v>
       </c>
       <c r="E663" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F663" t="inlineStr">
         <is>
@@ -53356,7 +53356,7 @@
         <v>45447</v>
       </c>
       <c r="E664" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F664" t="inlineStr">
         <is>
@@ -53429,7 +53429,7 @@
         <v>45219</v>
       </c>
       <c r="E665" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F665" t="inlineStr">
         <is>
@@ -53502,7 +53502,7 @@
         <v>45195</v>
       </c>
       <c r="E666" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F666" t="inlineStr">
         <is>
@@ -53575,7 +53575,7 @@
         <v>45559</v>
       </c>
       <c r="E667" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F667" t="inlineStr">
         <is>
@@ -53648,7 +53648,7 @@
         <v>45152</v>
       </c>
       <c r="E668" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F668" t="inlineStr">
         <is>
@@ -53721,7 +53721,7 @@
         <v>44951</v>
       </c>
       <c r="E669" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F669" t="inlineStr">
         <is>
@@ -53794,7 +53794,7 @@
         <v>44994</v>
       </c>
       <c r="E670" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F670" t="inlineStr">
         <is>
@@ -53867,7 +53867,7 @@
         <v>45004</v>
       </c>
       <c r="E671" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F671" t="inlineStr">
         <is>
@@ -53940,7 +53940,7 @@
         <v>45376</v>
       </c>
       <c r="E672" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F672" t="inlineStr">
         <is>
@@ -54013,7 +54013,7 @@
         <v>45097</v>
       </c>
       <c r="E673" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F673" t="inlineStr">
         <is>
@@ -54086,7 +54086,7 @@
         <v>45110</v>
       </c>
       <c r="E674" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F674" t="inlineStr">
         <is>
@@ -54159,7 +54159,7 @@
         <v>45544</v>
       </c>
       <c r="E675" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F675" t="inlineStr">
         <is>
@@ -54232,7 +54232,7 @@
         <v>45317</v>
       </c>
       <c r="E676" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F676" t="inlineStr">
         <is>
@@ -54305,7 +54305,7 @@
         <v>44986</v>
       </c>
       <c r="E677" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F677" t="inlineStr">
         <is>
@@ -54378,7 +54378,7 @@
         <v>45096</v>
       </c>
       <c r="E678" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F678" t="inlineStr">
         <is>
@@ -54451,7 +54451,7 @@
         <v>45027</v>
       </c>
       <c r="E679" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F679" t="inlineStr">
         <is>
@@ -54524,7 +54524,7 @@
         <v>44580</v>
       </c>
       <c r="E680" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F680" t="inlineStr">
         <is>
@@ -54597,7 +54597,7 @@
         <v>45595</v>
       </c>
       <c r="E681" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F681" t="inlineStr">
         <is>
@@ -54670,7 +54670,7 @@
         <v>45127</v>
       </c>
       <c r="E682" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F682" t="inlineStr">
         <is>
@@ -54743,7 +54743,7 @@
         <v>45609</v>
       </c>
       <c r="E683" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F683" t="inlineStr">
         <is>
@@ -54816,7 +54816,7 @@
         <v>45001</v>
       </c>
       <c r="E684" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F684" t="inlineStr">
         <is>
@@ -54889,7 +54889,7 @@
         <v>45428</v>
       </c>
       <c r="E685" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F685" t="inlineStr">
         <is>
@@ -54962,7 +54962,7 @@
         <v>45362</v>
       </c>
       <c r="E686" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F686" t="inlineStr">
         <is>
@@ -55035,7 +55035,7 @@
         <v>45169</v>
       </c>
       <c r="E687" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F687" t="inlineStr">
         <is>
@@ -55108,7 +55108,7 @@
         <v>45553</v>
       </c>
       <c r="E688" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F688" t="inlineStr">
         <is>
@@ -55186,7 +55186,7 @@
         <v>45608</v>
       </c>
       <c r="E689" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F689" t="inlineStr">
         <is>
@@ -55259,7 +55259,7 @@
         <v>45509</v>
       </c>
       <c r="E690" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F690" t="inlineStr">
         <is>
@@ -55332,7 +55332,7 @@
         <v>45608</v>
       </c>
       <c r="E691" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F691" t="inlineStr">
         <is>
@@ -55405,7 +55405,7 @@
         <v>44643</v>
       </c>
       <c r="E692" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F692" t="inlineStr">
         <is>
@@ -55478,7 +55478,7 @@
         <v>45727</v>
       </c>
       <c r="E693" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F693" t="inlineStr">
         <is>
@@ -55551,7 +55551,7 @@
         <v>45169</v>
       </c>
       <c r="E694" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F694" t="inlineStr">
         <is>
@@ -55624,7 +55624,7 @@
         <v>45198</v>
       </c>
       <c r="E695" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F695" t="inlineStr">
         <is>
@@ -55697,7 +55697,7 @@
         <v>45165</v>
       </c>
       <c r="E696" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F696" t="inlineStr">
         <is>
@@ -55770,7 +55770,7 @@
         <v>45574</v>
       </c>
       <c r="E697" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F697" t="inlineStr">
         <is>
@@ -55843,7 +55843,7 @@
         <v>45608</v>
       </c>
       <c r="E698" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F698" t="inlineStr">
         <is>
@@ -55916,7 +55916,7 @@
         <v>45200</v>
       </c>
       <c r="E699" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F699" t="inlineStr">
         <is>
@@ -55989,7 +55989,7 @@
         <v>45169</v>
       </c>
       <c r="E700" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F700" t="inlineStr">
         <is>
@@ -56062,7 +56062,7 @@
         <v>45667</v>
       </c>
       <c r="E701" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F701" t="inlineStr">
         <is>
@@ -56135,7 +56135,7 @@
         <v>45180</v>
       </c>
       <c r="E702" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F702" t="inlineStr">
         <is>
@@ -56208,7 +56208,7 @@
         <v>45351</v>
       </c>
       <c r="E703" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F703" t="inlineStr">
         <is>
@@ -56281,7 +56281,7 @@
         <v>45244</v>
       </c>
       <c r="E704" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F704" t="inlineStr">
         <is>
@@ -56354,7 +56354,7 @@
         <v>45160</v>
       </c>
       <c r="E705" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F705" t="inlineStr">
         <is>
@@ -56427,7 +56427,7 @@
         <v>45568</v>
       </c>
       <c r="E706" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F706" t="inlineStr">
         <is>
@@ -56500,7 +56500,7 @@
         <v>45167</v>
       </c>
       <c r="E707" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F707" t="inlineStr">
         <is>
@@ -56573,7 +56573,7 @@
         <v>45415</v>
       </c>
       <c r="E708" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F708" t="inlineStr">
         <is>
@@ -56646,7 +56646,7 @@
         <v>45261</v>
       </c>
       <c r="E709" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F709" t="inlineStr">
         <is>
@@ -56719,7 +56719,7 @@
         <v>45261</v>
       </c>
       <c r="E710" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F710" t="inlineStr">
         <is>
@@ -56792,7 +56792,7 @@
         <v>45707</v>
       </c>
       <c r="E711" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F711" t="inlineStr">
         <is>
@@ -56865,7 +56865,7 @@
         <v>45252</v>
       </c>
       <c r="E712" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F712" t="inlineStr">
         <is>
@@ -56938,7 +56938,7 @@
         <v>44679</v>
       </c>
       <c r="E713" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F713" t="inlineStr">
         <is>
@@ -57016,7 +57016,7 @@
         <v>45256</v>
       </c>
       <c r="E714" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F714" t="inlineStr">
         <is>
@@ -57089,7 +57089,7 @@
         <v>45127</v>
       </c>
       <c r="E715" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F715" t="inlineStr">
         <is>
@@ -57162,7 +57162,7 @@
         <v>45127</v>
       </c>
       <c r="E716" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F716" t="inlineStr">
         <is>
@@ -57235,7 +57235,7 @@
         <v>44714</v>
       </c>
       <c r="E717" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F717" t="inlineStr">
         <is>
@@ -57313,7 +57313,7 @@
         <v>45110</v>
       </c>
       <c r="E718" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F718" t="inlineStr">
         <is>
@@ -57386,7 +57386,7 @@
         <v>45197</v>
       </c>
       <c r="E719" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F719" t="inlineStr">
         <is>
@@ -57459,7 +57459,7 @@
         <v>45109</v>
       </c>
       <c r="E720" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F720" t="inlineStr">
         <is>
@@ -57532,7 +57532,7 @@
         <v>45314</v>
       </c>
       <c r="E721" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F721" t="inlineStr">
         <is>
@@ -57605,7 +57605,7 @@
         <v>45219</v>
       </c>
       <c r="E722" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F722" t="inlineStr">
         <is>
@@ -57678,7 +57678,7 @@
         <v>45219</v>
       </c>
       <c r="E723" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F723" t="inlineStr">
         <is>
@@ -57751,7 +57751,7 @@
         <v>45257</v>
       </c>
       <c r="E724" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F724" t="inlineStr">
         <is>
@@ -57829,7 +57829,7 @@
         <v>44846</v>
       </c>
       <c r="E725" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F725" t="inlineStr">
         <is>
@@ -57902,7 +57902,7 @@
         <v>45259</v>
       </c>
       <c r="E726" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F726" t="inlineStr">
         <is>
@@ -57975,7 +57975,7 @@
         <v>45264</v>
       </c>
       <c r="E727" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F727" t="inlineStr">
         <is>
@@ -58048,7 +58048,7 @@
         <v>45104</v>
       </c>
       <c r="E728" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F728" t="inlineStr">
         <is>
@@ -58126,7 +58126,7 @@
         <v>45307</v>
       </c>
       <c r="E729" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F729" t="inlineStr">
         <is>
@@ -58199,7 +58199,7 @@
         <v>45446</v>
       </c>
       <c r="E730" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F730" t="inlineStr">
         <is>
@@ -58272,7 +58272,7 @@
         <v>45373</v>
       </c>
       <c r="E731" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F731" t="inlineStr">
         <is>
@@ -58345,7 +58345,7 @@
         <v>45266</v>
       </c>
       <c r="E732" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F732" t="inlineStr">
         <is>
@@ -58418,7 +58418,7 @@
         <v>44902</v>
       </c>
       <c r="E733" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F733" t="inlineStr">
         <is>
@@ -58491,7 +58491,7 @@
         <v>45264</v>
       </c>
       <c r="E734" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F734" t="inlineStr">
         <is>
@@ -58564,7 +58564,7 @@
         <v>45261</v>
       </c>
       <c r="E735" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F735" t="inlineStr">
         <is>
@@ -58637,7 +58637,7 @@
         <v>45397</v>
       </c>
       <c r="E736" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F736" t="inlineStr">
         <is>
@@ -58710,7 +58710,7 @@
         <v>44846</v>
       </c>
       <c r="E737" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F737" t="inlineStr">
         <is>
@@ -58783,7 +58783,7 @@
         <v>45272</v>
       </c>
       <c r="E738" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F738" t="inlineStr">
         <is>
@@ -58856,7 +58856,7 @@
         <v>45266</v>
       </c>
       <c r="E739" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F739" t="inlineStr">
         <is>
@@ -58929,7 +58929,7 @@
         <v>44785</v>
       </c>
       <c r="E740" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F740" t="inlineStr">
         <is>
@@ -59002,7 +59002,7 @@
         <v>45747</v>
       </c>
       <c r="E741" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F741" t="inlineStr">
         <is>
@@ -59075,7 +59075,7 @@
         <v>45201</v>
       </c>
       <c r="E742" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F742" t="inlineStr">
         <is>
@@ -59148,7 +59148,7 @@
         <v>45037</v>
       </c>
       <c r="E743" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F743" t="inlineStr">
         <is>
@@ -59221,7 +59221,7 @@
         <v>45621</v>
       </c>
       <c r="E744" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
@@ -59294,7 +59294,7 @@
         <v>45197</v>
       </c>
       <c r="E745" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -59367,7 +59367,7 @@
         <v>45216</v>
       </c>
       <c r="E746" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -59440,7 +59440,7 @@
         <v>45044</v>
       </c>
       <c r="E747" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -59513,7 +59513,7 @@
         <v>45418</v>
       </c>
       <c r="E748" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
@@ -59586,7 +59586,7 @@
         <v>45282</v>
       </c>
       <c r="E749" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
@@ -59659,7 +59659,7 @@
         <v>45552</v>
       </c>
       <c r="E750" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
@@ -59732,7 +59732,7 @@
         <v>45523</v>
       </c>
       <c r="E751" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -59805,7 +59805,7 @@
         <v>45035</v>
       </c>
       <c r="E752" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -59878,7 +59878,7 @@
         <v>45001</v>
       </c>
       <c r="E753" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -59951,7 +59951,7 @@
         <v>45478</v>
       </c>
       <c r="E754" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -60024,7 +60024,7 @@
         <v>45261</v>
       </c>
       <c r="E755" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
@@ -60097,7 +60097,7 @@
         <v>44578</v>
       </c>
       <c r="E756" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
@@ -60170,7 +60170,7 @@
         <v>44652</v>
       </c>
       <c r="E757" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
@@ -60243,7 +60243,7 @@
         <v>45074</v>
       </c>
       <c r="E758" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -60321,7 +60321,7 @@
         <v>45257</v>
       </c>
       <c r="E759" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -60394,7 +60394,7 @@
         <v>45097</v>
       </c>
       <c r="E760" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -60467,7 +60467,7 @@
         <v>45351</v>
       </c>
       <c r="E761" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -60545,7 +60545,7 @@
         <v>44809</v>
       </c>
       <c r="E762" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -60618,7 +60618,7 @@
         <v>45097</v>
       </c>
       <c r="E763" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -60691,7 +60691,7 @@
         <v>45133</v>
       </c>
       <c r="E764" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
@@ -60764,7 +60764,7 @@
         <v>45446</v>
       </c>
       <c r="E765" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -60842,7 +60842,7 @@
         <v>45701</v>
       </c>
       <c r="E766" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
@@ -60920,7 +60920,7 @@
         <v>45701</v>
       </c>
       <c r="E767" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
@@ -60998,7 +60998,7 @@
         <v>45708</v>
       </c>
       <c r="E768" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -61076,7 +61076,7 @@
         <v>45799</v>
       </c>
       <c r="E769" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F769" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45819</v>
       </c>
       <c r="E770" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
@@ -61222,7 +61222,7 @@
         <v>45824</v>
       </c>
       <c r="E771" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -61295,7 +61295,7 @@
         <v>45835</v>
       </c>
       <c r="E772" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -61368,7 +61368,7 @@
         <v>45904</v>
       </c>
       <c r="E773" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -61441,7 +61441,7 @@
         <v>45943</v>
       </c>
       <c r="E774" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -61514,7 +61514,7 @@
         <v>45964</v>
       </c>
       <c r="E775" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
@@ -61592,7 +61592,7 @@
         <v>46038</v>
       </c>
       <c r="E776" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -61670,7 +61670,7 @@
         <v>46043</v>
       </c>
       <c r="E777" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -61743,7 +61743,7 @@
         <v>46052</v>
       </c>
       <c r="E778" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
@@ -61821,7 +61821,7 @@
         <v>44649</v>
       </c>
       <c r="E779" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
@@ -61894,7 +61894,7 @@
         <v>46066</v>
       </c>
       <c r="E780" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
@@ -61967,7 +61967,7 @@
         <v>46076</v>
       </c>
       <c r="E781" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -62040,7 +62040,7 @@
         <v>46133</v>
       </c>
       <c r="E782" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -62118,7 +62118,7 @@
         <v>46134</v>
       </c>
       <c r="E783" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
@@ -62191,7 +62191,7 @@
         <v>45727</v>
       </c>
       <c r="E784" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
